--- a/reports/2026-09-14.xlsx
+++ b/reports/2026-09-14.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C12843B-EF60-C84B-87FE-8BA6ADCE6AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0956AE35-19C7-4146-BA46-CFC388121D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3535,21 +3535,724 @@
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="17" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="44" fillId="10" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="44" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="60" fillId="17" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="60" fillId="17" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="60" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="60" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="45" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="45" fillId="18" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="10" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="10" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="66" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="66" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="66" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="66" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="66" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="66" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="66" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="66" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="94" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="94" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="23" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="78" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="76" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3577,15 +4280,6 @@
     <xf numFmtId="0" fontId="80" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="78" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3621,700 +4315,6 @@
     </xf>
     <xf numFmtId="0" fontId="81" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="94" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="94" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="66" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="66" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="66" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="66" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="66" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="17" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="66" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="66" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="66" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="45" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="45" fillId="18" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="43" fillId="10" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="43" fillId="10" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="43" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="43" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="43" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="10" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="60" fillId="17" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="60" fillId="17" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="60" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="60" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="20" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="20" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="20" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="17" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="44" fillId="10" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="44" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4729,16 +4729,16 @@
     <row r="1" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="4"/>
-      <c r="C1" s="513" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="513"/>
-      <c r="E1" s="513"/>
-      <c r="F1" s="513"/>
-      <c r="G1" s="513"/>
-      <c r="H1" s="513"/>
-      <c r="I1" s="513"/>
-      <c r="J1" s="513"/>
+      <c r="C1" s="427" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="427"/>
+      <c r="E1" s="427"/>
+      <c r="F1" s="427"/>
+      <c r="G1" s="427"/>
+      <c r="H1" s="427"/>
+      <c r="I1" s="427"/>
+      <c r="J1" s="427"/>
       <c r="K1" s="67" t="s">
         <v>223</v>
       </c>
@@ -4769,11 +4769,11 @@
     <row r="3" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
-      <c r="C3" s="517" t="s">
+      <c r="C3" s="431" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="518"/>
-      <c r="E3" s="518"/>
+      <c r="D3" s="432"/>
+      <c r="E3" s="432"/>
       <c r="F3" s="89" t="s">
         <v>1</v>
       </c>
@@ -4786,24 +4786,24 @@
       <c r="I3" s="59" t="s">
         <v>101</v>
       </c>
-      <c r="J3" s="514" t="s">
+      <c r="J3" s="428" t="s">
         <v>102</v>
       </c>
-      <c r="K3" s="515"/>
-      <c r="L3" s="515"/>
-      <c r="M3" s="516"/>
-      <c r="N3" s="516"/>
-      <c r="O3" s="516"/>
-      <c r="P3" s="516"/>
+      <c r="K3" s="429"/>
+      <c r="L3" s="429"/>
+      <c r="M3" s="430"/>
+      <c r="N3" s="430"/>
+      <c r="O3" s="430"/>
+      <c r="P3" s="430"/>
     </row>
     <row r="4" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="574"/>
-      <c r="C4" s="519" t="s">
+      <c r="B4" s="344"/>
+      <c r="C4" s="433" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="520"/>
-      <c r="E4" s="520"/>
+      <c r="D4" s="434"/>
+      <c r="E4" s="434"/>
       <c r="F4" s="91">
         <v>58</v>
       </c>
@@ -4812,10 +4812,10 @@
       </c>
       <c r="H4" s="92"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="524" t="s">
+      <c r="J4" s="438" t="s">
         <v>93</v>
       </c>
-      <c r="K4" s="525"/>
+      <c r="K4" s="439"/>
       <c r="L4" s="291" t="s">
         <v>175</v>
       </c>
@@ -4837,12 +4837,12 @@
     </row>
     <row r="5" spans="1:23" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="574"/>
-      <c r="C5" s="530" t="s">
+      <c r="B5" s="344"/>
+      <c r="C5" s="369" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="531"/>
-      <c r="E5" s="531"/>
+      <c r="D5" s="370"/>
+      <c r="E5" s="370"/>
       <c r="F5" s="91">
         <v>579</v>
       </c>
@@ -4853,10 +4853,10 @@
         <v>7</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="532" t="s">
+      <c r="J5" s="444" t="s">
         <v>56</v>
       </c>
-      <c r="K5" s="533"/>
+      <c r="K5" s="445"/>
       <c r="L5" s="292" t="s">
         <v>184</v>
       </c>
@@ -4878,12 +4878,12 @@
     </row>
     <row r="6" spans="1:23" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
-      <c r="B6" s="574"/>
-      <c r="C6" s="519" t="s">
+      <c r="B6" s="344"/>
+      <c r="C6" s="433" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="520"/>
-      <c r="E6" s="520"/>
+      <c r="D6" s="434"/>
+      <c r="E6" s="434"/>
       <c r="F6" s="91">
         <v>503</v>
       </c>
@@ -4894,10 +4894,10 @@
         <v>7</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="485" t="s">
+      <c r="J6" s="345" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="486"/>
+      <c r="K6" s="346"/>
       <c r="L6" s="275" t="s">
         <v>185</v>
       </c>
@@ -4919,12 +4919,12 @@
     </row>
     <row r="7" spans="1:23" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
-      <c r="B7" s="574"/>
-      <c r="C7" s="519" t="s">
+      <c r="B7" s="344"/>
+      <c r="C7" s="433" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="520"/>
-      <c r="E7" s="520"/>
+      <c r="D7" s="434"/>
+      <c r="E7" s="434"/>
       <c r="F7" s="164">
         <f>F4+F5-F6</f>
         <v>134</v>
@@ -4937,10 +4937,10 @@
         <v>7</v>
       </c>
       <c r="I7" s="8"/>
-      <c r="J7" s="498" t="s">
+      <c r="J7" s="412" t="s">
         <v>57</v>
       </c>
-      <c r="K7" s="499"/>
+      <c r="K7" s="413"/>
       <c r="L7" s="276">
         <v>0</v>
       </c>
@@ -4963,11 +4963,11 @@
     <row r="8" spans="1:23" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="528" t="s">
+      <c r="C8" s="442" t="s">
         <v>117</v>
       </c>
-      <c r="D8" s="529"/>
-      <c r="E8" s="529"/>
+      <c r="D8" s="443"/>
+      <c r="E8" s="443"/>
       <c r="F8" s="103">
         <v>0</v>
       </c>
@@ -4976,10 +4976,10 @@
       </c>
       <c r="H8" s="95"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="485" t="s">
+      <c r="J8" s="345" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="500"/>
+      <c r="K8" s="414"/>
       <c r="L8" s="276">
         <v>43481.85</v>
       </c>
@@ -5006,10 +5006,10 @@
       <c r="D9" s="10"/>
       <c r="E9" s="4"/>
       <c r="I9" s="11"/>
-      <c r="J9" s="501" t="s">
+      <c r="J9" s="415" t="s">
         <v>58</v>
       </c>
-      <c r="K9" s="502"/>
+      <c r="K9" s="416"/>
       <c r="L9" s="277">
         <f>50000-L8</f>
         <v>6518.1500000000015</v>
@@ -5036,12 +5036,12 @@
     </row>
     <row r="10" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="574"/>
-      <c r="C10" s="521" t="s">
+      <c r="B10" s="344"/>
+      <c r="C10" s="435" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="522"/>
-      <c r="E10" s="523"/>
+      <c r="D10" s="436"/>
+      <c r="E10" s="437"/>
       <c r="F10" s="89" t="s">
         <v>1</v>
       </c>
@@ -5052,14 +5052,14 @@
         <v>3</v>
       </c>
       <c r="I10" s="12"/>
-      <c r="J10" s="535" t="s">
+      <c r="J10" s="447" t="s">
         <v>147</v>
       </c>
-      <c r="K10" s="536"/>
-      <c r="L10" s="526">
+      <c r="K10" s="448"/>
+      <c r="L10" s="440">
         <v>22500</v>
       </c>
-      <c r="M10" s="527"/>
+      <c r="M10" s="441"/>
       <c r="N10" s="104"/>
       <c r="O10" s="104"/>
       <c r="P10" s="104"/>
@@ -5069,12 +5069,12 @@
     </row>
     <row r="11" spans="1:23" ht="23.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
-      <c r="B11" s="574"/>
-      <c r="C11" s="485" t="s">
+      <c r="B11" s="344"/>
+      <c r="C11" s="345" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="486"/>
-      <c r="E11" s="487"/>
+      <c r="D11" s="346"/>
+      <c r="E11" s="371"/>
       <c r="F11" s="69">
         <v>127855</v>
       </c>
@@ -5085,29 +5085,29 @@
         <v>146223.87</v>
       </c>
       <c r="I11" s="12"/>
-      <c r="J11" s="537" t="s">
+      <c r="J11" s="449" t="s">
         <v>60</v>
       </c>
-      <c r="K11" s="538"/>
-      <c r="L11" s="506">
+      <c r="K11" s="450"/>
+      <c r="L11" s="420">
         <v>13100</v>
       </c>
-      <c r="M11" s="507"/>
+      <c r="M11" s="421"/>
       <c r="N11" s="104"/>
       <c r="O11" s="86"/>
-      <c r="P11" s="534"/>
-      <c r="Q11" s="534"/>
-      <c r="R11" s="534"/>
+      <c r="P11" s="446"/>
+      <c r="Q11" s="446"/>
+      <c r="R11" s="446"/>
       <c r="S11" s="107"/>
     </row>
     <row r="12" spans="1:23" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
-      <c r="B12" s="574"/>
-      <c r="C12" s="530" t="s">
+      <c r="B12" s="344"/>
+      <c r="C12" s="369" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="531"/>
-      <c r="E12" s="531"/>
+      <c r="D12" s="370"/>
+      <c r="E12" s="370"/>
       <c r="F12" s="69">
         <v>33234</v>
       </c>
@@ -5120,10 +5120,10 @@
       <c r="I12" s="12"/>
       <c r="N12" s="105"/>
       <c r="O12" s="86"/>
-      <c r="T12" s="491" t="s">
+      <c r="T12" s="454" t="s">
         <v>211</v>
       </c>
-      <c r="U12" s="492"/>
+      <c r="U12" s="455"/>
       <c r="V12" s="321" t="s">
         <v>49</v>
       </c>
@@ -5133,12 +5133,12 @@
     </row>
     <row r="13" spans="1:23" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
-      <c r="B13" s="574"/>
-      <c r="C13" s="485" t="s">
+      <c r="B13" s="344"/>
+      <c r="C13" s="345" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="486"/>
-      <c r="E13" s="487"/>
+      <c r="D13" s="346"/>
+      <c r="E13" s="371"/>
       <c r="F13" s="69">
         <f>24789+8526+3350+455</f>
         <v>37120</v>
@@ -5150,20 +5150,20 @@
         <v>17945</v>
       </c>
       <c r="I13" s="12"/>
-      <c r="J13" s="521" t="s">
+      <c r="J13" s="435" t="s">
         <v>192</v>
       </c>
-      <c r="K13" s="522"/>
-      <c r="L13" s="522"/>
-      <c r="M13" s="523"/>
+      <c r="K13" s="436"/>
+      <c r="L13" s="436"/>
+      <c r="M13" s="437"/>
       <c r="N13" s="143" t="s">
         <v>95</v>
       </c>
       <c r="O13" s="106"/>
-      <c r="T13" s="491" t="s">
+      <c r="T13" s="454" t="s">
         <v>212</v>
       </c>
-      <c r="U13" s="491"/>
+      <c r="U13" s="454"/>
       <c r="V13" s="313">
         <f>N19+N20</f>
         <v>94908</v>
@@ -5175,12 +5175,12 @@
     </row>
     <row r="14" spans="1:23" s="13" customFormat="1" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14"/>
-      <c r="B14" s="575"/>
-      <c r="C14" s="586" t="s">
+      <c r="B14" s="347"/>
+      <c r="C14" s="372" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="587"/>
-      <c r="E14" s="588"/>
+      <c r="D14" s="373"/>
+      <c r="E14" s="374"/>
       <c r="F14" s="73">
         <f>F11+F12-F13</f>
         <v>123969</v>
@@ -5194,61 +5194,61 @@
         <v>159569.28</v>
       </c>
       <c r="I14" s="15"/>
-      <c r="J14" s="479" t="s">
+      <c r="J14" s="386" t="s">
         <v>2</v>
       </c>
-      <c r="K14" s="480"/>
-      <c r="L14" s="480"/>
-      <c r="M14" s="481"/>
+      <c r="K14" s="387"/>
+      <c r="L14" s="387"/>
+      <c r="M14" s="339"/>
       <c r="N14" s="144"/>
       <c r="O14" s="16"/>
       <c r="P14" s="300"/>
-      <c r="T14" s="511"/>
-      <c r="U14" s="512"/>
+      <c r="T14" s="425"/>
+      <c r="U14" s="426"/>
       <c r="V14" s="319"/>
       <c r="W14" s="319"/>
     </row>
     <row r="15" spans="1:23" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="574"/>
-      <c r="C15" s="503"/>
-      <c r="D15" s="504"/>
-      <c r="E15" s="505"/>
+      <c r="B15" s="344"/>
+      <c r="C15" s="417"/>
+      <c r="D15" s="418"/>
+      <c r="E15" s="419"/>
       <c r="F15" s="75"/>
       <c r="G15" s="76"/>
       <c r="H15" s="76"/>
       <c r="I15" s="17"/>
-      <c r="J15" s="508" t="s">
+      <c r="J15" s="422" t="s">
         <v>138</v>
       </c>
-      <c r="K15" s="509"/>
-      <c r="L15" s="509"/>
-      <c r="M15" s="510"/>
+      <c r="K15" s="423"/>
+      <c r="L15" s="423"/>
+      <c r="M15" s="424"/>
       <c r="N15" s="153">
         <v>79963</v>
       </c>
       <c r="O15" s="18"/>
-      <c r="T15" s="491" t="s">
+      <c r="T15" s="454" t="s">
         <v>213</v>
       </c>
-      <c r="U15" s="491"/>
+      <c r="U15" s="454"/>
       <c r="V15" s="312">
         <f>N31+N32</f>
         <v>37607</v>
       </c>
       <c r="W15" s="312">
         <f>N26+N27+N28</f>
-        <v>116843</v>
+        <v>113728</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="21" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
-      <c r="B16" s="574"/>
-      <c r="C16" s="476" t="s">
+      <c r="B16" s="344"/>
+      <c r="C16" s="400" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="477"/>
-      <c r="E16" s="478"/>
+      <c r="D16" s="401"/>
+      <c r="E16" s="402"/>
       <c r="F16" s="89" t="s">
         <v>49</v>
       </c>
@@ -5259,12 +5259,12 @@
         <v>3</v>
       </c>
       <c r="I16" s="17"/>
-      <c r="J16" s="482" t="s">
+      <c r="J16" s="451" t="s">
         <v>149</v>
       </c>
-      <c r="K16" s="483"/>
-      <c r="L16" s="483"/>
-      <c r="M16" s="484"/>
+      <c r="K16" s="452"/>
+      <c r="L16" s="452"/>
+      <c r="M16" s="453"/>
       <c r="N16" s="154">
         <v>13414</v>
       </c>
@@ -5272,19 +5272,19 @@
       <c r="Q16" s="65"/>
       <c r="R16" s="65"/>
       <c r="S16" s="65"/>
-      <c r="T16" s="493"/>
-      <c r="U16" s="494"/>
+      <c r="T16" s="456"/>
+      <c r="U16" s="457"/>
       <c r="V16" s="320"/>
       <c r="W16" s="320"/>
     </row>
     <row r="17" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="574"/>
-      <c r="C17" s="485" t="s">
+      <c r="B17" s="344"/>
+      <c r="C17" s="345" t="s">
         <v>123</v>
       </c>
-      <c r="D17" s="486"/>
-      <c r="E17" s="487"/>
+      <c r="D17" s="346"/>
+      <c r="E17" s="371"/>
       <c r="F17" s="71">
         <f>67483+31402</f>
         <v>98885</v>
@@ -5297,12 +5297,12 @@
         <v>65355.519999999997</v>
       </c>
       <c r="I17" s="17"/>
-      <c r="J17" s="488" t="s">
+      <c r="J17" s="375" t="s">
         <v>150</v>
       </c>
-      <c r="K17" s="489"/>
-      <c r="L17" s="489"/>
-      <c r="M17" s="490"/>
+      <c r="K17" s="376"/>
+      <c r="L17" s="376"/>
+      <c r="M17" s="377"/>
       <c r="N17" s="154">
         <v>4272</v>
       </c>
@@ -5325,12 +5325,12 @@
     </row>
     <row r="18" spans="1:23" ht="21" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
-      <c r="B18" s="574"/>
-      <c r="C18" s="485" t="s">
+      <c r="B18" s="344"/>
+      <c r="C18" s="345" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="486"/>
-      <c r="E18" s="487"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="371"/>
       <c r="F18" s="71">
         <v>15989</v>
       </c>
@@ -5341,12 +5341,12 @@
         <v>53150.84</v>
       </c>
       <c r="I18" s="17"/>
-      <c r="J18" s="495" t="s">
+      <c r="J18" s="397" t="s">
         <v>94</v>
       </c>
-      <c r="K18" s="496"/>
-      <c r="L18" s="496"/>
-      <c r="M18" s="497"/>
+      <c r="K18" s="398"/>
+      <c r="L18" s="398"/>
+      <c r="M18" s="399"/>
       <c r="N18" s="150"/>
       <c r="U18" t="s">
         <v>5</v>
@@ -5359,12 +5359,12 @@
     </row>
     <row r="19" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="B19" s="574"/>
-      <c r="C19" s="485" t="s">
+      <c r="B19" s="344"/>
+      <c r="C19" s="345" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="486"/>
-      <c r="E19" s="487"/>
+      <c r="D19" s="346"/>
+      <c r="E19" s="371"/>
       <c r="F19" s="71">
         <v>8415</v>
       </c>
@@ -5375,24 +5375,24 @@
         <v>41062.92</v>
       </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="488" t="s">
+      <c r="J19" s="375" t="s">
         <v>151</v>
       </c>
-      <c r="K19" s="489"/>
-      <c r="L19" s="489"/>
-      <c r="M19" s="490"/>
+      <c r="K19" s="376"/>
+      <c r="L19" s="376"/>
+      <c r="M19" s="377"/>
       <c r="N19" s="150">
         <v>59467</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
-      <c r="B20" s="574"/>
-      <c r="C20" s="485" t="s">
+      <c r="B20" s="344"/>
+      <c r="C20" s="345" t="s">
         <v>158</v>
       </c>
-      <c r="D20" s="486"/>
-      <c r="E20" s="487"/>
+      <c r="D20" s="346"/>
+      <c r="E20" s="371"/>
       <c r="F20" s="71">
         <v>680</v>
       </c>
@@ -5401,24 +5401,24 @@
       </c>
       <c r="H20" s="69"/>
       <c r="I20" s="19"/>
-      <c r="J20" s="488" t="s">
+      <c r="J20" s="375" t="s">
         <v>166</v>
       </c>
-      <c r="K20" s="489"/>
-      <c r="L20" s="489"/>
-      <c r="M20" s="490"/>
+      <c r="K20" s="376"/>
+      <c r="L20" s="376"/>
+      <c r="M20" s="377"/>
       <c r="N20" s="150">
         <v>35441</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
-      <c r="B21" s="574"/>
-      <c r="C21" s="485" t="s">
+      <c r="B21" s="344"/>
+      <c r="C21" s="345" t="s">
         <v>122</v>
       </c>
-      <c r="D21" s="486"/>
-      <c r="E21" s="487"/>
+      <c r="D21" s="346"/>
+      <c r="E21" s="371"/>
       <c r="F21" s="71" t="s">
         <v>118</v>
       </c>
@@ -5427,21 +5427,21 @@
         <v>0</v>
       </c>
       <c r="I21" s="19"/>
-      <c r="J21" s="488"/>
-      <c r="K21" s="489"/>
-      <c r="L21" s="489"/>
-      <c r="M21" s="490"/>
+      <c r="J21" s="375"/>
+      <c r="K21" s="376"/>
+      <c r="L21" s="376"/>
+      <c r="M21" s="377"/>
       <c r="N21" s="150"/>
       <c r="P21" s="297"/>
     </row>
     <row r="22" spans="1:23" ht="23.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
-      <c r="B22" s="574"/>
-      <c r="C22" s="549" t="s">
+      <c r="B22" s="344"/>
+      <c r="C22" s="378" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="550"/>
-      <c r="E22" s="551"/>
+      <c r="D22" s="379"/>
+      <c r="E22" s="380"/>
       <c r="F22" s="73">
         <f>SUM(F17:F21)</f>
         <v>123969</v>
@@ -5455,12 +5455,12 @@
         <v>159569.27999999997</v>
       </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="566" t="s">
+      <c r="J22" s="381" t="s">
         <v>144</v>
       </c>
-      <c r="K22" s="567"/>
-      <c r="L22" s="567"/>
-      <c r="M22" s="568"/>
+      <c r="K22" s="382"/>
+      <c r="L22" s="382"/>
+      <c r="M22" s="383"/>
       <c r="N22" s="155">
         <f>SUM(N15:N21)</f>
         <v>192557</v>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="23" spans="1:23" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-      <c r="B23" s="574"/>
+      <c r="B23" s="344"/>
       <c r="C23" s="52"/>
       <c r="D23" s="53"/>
       <c r="E23" s="54"/>
@@ -5481,12 +5481,12 @@
     </row>
     <row r="24" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="574"/>
-      <c r="C24" s="476" t="s">
+      <c r="B24" s="344"/>
+      <c r="C24" s="400" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="477"/>
-      <c r="E24" s="478"/>
+      <c r="D24" s="401"/>
+      <c r="E24" s="402"/>
       <c r="F24" s="89" t="s">
         <v>1</v>
       </c>
@@ -5497,17 +5497,17 @@
         <v>3</v>
       </c>
       <c r="I24" s="7"/>
-      <c r="J24" s="571" t="s">
+      <c r="J24" s="391" t="s">
         <v>146</v>
       </c>
-      <c r="K24" s="572"/>
-      <c r="L24" s="572"/>
-      <c r="M24" s="573"/>
+      <c r="K24" s="392"/>
+      <c r="L24" s="392"/>
+      <c r="M24" s="393"/>
       <c r="N24" s="147" t="s">
         <v>96</v>
       </c>
-      <c r="O24" s="569"/>
-      <c r="P24" s="570"/>
+      <c r="O24" s="384"/>
+      <c r="P24" s="385"/>
       <c r="Q24" s="58"/>
       <c r="R24" s="66"/>
       <c r="S24" s="66"/>
@@ -5515,11 +5515,11 @@
     <row r="25" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="20"/>
-      <c r="C25" s="485" t="s">
+      <c r="C25" s="345" t="s">
         <v>130</v>
       </c>
-      <c r="D25" s="486"/>
-      <c r="E25" s="487"/>
+      <c r="D25" s="346"/>
+      <c r="E25" s="371"/>
       <c r="F25" s="71">
         <f>F13-F26-F28</f>
         <v>28139</v>
@@ -5529,12 +5529,12 @@
         <v>3002</v>
       </c>
       <c r="I25" s="7"/>
-      <c r="J25" s="479" t="s">
+      <c r="J25" s="386" t="s">
         <v>2</v>
       </c>
-      <c r="K25" s="480"/>
-      <c r="L25" s="480"/>
-      <c r="M25" s="481"/>
+      <c r="K25" s="387"/>
+      <c r="L25" s="387"/>
+      <c r="M25" s="339"/>
       <c r="N25" s="145"/>
       <c r="O25" s="58"/>
       <c r="P25" s="58"/>
@@ -5545,11 +5545,11 @@
     <row r="26" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="20"/>
-      <c r="C26" s="485" t="s">
+      <c r="C26" s="345" t="s">
         <v>126</v>
       </c>
-      <c r="D26" s="486"/>
-      <c r="E26" s="487"/>
+      <c r="D26" s="346"/>
+      <c r="E26" s="371"/>
       <c r="F26" s="71">
         <v>8526</v>
       </c>
@@ -5559,15 +5559,14 @@
         <v>6902</v>
       </c>
       <c r="I26" s="7"/>
-      <c r="J26" s="540" t="s">
+      <c r="J26" s="356" t="s">
         <v>140</v>
       </c>
-      <c r="K26" s="541"/>
-      <c r="L26" s="541"/>
-      <c r="M26" s="542"/>
+      <c r="K26" s="357"/>
+      <c r="L26" s="357"/>
+      <c r="M26" s="358"/>
       <c r="N26" s="150">
-        <f>7254+26132+15200+16350-16000</f>
-        <v>48936</v>
+        <v>49630</v>
       </c>
       <c r="P26" s="58"/>
       <c r="Q26" s="58"/>
@@ -5584,15 +5583,14 @@
       <c r="G27" s="181"/>
       <c r="H27" s="121"/>
       <c r="I27" s="7"/>
-      <c r="J27" s="540" t="s">
+      <c r="J27" s="356" t="s">
         <v>139</v>
       </c>
-      <c r="K27" s="541"/>
-      <c r="L27" s="541"/>
-      <c r="M27" s="542"/>
+      <c r="K27" s="357"/>
+      <c r="L27" s="357"/>
+      <c r="M27" s="358"/>
       <c r="N27" s="150">
-        <f>81255-8000-8000</f>
-        <v>65255</v>
+        <v>61446</v>
       </c>
       <c r="P27" s="180"/>
       <c r="Q27" s="180"/>
@@ -5602,11 +5600,11 @@
     <row r="28" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="20"/>
-      <c r="C28" s="485" t="s">
+      <c r="C28" s="345" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="486"/>
-      <c r="E28" s="487"/>
+      <c r="D28" s="346"/>
+      <c r="E28" s="371"/>
       <c r="F28" s="71">
         <v>455</v>
       </c>
@@ -5616,12 +5614,12 @@
         <v>8041</v>
       </c>
       <c r="I28" s="7"/>
-      <c r="J28" s="540" t="s">
+      <c r="J28" s="356" t="s">
         <v>161</v>
       </c>
-      <c r="K28" s="541"/>
-      <c r="L28" s="541"/>
-      <c r="M28" s="542"/>
+      <c r="K28" s="357"/>
+      <c r="L28" s="357"/>
+      <c r="M28" s="358"/>
       <c r="N28" s="150">
         <v>2652</v>
       </c>
@@ -5633,11 +5631,11 @@
     <row r="29" spans="1:23" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="20"/>
-      <c r="C29" s="485" t="s">
+      <c r="C29" s="345" t="s">
         <v>128</v>
       </c>
-      <c r="D29" s="486"/>
-      <c r="E29" s="487"/>
+      <c r="D29" s="346"/>
+      <c r="E29" s="371"/>
       <c r="F29" s="71">
         <v>3350</v>
       </c>
@@ -5646,10 +5644,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="7"/>
-      <c r="J29" s="540"/>
-      <c r="K29" s="541"/>
-      <c r="L29" s="541"/>
-      <c r="M29" s="542"/>
+      <c r="J29" s="356"/>
+      <c r="K29" s="357"/>
+      <c r="L29" s="357"/>
+      <c r="M29" s="358"/>
       <c r="N29" s="150"/>
       <c r="P29" s="58"/>
       <c r="Q29" s="58"/>
@@ -5659,23 +5657,23 @@
     <row r="30" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="20"/>
-      <c r="C30" s="485" t="s">
+      <c r="C30" s="345" t="s">
         <v>129</v>
       </c>
-      <c r="D30" s="486"/>
-      <c r="E30" s="487"/>
+      <c r="D30" s="346"/>
+      <c r="E30" s="371"/>
       <c r="F30" s="71"/>
       <c r="G30" s="102"/>
       <c r="H30" s="123">
         <v>0</v>
       </c>
       <c r="I30" s="7"/>
-      <c r="J30" s="495" t="s">
+      <c r="J30" s="397" t="s">
         <v>94</v>
       </c>
-      <c r="K30" s="496"/>
-      <c r="L30" s="496"/>
-      <c r="M30" s="497"/>
+      <c r="K30" s="398"/>
+      <c r="L30" s="398"/>
+      <c r="M30" s="399"/>
       <c r="N30" s="151"/>
       <c r="P30" s="58"/>
       <c r="Q30" s="58"/>
@@ -5685,23 +5683,23 @@
     <row r="31" spans="1:23" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="20"/>
-      <c r="C31" s="485" t="s">
+      <c r="C31" s="345" t="s">
         <v>131</v>
       </c>
-      <c r="D31" s="486"/>
-      <c r="E31" s="487"/>
+      <c r="D31" s="346"/>
+      <c r="E31" s="371"/>
       <c r="F31" s="71"/>
       <c r="G31" s="99"/>
       <c r="H31" s="121">
         <v>0</v>
       </c>
       <c r="I31" s="7"/>
-      <c r="J31" s="552" t="s">
+      <c r="J31" s="388" t="s">
         <v>98</v>
       </c>
-      <c r="K31" s="553"/>
-      <c r="L31" s="553"/>
-      <c r="M31" s="554"/>
+      <c r="K31" s="389"/>
+      <c r="L31" s="389"/>
+      <c r="M31" s="390"/>
       <c r="N31" s="150">
         <v>11830</v>
       </c>
@@ -5713,11 +5711,11 @@
     <row r="32" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="20"/>
-      <c r="C32" s="549" t="s">
+      <c r="C32" s="378" t="s">
         <v>132</v>
       </c>
-      <c r="D32" s="550"/>
-      <c r="E32" s="551"/>
+      <c r="D32" s="379"/>
+      <c r="E32" s="380"/>
       <c r="F32" s="71">
         <f>SUM(F25:F31)</f>
         <v>40470</v>
@@ -5731,12 +5729,12 @@
         <v>17945</v>
       </c>
       <c r="I32" s="7"/>
-      <c r="J32" s="552" t="s">
+      <c r="J32" s="388" t="s">
         <v>167</v>
       </c>
-      <c r="K32" s="553"/>
-      <c r="L32" s="553"/>
-      <c r="M32" s="554"/>
+      <c r="K32" s="389"/>
+      <c r="L32" s="389"/>
+      <c r="M32" s="390"/>
       <c r="N32" s="150">
         <f>25777</f>
         <v>25777</v>
@@ -5750,10 +5748,10 @@
       <c r="A33" s="3"/>
       <c r="B33" s="20"/>
       <c r="I33" s="7"/>
-      <c r="J33" s="552"/>
-      <c r="K33" s="553"/>
-      <c r="L33" s="553"/>
-      <c r="M33" s="554"/>
+      <c r="J33" s="388"/>
+      <c r="K33" s="389"/>
+      <c r="L33" s="389"/>
+      <c r="M33" s="390"/>
       <c r="N33" s="152"/>
       <c r="O33" s="61"/>
       <c r="P33" s="61"/>
@@ -5764,11 +5762,11 @@
     <row r="34" spans="1:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="20"/>
-      <c r="C34" s="546" t="s">
+      <c r="C34" s="403" t="s">
         <v>104</v>
       </c>
-      <c r="D34" s="547"/>
-      <c r="E34" s="548"/>
+      <c r="D34" s="404"/>
+      <c r="E34" s="405"/>
       <c r="F34" s="77" t="str">
         <f>K1</f>
         <v>14.09.2026</v>
@@ -5780,15 +5778,15 @@
         <v>233</v>
       </c>
       <c r="I34" s="7"/>
-      <c r="J34" s="555" t="s">
+      <c r="J34" s="406" t="s">
         <v>143</v>
       </c>
-      <c r="K34" s="556"/>
-      <c r="L34" s="556"/>
-      <c r="M34" s="557"/>
+      <c r="K34" s="407"/>
+      <c r="L34" s="407"/>
+      <c r="M34" s="408"/>
       <c r="N34" s="163">
         <f>SUM(N26:N33)</f>
-        <v>154450</v>
+        <v>151335</v>
       </c>
       <c r="O34" s="63"/>
       <c r="R34" s="61"/>
@@ -5844,11 +5842,11 @@
         <v>0</v>
       </c>
       <c r="I36" s="7"/>
-      <c r="J36" s="577" t="s">
+      <c r="J36" s="349" t="s">
         <v>159</v>
       </c>
-      <c r="K36" s="578"/>
-      <c r="L36" s="579"/>
+      <c r="K36" s="350"/>
+      <c r="L36" s="351"/>
       <c r="M36" s="112" t="s">
         <v>116</v>
       </c>
@@ -5861,10 +5859,10 @@
       <c r="P36" s="165" t="s">
         <v>141</v>
       </c>
-      <c r="Q36" s="457" t="s">
+      <c r="Q36" s="458" t="s">
         <v>152</v>
       </c>
-      <c r="R36" s="458"/>
+      <c r="R36" s="459"/>
       <c r="S36" s="61"/>
     </row>
     <row r="37" spans="1:19" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5883,11 +5881,11 @@
       <c r="G37" s="134"/>
       <c r="H37" s="134"/>
       <c r="I37" s="7"/>
-      <c r="J37" s="473" t="s">
+      <c r="J37" s="352" t="s">
         <v>197</v>
       </c>
-      <c r="K37" s="474"/>
-      <c r="L37" s="475"/>
+      <c r="K37" s="353"/>
+      <c r="L37" s="354"/>
       <c r="M37" s="149">
         <v>59104</v>
       </c>
@@ -5900,10 +5898,10 @@
       <c r="P37" s="256" t="s">
         <v>236</v>
       </c>
-      <c r="Q37" s="461" t="s">
+      <c r="Q37" s="462" t="s">
         <v>217</v>
       </c>
-      <c r="R37" s="462"/>
+      <c r="R37" s="463"/>
       <c r="S37" s="61"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5925,11 +5923,11 @@
       </c>
       <c r="H38" s="134"/>
       <c r="I38" s="7"/>
-      <c r="J38" s="473" t="s">
+      <c r="J38" s="352" t="s">
         <v>214</v>
       </c>
-      <c r="K38" s="474"/>
-      <c r="L38" s="475"/>
+      <c r="K38" s="353"/>
+      <c r="L38" s="354"/>
       <c r="M38" s="149">
         <v>61650</v>
       </c>
@@ -5942,10 +5940,10 @@
       <c r="P38" s="256" t="s">
         <v>226</v>
       </c>
-      <c r="Q38" s="461" t="s">
+      <c r="Q38" s="462" t="s">
         <v>223</v>
       </c>
-      <c r="R38" s="462"/>
+      <c r="R38" s="463"/>
       <c r="S38" s="61"/>
     </row>
     <row r="39" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5967,11 +5965,11 @@
       </c>
       <c r="H39" s="134"/>
       <c r="I39" s="7"/>
-      <c r="J39" s="473" t="s">
+      <c r="J39" s="352" t="s">
         <v>204</v>
       </c>
-      <c r="K39" s="474"/>
-      <c r="L39" s="475"/>
+      <c r="K39" s="353"/>
+      <c r="L39" s="354"/>
       <c r="M39" s="149">
         <v>75204</v>
       </c>
@@ -5984,10 +5982,10 @@
       <c r="P39" s="256" t="s">
         <v>208</v>
       </c>
-      <c r="Q39" s="466" t="s">
+      <c r="Q39" s="467" t="s">
         <v>225</v>
       </c>
-      <c r="R39" s="466"/>
+      <c r="R39" s="467"/>
       <c r="S39" s="61"/>
     </row>
     <row r="40" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6000,15 +5998,15 @@
       <c r="G40" s="134"/>
       <c r="H40" s="134"/>
       <c r="I40" s="7"/>
-      <c r="J40" s="473"/>
-      <c r="K40" s="474"/>
-      <c r="L40" s="475"/>
+      <c r="J40" s="352"/>
+      <c r="K40" s="353"/>
+      <c r="L40" s="354"/>
       <c r="M40" s="149"/>
       <c r="N40" s="149"/>
       <c r="O40" s="265"/>
       <c r="P40" s="256"/>
-      <c r="Q40" s="461"/>
-      <c r="R40" s="462"/>
+      <c r="Q40" s="462"/>
+      <c r="R40" s="463"/>
       <c r="S40" s="61"/>
     </row>
     <row r="41" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6021,11 +6019,11 @@
       <c r="G41" s="134"/>
       <c r="H41" s="134"/>
       <c r="I41" s="7"/>
-      <c r="J41" s="465" t="s">
+      <c r="J41" s="466" t="s">
         <v>243</v>
       </c>
-      <c r="K41" s="465"/>
-      <c r="L41" s="465"/>
+      <c r="K41" s="466"/>
+      <c r="L41" s="466"/>
       <c r="M41" s="149">
         <v>60000</v>
       </c>
@@ -6034,10 +6032,10 @@
         <v>244</v>
       </c>
       <c r="P41" s="256"/>
-      <c r="Q41" s="466" t="s">
+      <c r="Q41" s="467" t="s">
         <v>225</v>
       </c>
-      <c r="R41" s="466"/>
+      <c r="R41" s="467"/>
       <c r="S41" s="61"/>
     </row>
     <row r="42" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6050,15 +6048,15 @@
       <c r="G42" s="134"/>
       <c r="H42" s="134"/>
       <c r="I42" s="7"/>
-      <c r="J42" s="465"/>
-      <c r="K42" s="465"/>
-      <c r="L42" s="465"/>
+      <c r="J42" s="466"/>
+      <c r="K42" s="466"/>
+      <c r="L42" s="466"/>
       <c r="M42" s="149"/>
       <c r="N42" s="149"/>
       <c r="O42" s="265"/>
       <c r="P42" s="256"/>
-      <c r="Q42" s="466"/>
-      <c r="R42" s="466"/>
+      <c r="Q42" s="467"/>
+      <c r="R42" s="467"/>
       <c r="S42" s="61"/>
     </row>
     <row r="43" spans="1:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6082,20 +6080,20 @@
         <v>0</v>
       </c>
       <c r="I43" s="7"/>
-      <c r="J43" s="469" t="s">
+      <c r="J43" s="468" t="s">
         <v>99</v>
       </c>
-      <c r="K43" s="470"/>
-      <c r="L43" s="470"/>
-      <c r="M43" s="470"/>
+      <c r="K43" s="469"/>
+      <c r="L43" s="469"/>
+      <c r="M43" s="469"/>
       <c r="N43" s="166"/>
       <c r="O43" s="167">
         <f>SUM(N37:N40)</f>
         <v>120504</v>
       </c>
       <c r="P43" s="254"/>
-      <c r="Q43" s="459"/>
-      <c r="R43" s="459"/>
+      <c r="Q43" s="460"/>
+      <c r="R43" s="460"/>
       <c r="S43" s="61"/>
     </row>
     <row r="44" spans="1:19" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6114,20 +6112,20 @@
       </c>
       <c r="H44" s="136"/>
       <c r="I44" s="7"/>
-      <c r="J44" s="543" t="s">
+      <c r="J44" s="394" t="s">
         <v>100</v>
       </c>
-      <c r="K44" s="544"/>
-      <c r="L44" s="544"/>
-      <c r="M44" s="544"/>
-      <c r="N44" s="545"/>
+      <c r="K44" s="395"/>
+      <c r="L44" s="395"/>
+      <c r="M44" s="395"/>
+      <c r="N44" s="396"/>
       <c r="O44" s="148">
         <f>N22+N34+O43</f>
-        <v>467511</v>
+        <v>464396</v>
       </c>
       <c r="P44" s="255"/>
-      <c r="Q44" s="460"/>
-      <c r="R44" s="460"/>
+      <c r="Q44" s="461"/>
+      <c r="R44" s="461"/>
       <c r="S44" s="61"/>
     </row>
     <row r="45" spans="1:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6177,10 +6175,10 @@
       <c r="H46" s="134">
         <v>6</v>
       </c>
-      <c r="J46" s="471" t="s">
+      <c r="J46" s="470" t="s">
         <v>103</v>
       </c>
-      <c r="K46" s="472"/>
+      <c r="K46" s="471"/>
       <c r="L46" s="116" t="s">
         <v>1</v>
       </c>
@@ -6218,10 +6216,10 @@
       <c r="H47" s="134">
         <v>0</v>
       </c>
-      <c r="J47" s="467" t="s">
+      <c r="J47" s="366" t="s">
         <v>15</v>
       </c>
-      <c r="K47" s="468"/>
+      <c r="K47" s="367"/>
       <c r="L47" s="156">
         <v>48.31</v>
       </c>
@@ -6240,11 +6238,11 @@
         <v>2.0579999999999998</v>
       </c>
       <c r="Q47" s="156">
-        <v>6.3550000000000004</v>
+        <v>6.4169999999999998</v>
       </c>
       <c r="R47" s="157">
         <f>O47+P47+Q47</f>
-        <v>117.6178</v>
+        <v>117.6798</v>
       </c>
       <c r="S47" s="115"/>
     </row>
@@ -6273,10 +6271,10 @@
         <f>SUM(H36:H47)</f>
         <v>6</v>
       </c>
-      <c r="J48" s="467" t="s">
+      <c r="J48" s="366" t="s">
         <v>16</v>
       </c>
-      <c r="K48" s="468"/>
+      <c r="K48" s="367"/>
       <c r="L48" s="156">
         <v>44.578000000000003</v>
       </c>
@@ -6294,11 +6292,11 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="Q48" s="156">
-        <v>6.3369999999999997</v>
+        <v>6.3789999999999996</v>
       </c>
       <c r="R48" s="157">
         <f>O48+P48+Q48</f>
-        <v>109.16200000000001</v>
+        <v>109.20400000000001</v>
       </c>
       <c r="S48" s="115"/>
     </row>
@@ -6312,10 +6310,10 @@
       <c r="F49" s="80"/>
       <c r="G49" s="84"/>
       <c r="H49" s="85"/>
-      <c r="J49" s="467" t="s">
+      <c r="J49" s="366" t="s">
         <v>17</v>
       </c>
-      <c r="K49" s="468"/>
+      <c r="K49" s="367"/>
       <c r="L49" s="156">
         <f>(L47-L48)/L47*100</f>
         <v>7.7251086731525547</v>
@@ -6362,10 +6360,10 @@
         <v>3</v>
       </c>
       <c r="I50" s="64"/>
-      <c r="J50" s="560" t="s">
+      <c r="J50" s="409" t="s">
         <v>18</v>
       </c>
-      <c r="K50" s="561"/>
+      <c r="K50" s="410"/>
       <c r="L50" s="156">
         <f>F13/L47/1000</f>
         <v>0.76837093769405918</v>
@@ -6413,17 +6411,17 @@
       </c>
       <c r="J51" s="140"/>
       <c r="K51" s="141"/>
-      <c r="L51" s="467" t="s">
+      <c r="L51" s="366" t="s">
         <v>148</v>
       </c>
-      <c r="M51" s="468"/>
-      <c r="N51" s="585"/>
+      <c r="M51" s="367"/>
+      <c r="N51" s="368"/>
       <c r="O51" s="158">
         <v>260.209</v>
       </c>
       <c r="P51" s="142"/>
-      <c r="Q51" s="463"/>
-      <c r="R51" s="464"/>
+      <c r="Q51" s="464"/>
+      <c r="R51" s="465"/>
       <c r="S51" s="109"/>
     </row>
     <row r="52" spans="1:19" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6443,24 +6441,24 @@
     </row>
     <row r="53" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
-      <c r="B53" s="563" t="s">
+      <c r="B53" s="363" t="s">
         <v>135</v>
       </c>
-      <c r="C53" s="564"/>
-      <c r="D53" s="564"/>
-      <c r="E53" s="564"/>
-      <c r="F53" s="564"/>
-      <c r="G53" s="565"/>
+      <c r="C53" s="364"/>
+      <c r="D53" s="364"/>
+      <c r="E53" s="364"/>
+      <c r="F53" s="364"/>
+      <c r="G53" s="365"/>
       <c r="H53" s="68"/>
-      <c r="J53" s="563" t="s">
+      <c r="J53" s="363" t="s">
         <v>136</v>
       </c>
-      <c r="K53" s="564"/>
-      <c r="L53" s="564"/>
-      <c r="M53" s="564"/>
-      <c r="N53" s="564"/>
-      <c r="O53" s="564"/>
-      <c r="P53" s="565"/>
+      <c r="K53" s="364"/>
+      <c r="L53" s="364"/>
+      <c r="M53" s="364"/>
+      <c r="N53" s="364"/>
+      <c r="O53" s="364"/>
+      <c r="P53" s="365"/>
       <c r="Q53" s="60"/>
       <c r="R53" s="60"/>
       <c r="S53" s="60"/>
@@ -6470,33 +6468,33 @@
       <c r="B54" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="C54" s="581" t="s">
+      <c r="C54" s="359" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="582"/>
+      <c r="D54" s="360"/>
       <c r="E54" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F54" s="558" t="s">
+      <c r="F54" s="338" t="s">
         <v>22</v>
       </c>
-      <c r="G54" s="559"/>
+      <c r="G54" s="340"/>
       <c r="H54" s="60"/>
       <c r="J54" s="160" t="s">
         <v>23</v>
       </c>
-      <c r="K54" s="562" t="s">
+      <c r="K54" s="411" t="s">
         <v>21</v>
       </c>
-      <c r="L54" s="562"/>
-      <c r="M54" s="562"/>
+      <c r="L54" s="411"/>
+      <c r="M54" s="411"/>
       <c r="N54" s="159" t="s">
         <v>145</v>
       </c>
-      <c r="O54" s="583" t="s">
+      <c r="O54" s="361" t="s">
         <v>22</v>
       </c>
-      <c r="P54" s="584"/>
+      <c r="P54" s="362"/>
       <c r="Q54" s="60"/>
       <c r="R54" s="60"/>
       <c r="S54" s="60"/>
@@ -6506,33 +6504,33 @@
       <c r="B55" s="182">
         <v>1</v>
       </c>
-      <c r="C55" s="558" t="s">
+      <c r="C55" s="338" t="s">
         <v>228</v>
       </c>
-      <c r="D55" s="481"/>
+      <c r="D55" s="339"/>
       <c r="E55" s="169" t="s">
         <v>242</v>
       </c>
-      <c r="F55" s="558" t="s">
+      <c r="F55" s="338" t="s">
         <v>282</v>
       </c>
-      <c r="G55" s="559"/>
+      <c r="G55" s="340"/>
       <c r="H55" s="44"/>
       <c r="J55" s="257">
         <v>1</v>
       </c>
-      <c r="K55" s="539" t="s">
+      <c r="K55" s="341" t="s">
         <v>238</v>
       </c>
-      <c r="L55" s="539"/>
-      <c r="M55" s="539"/>
+      <c r="L55" s="341"/>
+      <c r="M55" s="341"/>
       <c r="N55" s="258" t="s">
         <v>240</v>
       </c>
-      <c r="O55" s="539" t="s">
+      <c r="O55" s="341" t="s">
         <v>281</v>
       </c>
-      <c r="P55" s="539"/>
+      <c r="P55" s="341"/>
       <c r="Q55" s="60"/>
       <c r="R55" s="60"/>
       <c r="S55" s="60"/>
@@ -6542,33 +6540,33 @@
       <c r="B56" s="328">
         <v>2</v>
       </c>
-      <c r="C56" s="558" t="s">
+      <c r="C56" s="338" t="s">
         <v>241</v>
       </c>
-      <c r="D56" s="481"/>
+      <c r="D56" s="339"/>
       <c r="E56" s="169" t="s">
         <v>229</v>
       </c>
-      <c r="F56" s="558" t="s">
+      <c r="F56" s="338" t="s">
         <v>221</v>
       </c>
-      <c r="G56" s="559"/>
+      <c r="G56" s="340"/>
       <c r="H56" s="44"/>
       <c r="J56" s="329">
         <v>2</v>
       </c>
-      <c r="K56" s="539" t="s">
+      <c r="K56" s="341" t="s">
         <v>238</v>
       </c>
-      <c r="L56" s="539"/>
-      <c r="M56" s="539"/>
+      <c r="L56" s="341"/>
+      <c r="M56" s="341"/>
       <c r="N56" s="258" t="s">
         <v>239</v>
       </c>
-      <c r="O56" s="539" t="s">
+      <c r="O56" s="341" t="s">
         <v>221</v>
       </c>
-      <c r="P56" s="539"/>
+      <c r="P56" s="341"/>
       <c r="Q56" s="60"/>
       <c r="R56" s="60"/>
       <c r="S56" s="60"/>
@@ -6576,27 +6574,27 @@
     <row r="57" spans="1:19" ht="21" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="328"/>
-      <c r="C57" s="558"/>
-      <c r="D57" s="481"/>
+      <c r="C57" s="338"/>
+      <c r="D57" s="339"/>
       <c r="E57" s="169"/>
-      <c r="F57" s="558"/>
-      <c r="G57" s="559"/>
+      <c r="F57" s="338"/>
+      <c r="G57" s="340"/>
       <c r="H57" s="44"/>
       <c r="J57" s="331">
         <v>3</v>
       </c>
-      <c r="K57" s="539" t="s">
+      <c r="K57" s="341" t="s">
         <v>206</v>
       </c>
-      <c r="L57" s="539"/>
-      <c r="M57" s="539"/>
+      <c r="L57" s="341"/>
+      <c r="M57" s="341"/>
       <c r="N57" s="258" t="s">
         <v>237</v>
       </c>
-      <c r="O57" s="539" t="s">
+      <c r="O57" s="341" t="s">
         <v>221</v>
       </c>
-      <c r="P57" s="539"/>
+      <c r="P57" s="341"/>
       <c r="Q57" s="60"/>
       <c r="R57" s="60"/>
       <c r="S57" s="60"/>
@@ -6623,23 +6621,23 @@
     </row>
     <row r="59" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
-      <c r="B59" s="580" t="s">
+      <c r="B59" s="355" t="s">
         <v>234</v>
       </c>
-      <c r="C59" s="580"/>
-      <c r="D59" s="580"/>
-      <c r="E59" s="580"/>
-      <c r="F59" s="580"/>
-      <c r="G59" s="580"/>
-      <c r="H59" s="580"/>
-      <c r="I59" s="580"/>
-      <c r="J59" s="580"/>
-      <c r="K59" s="580"/>
-      <c r="L59" s="580"/>
-      <c r="M59" s="580"/>
-      <c r="N59" s="580"/>
-      <c r="O59" s="580"/>
-      <c r="P59" s="580"/>
+      <c r="C59" s="355"/>
+      <c r="D59" s="355"/>
+      <c r="E59" s="355"/>
+      <c r="F59" s="355"/>
+      <c r="G59" s="355"/>
+      <c r="H59" s="355"/>
+      <c r="I59" s="355"/>
+      <c r="J59" s="355"/>
+      <c r="K59" s="355"/>
+      <c r="L59" s="355"/>
+      <c r="M59" s="355"/>
+      <c r="N59" s="355"/>
+      <c r="O59" s="355"/>
+      <c r="P59" s="355"/>
     </row>
     <row r="60" spans="1:19" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3"/>
@@ -6661,46 +6659,46 @@
     </row>
     <row r="61" spans="1:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B61" s="3"/>
-      <c r="C61" s="593" t="s">
+      <c r="C61" s="337" t="s">
         <v>94</v>
       </c>
-      <c r="D61" s="593"/>
-      <c r="E61" s="593"/>
-      <c r="F61" s="593"/>
+      <c r="D61" s="337"/>
+      <c r="E61" s="337"/>
+      <c r="F61" s="337"/>
       <c r="G61" s="40"/>
       <c r="H61" s="40"/>
       <c r="I61" s="3"/>
-      <c r="J61" s="593" t="s">
+      <c r="J61" s="337" t="s">
         <v>89</v>
       </c>
-      <c r="K61" s="593"/>
-      <c r="L61" s="593"/>
-      <c r="M61" s="593"/>
-      <c r="N61" s="593"/>
+      <c r="K61" s="337"/>
+      <c r="L61" s="337"/>
+      <c r="M61" s="337"/>
+      <c r="N61" s="337"/>
       <c r="O61" s="42"/>
     </row>
     <row r="62" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B62" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="C62" s="576" t="s">
+      <c r="C62" s="348" t="s">
         <v>78</v>
       </c>
-      <c r="D62" s="576"/>
-      <c r="E62" s="576"/>
-      <c r="F62" s="576"/>
+      <c r="D62" s="348"/>
+      <c r="E62" s="348"/>
+      <c r="F62" s="348"/>
       <c r="G62" s="40"/>
       <c r="H62" s="40"/>
       <c r="I62" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="J62" s="576" t="s">
+      <c r="J62" s="348" t="s">
         <v>78</v>
       </c>
-      <c r="K62" s="576"/>
-      <c r="L62" s="576"/>
-      <c r="M62" s="576"/>
-      <c r="N62" s="576"/>
+      <c r="K62" s="348"/>
+      <c r="L62" s="348"/>
+      <c r="M62" s="348"/>
+      <c r="N62" s="348"/>
       <c r="O62" s="42"/>
     </row>
     <row r="63" spans="1:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
@@ -7124,11 +7122,11 @@
       <c r="G81" s="299"/>
       <c r="H81" s="282"/>
       <c r="I81" s="271"/>
-      <c r="J81" s="592"/>
-      <c r="K81" s="592"/>
-      <c r="L81" s="592"/>
-      <c r="M81" s="592"/>
-      <c r="N81" s="592"/>
+      <c r="J81" s="336"/>
+      <c r="K81" s="336"/>
+      <c r="L81" s="336"/>
+      <c r="M81" s="336"/>
+      <c r="N81" s="336"/>
       <c r="O81" s="284"/>
     </row>
     <row r="82" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
@@ -7144,11 +7142,11 @@
       <c r="G82" s="299"/>
       <c r="H82" s="282"/>
       <c r="I82" s="271"/>
-      <c r="J82" s="592"/>
-      <c r="K82" s="592"/>
-      <c r="L82" s="592"/>
-      <c r="M82" s="592"/>
-      <c r="N82" s="592"/>
+      <c r="J82" s="336"/>
+      <c r="K82" s="336"/>
+      <c r="L82" s="336"/>
+      <c r="M82" s="336"/>
+      <c r="N82" s="336"/>
       <c r="O82" s="296"/>
     </row>
     <row r="83" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
@@ -7208,13 +7206,13 @@
       <c r="I85" s="271">
         <v>1</v>
       </c>
-      <c r="J85" s="591" t="s">
+      <c r="J85" s="335" t="s">
         <v>274</v>
       </c>
-      <c r="K85" s="591"/>
-      <c r="L85" s="591"/>
-      <c r="M85" s="591"/>
-      <c r="N85" s="591"/>
+      <c r="K85" s="335"/>
+      <c r="L85" s="335"/>
+      <c r="M85" s="335"/>
+      <c r="N85" s="335"/>
       <c r="O85" s="307"/>
     </row>
     <row r="86" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
@@ -7232,13 +7230,13 @@
       <c r="I86" s="271">
         <v>2</v>
       </c>
-      <c r="J86" s="591" t="s">
+      <c r="J86" s="335" t="s">
         <v>275</v>
       </c>
-      <c r="K86" s="591"/>
-      <c r="L86" s="591"/>
-      <c r="M86" s="591"/>
-      <c r="N86" s="591"/>
+      <c r="K86" s="335"/>
+      <c r="L86" s="335"/>
+      <c r="M86" s="335"/>
+      <c r="N86" s="335"/>
       <c r="O86" s="308"/>
     </row>
     <row r="87" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
@@ -7256,13 +7254,13 @@
       <c r="I87" s="271">
         <v>3</v>
       </c>
-      <c r="J87" s="591" t="s">
+      <c r="J87" s="335" t="s">
         <v>218</v>
       </c>
-      <c r="K87" s="591"/>
-      <c r="L87" s="591"/>
-      <c r="M87" s="591"/>
-      <c r="N87" s="591"/>
+      <c r="K87" s="335"/>
+      <c r="L87" s="335"/>
+      <c r="M87" s="335"/>
+      <c r="N87" s="335"/>
       <c r="O87" s="308"/>
     </row>
     <row r="88" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -7275,25 +7273,25 @@
       <c r="I88" s="271">
         <v>4</v>
       </c>
-      <c r="J88" s="591" t="s">
+      <c r="J88" s="335" t="s">
         <v>276</v>
       </c>
-      <c r="K88" s="591"/>
-      <c r="L88" s="591"/>
-      <c r="M88" s="591"/>
-      <c r="N88" s="591"/>
-      <c r="O88" s="591"/>
+      <c r="K88" s="335"/>
+      <c r="L88" s="335"/>
+      <c r="M88" s="335"/>
+      <c r="N88" s="335"/>
+      <c r="O88" s="335"/>
     </row>
     <row r="89" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B89" s="111"/>
       <c r="H89" s="282"/>
       <c r="I89" s="271"/>
-      <c r="J89" s="591"/>
-      <c r="K89" s="591"/>
-      <c r="L89" s="591"/>
-      <c r="M89" s="591"/>
-      <c r="N89" s="591"/>
-      <c r="O89" s="591"/>
+      <c r="J89" s="335"/>
+      <c r="K89" s="335"/>
+      <c r="L89" s="335"/>
+      <c r="M89" s="335"/>
+      <c r="N89" s="335"/>
+      <c r="O89" s="335"/>
     </row>
     <row r="90" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B90" s="111"/>
@@ -7304,12 +7302,12 @@
       <c r="G90" s="298"/>
       <c r="H90" s="282"/>
       <c r="I90" s="271"/>
-      <c r="J90" s="591"/>
-      <c r="K90" s="591"/>
-      <c r="L90" s="591"/>
-      <c r="M90" s="591"/>
-      <c r="N90" s="591"/>
-      <c r="O90" s="591"/>
+      <c r="J90" s="335"/>
+      <c r="K90" s="335"/>
+      <c r="L90" s="335"/>
+      <c r="M90" s="335"/>
+      <c r="N90" s="335"/>
+      <c r="O90" s="335"/>
       <c r="P90" s="266"/>
     </row>
     <row r="91" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
@@ -7321,12 +7319,12 @@
       <c r="G91" s="298"/>
       <c r="H91" s="282"/>
       <c r="I91" s="271"/>
-      <c r="J91" s="591"/>
-      <c r="K91" s="591"/>
-      <c r="L91" s="591"/>
-      <c r="M91" s="591"/>
-      <c r="N91" s="591"/>
-      <c r="O91" s="591"/>
+      <c r="J91" s="335"/>
+      <c r="K91" s="335"/>
+      <c r="L91" s="335"/>
+      <c r="M91" s="335"/>
+      <c r="N91" s="335"/>
+      <c r="O91" s="335"/>
     </row>
     <row r="92" spans="2:16" ht="24" x14ac:dyDescent="0.15">
       <c r="B92" s="111"/>
@@ -7337,12 +7335,12 @@
       <c r="G92" s="298"/>
       <c r="H92" s="282"/>
       <c r="I92" s="271"/>
-      <c r="J92" s="591"/>
-      <c r="K92" s="591"/>
-      <c r="L92" s="591"/>
-      <c r="M92" s="591"/>
-      <c r="N92" s="591"/>
-      <c r="O92" s="591"/>
+      <c r="J92" s="335"/>
+      <c r="K92" s="335"/>
+      <c r="L92" s="335"/>
+      <c r="M92" s="335"/>
+      <c r="N92" s="335"/>
+      <c r="O92" s="335"/>
     </row>
     <row r="93" spans="2:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B93" s="111"/>
@@ -7353,12 +7351,12 @@
       <c r="G93" s="299"/>
       <c r="H93" s="282"/>
       <c r="I93" s="271"/>
-      <c r="J93" s="591"/>
-      <c r="K93" s="591"/>
-      <c r="L93" s="591"/>
-      <c r="M93" s="591"/>
-      <c r="N93" s="591"/>
-      <c r="O93" s="591"/>
+      <c r="J93" s="335"/>
+      <c r="K93" s="335"/>
+      <c r="L93" s="335"/>
+      <c r="M93" s="335"/>
+      <c r="N93" s="335"/>
+      <c r="O93" s="335"/>
     </row>
     <row r="94" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B94" s="111"/>
@@ -7369,11 +7367,11 @@
       <c r="G94" s="299"/>
       <c r="H94" s="282"/>
       <c r="I94" s="266"/>
-      <c r="J94" s="590"/>
-      <c r="K94" s="590"/>
-      <c r="L94" s="590"/>
-      <c r="M94" s="590"/>
-      <c r="N94" s="590"/>
+      <c r="J94" s="342"/>
+      <c r="K94" s="342"/>
+      <c r="L94" s="342"/>
+      <c r="M94" s="342"/>
+      <c r="N94" s="342"/>
       <c r="O94" s="39"/>
     </row>
     <row r="95" spans="2:16" ht="24" x14ac:dyDescent="0.2">
@@ -7383,11 +7381,11 @@
       <c r="F95" s="299"/>
       <c r="G95" s="299"/>
       <c r="H95" s="282"/>
-      <c r="J95" s="590"/>
-      <c r="K95" s="590"/>
-      <c r="L95" s="590"/>
-      <c r="M95" s="590"/>
-      <c r="N95" s="590"/>
+      <c r="J95" s="342"/>
+      <c r="K95" s="342"/>
+      <c r="L95" s="342"/>
+      <c r="M95" s="342"/>
+      <c r="N95" s="342"/>
       <c r="O95" s="39"/>
     </row>
     <row r="96" spans="2:16" ht="24" x14ac:dyDescent="0.2">
@@ -7397,11 +7395,11 @@
       <c r="F96" s="282"/>
       <c r="G96" s="282"/>
       <c r="H96" s="282"/>
-      <c r="J96" s="590"/>
-      <c r="K96" s="590"/>
-      <c r="L96" s="590"/>
-      <c r="M96" s="590"/>
-      <c r="N96" s="590"/>
+      <c r="J96" s="342"/>
+      <c r="K96" s="342"/>
+      <c r="L96" s="342"/>
+      <c r="M96" s="342"/>
+      <c r="N96" s="342"/>
       <c r="O96" s="39"/>
     </row>
     <row r="97" spans="2:15" ht="24" x14ac:dyDescent="0.15">
@@ -7412,11 +7410,11 @@
       <c r="F97" s="267"/>
       <c r="G97" s="267"/>
       <c r="H97" s="267"/>
-      <c r="J97" s="590"/>
-      <c r="K97" s="590"/>
-      <c r="L97" s="590"/>
-      <c r="M97" s="590"/>
-      <c r="N97" s="590"/>
+      <c r="J97" s="342"/>
+      <c r="K97" s="342"/>
+      <c r="L97" s="342"/>
+      <c r="M97" s="342"/>
+      <c r="N97" s="342"/>
       <c r="O97" s="39"/>
     </row>
     <row r="98" spans="2:15" ht="22.5" x14ac:dyDescent="0.15">
@@ -7443,11 +7441,11 @@
       <c r="F99" s="251"/>
       <c r="G99" s="251"/>
       <c r="H99" s="251"/>
-      <c r="J99" s="590"/>
-      <c r="K99" s="590"/>
-      <c r="L99" s="590"/>
-      <c r="M99" s="590"/>
-      <c r="N99" s="590"/>
+      <c r="J99" s="342"/>
+      <c r="K99" s="342"/>
+      <c r="L99" s="342"/>
+      <c r="M99" s="342"/>
+      <c r="N99" s="342"/>
       <c r="O99" s="39"/>
     </row>
     <row r="100" spans="2:15" ht="22.5" x14ac:dyDescent="0.15">
@@ -7458,11 +7456,11 @@
       <c r="F100" s="251"/>
       <c r="G100" s="251"/>
       <c r="H100" s="251"/>
-      <c r="J100" s="590"/>
-      <c r="K100" s="590"/>
-      <c r="L100" s="590"/>
-      <c r="M100" s="590"/>
-      <c r="N100" s="590"/>
+      <c r="J100" s="342"/>
+      <c r="K100" s="342"/>
+      <c r="L100" s="342"/>
+      <c r="M100" s="342"/>
+      <c r="N100" s="342"/>
       <c r="O100" s="39"/>
     </row>
     <row r="101" spans="2:15" ht="22.5" x14ac:dyDescent="0.15">
@@ -7473,1289 +7471,1512 @@
       <c r="F101" s="251"/>
       <c r="G101" s="251"/>
       <c r="H101" s="251"/>
-      <c r="J101" s="590"/>
-      <c r="K101" s="590"/>
-      <c r="L101" s="590"/>
-      <c r="M101" s="590"/>
-      <c r="N101" s="590"/>
+      <c r="J101" s="342"/>
+      <c r="K101" s="342"/>
+      <c r="L101" s="342"/>
+      <c r="M101" s="342"/>
+      <c r="N101" s="342"/>
       <c r="O101" s="39"/>
     </row>
     <row r="102" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C102" s="589"/>
-      <c r="D102" s="589"/>
-      <c r="E102" s="589"/>
-      <c r="F102" s="589"/>
-      <c r="G102" s="589"/>
-      <c r="H102" s="589"/>
-      <c r="J102" s="590"/>
-      <c r="K102" s="590"/>
-      <c r="L102" s="590"/>
-      <c r="M102" s="590"/>
-      <c r="N102" s="590"/>
+      <c r="C102" s="343"/>
+      <c r="D102" s="343"/>
+      <c r="E102" s="343"/>
+      <c r="F102" s="343"/>
+      <c r="G102" s="343"/>
+      <c r="H102" s="343"/>
+      <c r="J102" s="342"/>
+      <c r="K102" s="342"/>
+      <c r="L102" s="342"/>
+      <c r="M102" s="342"/>
+      <c r="N102" s="342"/>
       <c r="O102" s="39"/>
     </row>
     <row r="103" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C103" s="589"/>
-      <c r="D103" s="589"/>
-      <c r="E103" s="589"/>
-      <c r="F103" s="589"/>
-      <c r="G103" s="589"/>
-      <c r="H103" s="589"/>
-      <c r="J103" s="590"/>
-      <c r="K103" s="590"/>
-      <c r="L103" s="590"/>
-      <c r="M103" s="590"/>
-      <c r="N103" s="590"/>
+      <c r="C103" s="343"/>
+      <c r="D103" s="343"/>
+      <c r="E103" s="343"/>
+      <c r="F103" s="343"/>
+      <c r="G103" s="343"/>
+      <c r="H103" s="343"/>
+      <c r="J103" s="342"/>
+      <c r="K103" s="342"/>
+      <c r="L103" s="342"/>
+      <c r="M103" s="342"/>
+      <c r="N103" s="342"/>
       <c r="O103" s="39"/>
     </row>
     <row r="104" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C104" s="589"/>
-      <c r="D104" s="589"/>
-      <c r="E104" s="589"/>
-      <c r="F104" s="589"/>
-      <c r="G104" s="589"/>
-      <c r="H104" s="589"/>
-      <c r="J104" s="590"/>
-      <c r="K104" s="590"/>
-      <c r="L104" s="590"/>
-      <c r="M104" s="590"/>
-      <c r="N104" s="590"/>
+      <c r="C104" s="343"/>
+      <c r="D104" s="343"/>
+      <c r="E104" s="343"/>
+      <c r="F104" s="343"/>
+      <c r="G104" s="343"/>
+      <c r="H104" s="343"/>
+      <c r="J104" s="342"/>
+      <c r="K104" s="342"/>
+      <c r="L104" s="342"/>
+      <c r="M104" s="342"/>
+      <c r="N104" s="342"/>
       <c r="O104" s="39"/>
     </row>
     <row r="105" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C105" s="589"/>
-      <c r="D105" s="589"/>
-      <c r="E105" s="589"/>
-      <c r="F105" s="589"/>
-      <c r="G105" s="589"/>
-      <c r="H105" s="589"/>
-      <c r="J105" s="590"/>
-      <c r="K105" s="590"/>
-      <c r="L105" s="590"/>
-      <c r="M105" s="590"/>
-      <c r="N105" s="590"/>
+      <c r="C105" s="343"/>
+      <c r="D105" s="343"/>
+      <c r="E105" s="343"/>
+      <c r="F105" s="343"/>
+      <c r="G105" s="343"/>
+      <c r="H105" s="343"/>
+      <c r="J105" s="342"/>
+      <c r="K105" s="342"/>
+      <c r="L105" s="342"/>
+      <c r="M105" s="342"/>
+      <c r="N105" s="342"/>
       <c r="O105" s="39"/>
     </row>
     <row r="106" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C106" s="589"/>
-      <c r="D106" s="589"/>
-      <c r="E106" s="589"/>
-      <c r="F106" s="589"/>
-      <c r="G106" s="589"/>
-      <c r="H106" s="589"/>
-      <c r="J106" s="590"/>
-      <c r="K106" s="590"/>
-      <c r="L106" s="590"/>
-      <c r="M106" s="590"/>
-      <c r="N106" s="590"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
+      <c r="G106" s="343"/>
+      <c r="H106" s="343"/>
+      <c r="J106" s="342"/>
+      <c r="K106" s="342"/>
+      <c r="L106" s="342"/>
+      <c r="M106" s="342"/>
+      <c r="N106" s="342"/>
       <c r="O106" s="39"/>
     </row>
     <row r="107" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C107" s="589"/>
-      <c r="D107" s="589"/>
-      <c r="E107" s="589"/>
-      <c r="F107" s="589"/>
-      <c r="G107" s="589"/>
-      <c r="H107" s="589"/>
-      <c r="J107" s="590"/>
-      <c r="K107" s="590"/>
-      <c r="L107" s="590"/>
-      <c r="M107" s="590"/>
-      <c r="N107" s="590"/>
+      <c r="C107" s="343"/>
+      <c r="D107" s="343"/>
+      <c r="E107" s="343"/>
+      <c r="F107" s="343"/>
+      <c r="G107" s="343"/>
+      <c r="H107" s="343"/>
+      <c r="J107" s="342"/>
+      <c r="K107" s="342"/>
+      <c r="L107" s="342"/>
+      <c r="M107" s="342"/>
+      <c r="N107" s="342"/>
       <c r="O107" s="39"/>
     </row>
     <row r="108" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C108" s="589"/>
-      <c r="D108" s="589"/>
-      <c r="E108" s="589"/>
-      <c r="F108" s="589"/>
-      <c r="G108" s="589"/>
-      <c r="H108" s="589"/>
-      <c r="J108" s="590"/>
-      <c r="K108" s="590"/>
-      <c r="L108" s="590"/>
-      <c r="M108" s="590"/>
-      <c r="N108" s="590"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
+      <c r="G108" s="343"/>
+      <c r="H108" s="343"/>
+      <c r="J108" s="342"/>
+      <c r="K108" s="342"/>
+      <c r="L108" s="342"/>
+      <c r="M108" s="342"/>
+      <c r="N108" s="342"/>
       <c r="O108" s="39"/>
     </row>
     <row r="109" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C109" s="589"/>
-      <c r="D109" s="589"/>
-      <c r="E109" s="589"/>
-      <c r="F109" s="589"/>
-      <c r="G109" s="589"/>
-      <c r="H109" s="589"/>
-      <c r="J109" s="590"/>
-      <c r="K109" s="590"/>
-      <c r="L109" s="590"/>
-      <c r="M109" s="590"/>
-      <c r="N109" s="590"/>
+      <c r="C109" s="343"/>
+      <c r="D109" s="343"/>
+      <c r="E109" s="343"/>
+      <c r="F109" s="343"/>
+      <c r="G109" s="343"/>
+      <c r="H109" s="343"/>
+      <c r="J109" s="342"/>
+      <c r="K109" s="342"/>
+      <c r="L109" s="342"/>
+      <c r="M109" s="342"/>
+      <c r="N109" s="342"/>
       <c r="O109" s="39"/>
     </row>
     <row r="110" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C110" s="589"/>
-      <c r="D110" s="589"/>
-      <c r="E110" s="589"/>
-      <c r="F110" s="589"/>
-      <c r="G110" s="589"/>
-      <c r="H110" s="589"/>
-      <c r="J110" s="590"/>
-      <c r="K110" s="590"/>
-      <c r="L110" s="590"/>
-      <c r="M110" s="590"/>
-      <c r="N110" s="590"/>
+      <c r="C110" s="343"/>
+      <c r="D110" s="343"/>
+      <c r="E110" s="343"/>
+      <c r="F110" s="343"/>
+      <c r="G110" s="343"/>
+      <c r="H110" s="343"/>
+      <c r="J110" s="342"/>
+      <c r="K110" s="342"/>
+      <c r="L110" s="342"/>
+      <c r="M110" s="342"/>
+      <c r="N110" s="342"/>
       <c r="O110" s="39"/>
     </row>
     <row r="111" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C111" s="589"/>
-      <c r="D111" s="589"/>
-      <c r="E111" s="589"/>
-      <c r="F111" s="589"/>
-      <c r="G111" s="589"/>
-      <c r="H111" s="589"/>
-      <c r="J111" s="590"/>
-      <c r="K111" s="590"/>
-      <c r="L111" s="590"/>
-      <c r="M111" s="590"/>
-      <c r="N111" s="590"/>
+      <c r="C111" s="343"/>
+      <c r="D111" s="343"/>
+      <c r="E111" s="343"/>
+      <c r="F111" s="343"/>
+      <c r="G111" s="343"/>
+      <c r="H111" s="343"/>
+      <c r="J111" s="342"/>
+      <c r="K111" s="342"/>
+      <c r="L111" s="342"/>
+      <c r="M111" s="342"/>
+      <c r="N111" s="342"/>
       <c r="O111" s="39"/>
     </row>
     <row r="112" spans="2:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C112" s="589"/>
-      <c r="D112" s="589"/>
-      <c r="E112" s="589"/>
-      <c r="F112" s="589"/>
-      <c r="G112" s="589"/>
-      <c r="H112" s="589"/>
-      <c r="J112" s="590"/>
-      <c r="K112" s="590"/>
-      <c r="L112" s="590"/>
-      <c r="M112" s="590"/>
-      <c r="N112" s="590"/>
+      <c r="C112" s="343"/>
+      <c r="D112" s="343"/>
+      <c r="E112" s="343"/>
+      <c r="F112" s="343"/>
+      <c r="G112" s="343"/>
+      <c r="H112" s="343"/>
+      <c r="J112" s="342"/>
+      <c r="K112" s="342"/>
+      <c r="L112" s="342"/>
+      <c r="M112" s="342"/>
+      <c r="N112" s="342"/>
       <c r="O112" s="39"/>
     </row>
     <row r="113" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C113" s="589"/>
-      <c r="D113" s="589"/>
-      <c r="E113" s="589"/>
-      <c r="F113" s="589"/>
-      <c r="G113" s="589"/>
-      <c r="H113" s="589"/>
-      <c r="J113" s="590"/>
-      <c r="K113" s="590"/>
-      <c r="L113" s="590"/>
-      <c r="M113" s="590"/>
-      <c r="N113" s="590"/>
+      <c r="C113" s="343"/>
+      <c r="D113" s="343"/>
+      <c r="E113" s="343"/>
+      <c r="F113" s="343"/>
+      <c r="G113" s="343"/>
+      <c r="H113" s="343"/>
+      <c r="J113" s="342"/>
+      <c r="K113" s="342"/>
+      <c r="L113" s="342"/>
+      <c r="M113" s="342"/>
+      <c r="N113" s="342"/>
       <c r="O113" s="39"/>
     </row>
     <row r="114" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C114" s="589"/>
-      <c r="D114" s="589"/>
-      <c r="E114" s="589"/>
-      <c r="F114" s="589"/>
-      <c r="G114" s="589"/>
-      <c r="H114" s="589"/>
-      <c r="J114" s="590"/>
-      <c r="K114" s="590"/>
-      <c r="L114" s="590"/>
-      <c r="M114" s="590"/>
-      <c r="N114" s="590"/>
+      <c r="C114" s="343"/>
+      <c r="D114" s="343"/>
+      <c r="E114" s="343"/>
+      <c r="F114" s="343"/>
+      <c r="G114" s="343"/>
+      <c r="H114" s="343"/>
+      <c r="J114" s="342"/>
+      <c r="K114" s="342"/>
+      <c r="L114" s="342"/>
+      <c r="M114" s="342"/>
+      <c r="N114" s="342"/>
       <c r="O114" s="39"/>
     </row>
     <row r="115" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C115" s="589"/>
-      <c r="D115" s="589"/>
-      <c r="E115" s="589"/>
-      <c r="F115" s="589"/>
-      <c r="G115" s="589"/>
-      <c r="H115" s="589"/>
-      <c r="J115" s="590"/>
-      <c r="K115" s="590"/>
-      <c r="L115" s="590"/>
-      <c r="M115" s="590"/>
-      <c r="N115" s="590"/>
+      <c r="C115" s="343"/>
+      <c r="D115" s="343"/>
+      <c r="E115" s="343"/>
+      <c r="F115" s="343"/>
+      <c r="G115" s="343"/>
+      <c r="H115" s="343"/>
+      <c r="J115" s="342"/>
+      <c r="K115" s="342"/>
+      <c r="L115" s="342"/>
+      <c r="M115" s="342"/>
+      <c r="N115" s="342"/>
       <c r="O115" s="39"/>
     </row>
     <row r="116" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C116" s="589"/>
-      <c r="D116" s="589"/>
-      <c r="E116" s="589"/>
-      <c r="F116" s="589"/>
-      <c r="G116" s="589"/>
-      <c r="H116" s="589"/>
-      <c r="J116" s="590"/>
-      <c r="K116" s="590"/>
-      <c r="L116" s="590"/>
-      <c r="M116" s="590"/>
-      <c r="N116" s="590"/>
+      <c r="C116" s="343"/>
+      <c r="D116" s="343"/>
+      <c r="E116" s="343"/>
+      <c r="F116" s="343"/>
+      <c r="G116" s="343"/>
+      <c r="H116" s="343"/>
+      <c r="J116" s="342"/>
+      <c r="K116" s="342"/>
+      <c r="L116" s="342"/>
+      <c r="M116" s="342"/>
+      <c r="N116" s="342"/>
       <c r="O116" s="39"/>
     </row>
     <row r="117" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C117" s="589"/>
-      <c r="D117" s="589"/>
-      <c r="E117" s="589"/>
-      <c r="F117" s="589"/>
-      <c r="G117" s="589"/>
-      <c r="H117" s="589"/>
-      <c r="J117" s="590"/>
-      <c r="K117" s="590"/>
-      <c r="L117" s="590"/>
-      <c r="M117" s="590"/>
-      <c r="N117" s="590"/>
+      <c r="C117" s="343"/>
+      <c r="D117" s="343"/>
+      <c r="E117" s="343"/>
+      <c r="F117" s="343"/>
+      <c r="G117" s="343"/>
+      <c r="H117" s="343"/>
+      <c r="J117" s="342"/>
+      <c r="K117" s="342"/>
+      <c r="L117" s="342"/>
+      <c r="M117" s="342"/>
+      <c r="N117" s="342"/>
       <c r="O117" s="39"/>
     </row>
     <row r="118" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C118" s="589"/>
-      <c r="D118" s="589"/>
-      <c r="E118" s="589"/>
-      <c r="F118" s="589"/>
-      <c r="G118" s="589"/>
-      <c r="H118" s="589"/>
-      <c r="J118" s="590"/>
-      <c r="K118" s="590"/>
-      <c r="L118" s="590"/>
-      <c r="M118" s="590"/>
-      <c r="N118" s="590"/>
+      <c r="C118" s="343"/>
+      <c r="D118" s="343"/>
+      <c r="E118" s="343"/>
+      <c r="F118" s="343"/>
+      <c r="G118" s="343"/>
+      <c r="H118" s="343"/>
+      <c r="J118" s="342"/>
+      <c r="K118" s="342"/>
+      <c r="L118" s="342"/>
+      <c r="M118" s="342"/>
+      <c r="N118" s="342"/>
       <c r="O118" s="39"/>
     </row>
     <row r="119" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C119" s="589"/>
-      <c r="D119" s="589"/>
-      <c r="E119" s="589"/>
-      <c r="F119" s="589"/>
-      <c r="G119" s="589"/>
-      <c r="H119" s="589"/>
-      <c r="J119" s="590"/>
-      <c r="K119" s="590"/>
-      <c r="L119" s="590"/>
-      <c r="M119" s="590"/>
-      <c r="N119" s="590"/>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
+      <c r="G119" s="343"/>
+      <c r="H119" s="343"/>
+      <c r="J119" s="342"/>
+      <c r="K119" s="342"/>
+      <c r="L119" s="342"/>
+      <c r="M119" s="342"/>
+      <c r="N119" s="342"/>
       <c r="O119" s="39"/>
     </row>
     <row r="120" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C120" s="589"/>
-      <c r="D120" s="589"/>
-      <c r="E120" s="589"/>
-      <c r="F120" s="589"/>
-      <c r="G120" s="589"/>
-      <c r="H120" s="589"/>
-      <c r="J120" s="590"/>
-      <c r="K120" s="590"/>
-      <c r="L120" s="590"/>
-      <c r="M120" s="590"/>
-      <c r="N120" s="590"/>
+      <c r="C120" s="343"/>
+      <c r="D120" s="343"/>
+      <c r="E120" s="343"/>
+      <c r="F120" s="343"/>
+      <c r="G120" s="343"/>
+      <c r="H120" s="343"/>
+      <c r="J120" s="342"/>
+      <c r="K120" s="342"/>
+      <c r="L120" s="342"/>
+      <c r="M120" s="342"/>
+      <c r="N120" s="342"/>
       <c r="O120" s="39"/>
     </row>
     <row r="121" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C121" s="589"/>
-      <c r="D121" s="589"/>
-      <c r="E121" s="589"/>
-      <c r="F121" s="589"/>
-      <c r="G121" s="589"/>
-      <c r="H121" s="589"/>
-      <c r="J121" s="590"/>
-      <c r="K121" s="590"/>
-      <c r="L121" s="590"/>
-      <c r="M121" s="590"/>
-      <c r="N121" s="590"/>
+      <c r="C121" s="343"/>
+      <c r="D121" s="343"/>
+      <c r="E121" s="343"/>
+      <c r="F121" s="343"/>
+      <c r="G121" s="343"/>
+      <c r="H121" s="343"/>
+      <c r="J121" s="342"/>
+      <c r="K121" s="342"/>
+      <c r="L121" s="342"/>
+      <c r="M121" s="342"/>
+      <c r="N121" s="342"/>
       <c r="O121" s="39"/>
     </row>
     <row r="122" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C122" s="589"/>
-      <c r="D122" s="589"/>
-      <c r="E122" s="589"/>
-      <c r="F122" s="589"/>
-      <c r="G122" s="589"/>
-      <c r="H122" s="589"/>
-      <c r="J122" s="590"/>
-      <c r="K122" s="590"/>
-      <c r="L122" s="590"/>
-      <c r="M122" s="590"/>
-      <c r="N122" s="590"/>
+      <c r="C122" s="343"/>
+      <c r="D122" s="343"/>
+      <c r="E122" s="343"/>
+      <c r="F122" s="343"/>
+      <c r="G122" s="343"/>
+      <c r="H122" s="343"/>
+      <c r="J122" s="342"/>
+      <c r="K122" s="342"/>
+      <c r="L122" s="342"/>
+      <c r="M122" s="342"/>
+      <c r="N122" s="342"/>
       <c r="O122" s="39"/>
     </row>
     <row r="123" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C123" s="589"/>
-      <c r="D123" s="589"/>
-      <c r="E123" s="589"/>
-      <c r="F123" s="589"/>
-      <c r="G123" s="589"/>
-      <c r="H123" s="589"/>
-      <c r="J123" s="590"/>
-      <c r="K123" s="590"/>
-      <c r="L123" s="590"/>
-      <c r="M123" s="590"/>
-      <c r="N123" s="590"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
+      <c r="G123" s="343"/>
+      <c r="H123" s="343"/>
+      <c r="J123" s="342"/>
+      <c r="K123" s="342"/>
+      <c r="L123" s="342"/>
+      <c r="M123" s="342"/>
+      <c r="N123" s="342"/>
       <c r="O123" s="39"/>
     </row>
     <row r="124" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C124" s="589"/>
-      <c r="D124" s="589"/>
-      <c r="E124" s="589"/>
-      <c r="F124" s="589"/>
-      <c r="G124" s="589"/>
-      <c r="H124" s="589"/>
-      <c r="J124" s="590"/>
-      <c r="K124" s="590"/>
-      <c r="L124" s="590"/>
-      <c r="M124" s="590"/>
-      <c r="N124" s="590"/>
+      <c r="C124" s="343"/>
+      <c r="D124" s="343"/>
+      <c r="E124" s="343"/>
+      <c r="F124" s="343"/>
+      <c r="G124" s="343"/>
+      <c r="H124" s="343"/>
+      <c r="J124" s="342"/>
+      <c r="K124" s="342"/>
+      <c r="L124" s="342"/>
+      <c r="M124" s="342"/>
+      <c r="N124" s="342"/>
       <c r="O124" s="39"/>
     </row>
     <row r="125" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C125" s="589"/>
-      <c r="D125" s="589"/>
-      <c r="E125" s="589"/>
-      <c r="F125" s="589"/>
-      <c r="G125" s="589"/>
-      <c r="H125" s="589"/>
-      <c r="J125" s="590"/>
-      <c r="K125" s="590"/>
-      <c r="L125" s="590"/>
-      <c r="M125" s="590"/>
-      <c r="N125" s="590"/>
+      <c r="C125" s="343"/>
+      <c r="D125" s="343"/>
+      <c r="E125" s="343"/>
+      <c r="F125" s="343"/>
+      <c r="G125" s="343"/>
+      <c r="H125" s="343"/>
+      <c r="J125" s="342"/>
+      <c r="K125" s="342"/>
+      <c r="L125" s="342"/>
+      <c r="M125" s="342"/>
+      <c r="N125" s="342"/>
       <c r="O125" s="39"/>
     </row>
     <row r="126" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C126" s="589"/>
-      <c r="D126" s="589"/>
-      <c r="E126" s="589"/>
-      <c r="F126" s="589"/>
-      <c r="G126" s="589"/>
-      <c r="H126" s="589"/>
-      <c r="J126" s="590"/>
-      <c r="K126" s="590"/>
-      <c r="L126" s="590"/>
-      <c r="M126" s="590"/>
-      <c r="N126" s="590"/>
+      <c r="C126" s="343"/>
+      <c r="D126" s="343"/>
+      <c r="E126" s="343"/>
+      <c r="F126" s="343"/>
+      <c r="G126" s="343"/>
+      <c r="H126" s="343"/>
+      <c r="J126" s="342"/>
+      <c r="K126" s="342"/>
+      <c r="L126" s="342"/>
+      <c r="M126" s="342"/>
+      <c r="N126" s="342"/>
       <c r="O126" s="39"/>
     </row>
     <row r="127" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C127" s="589"/>
-      <c r="D127" s="589"/>
-      <c r="E127" s="589"/>
-      <c r="F127" s="589"/>
-      <c r="G127" s="589"/>
-      <c r="H127" s="589"/>
-      <c r="J127" s="590"/>
-      <c r="K127" s="590"/>
-      <c r="L127" s="590"/>
-      <c r="M127" s="590"/>
-      <c r="N127" s="590"/>
+      <c r="C127" s="343"/>
+      <c r="D127" s="343"/>
+      <c r="E127" s="343"/>
+      <c r="F127" s="343"/>
+      <c r="G127" s="343"/>
+      <c r="H127" s="343"/>
+      <c r="J127" s="342"/>
+      <c r="K127" s="342"/>
+      <c r="L127" s="342"/>
+      <c r="M127" s="342"/>
+      <c r="N127" s="342"/>
       <c r="O127" s="39"/>
     </row>
     <row r="128" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C128" s="589"/>
-      <c r="D128" s="589"/>
-      <c r="E128" s="589"/>
-      <c r="F128" s="589"/>
-      <c r="G128" s="589"/>
-      <c r="H128" s="589"/>
-      <c r="J128" s="590"/>
-      <c r="K128" s="590"/>
-      <c r="L128" s="590"/>
-      <c r="M128" s="590"/>
-      <c r="N128" s="590"/>
+      <c r="C128" s="343"/>
+      <c r="D128" s="343"/>
+      <c r="E128" s="343"/>
+      <c r="F128" s="343"/>
+      <c r="G128" s="343"/>
+      <c r="H128" s="343"/>
+      <c r="J128" s="342"/>
+      <c r="K128" s="342"/>
+      <c r="L128" s="342"/>
+      <c r="M128" s="342"/>
+      <c r="N128" s="342"/>
       <c r="O128" s="39"/>
     </row>
     <row r="129" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C129" s="589"/>
-      <c r="D129" s="589"/>
-      <c r="E129" s="589"/>
-      <c r="F129" s="589"/>
-      <c r="G129" s="589"/>
-      <c r="H129" s="589"/>
-      <c r="J129" s="590"/>
-      <c r="K129" s="590"/>
-      <c r="L129" s="590"/>
-      <c r="M129" s="590"/>
-      <c r="N129" s="590"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
+      <c r="G129" s="343"/>
+      <c r="H129" s="343"/>
+      <c r="J129" s="342"/>
+      <c r="K129" s="342"/>
+      <c r="L129" s="342"/>
+      <c r="M129" s="342"/>
+      <c r="N129" s="342"/>
       <c r="O129" s="39"/>
     </row>
     <row r="130" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C130" s="589"/>
-      <c r="D130" s="589"/>
-      <c r="E130" s="589"/>
-      <c r="F130" s="589"/>
-      <c r="G130" s="589"/>
-      <c r="H130" s="589"/>
-      <c r="J130" s="590"/>
-      <c r="K130" s="590"/>
-      <c r="L130" s="590"/>
-      <c r="M130" s="590"/>
-      <c r="N130" s="590"/>
+      <c r="C130" s="343"/>
+      <c r="D130" s="343"/>
+      <c r="E130" s="343"/>
+      <c r="F130" s="343"/>
+      <c r="G130" s="343"/>
+      <c r="H130" s="343"/>
+      <c r="J130" s="342"/>
+      <c r="K130" s="342"/>
+      <c r="L130" s="342"/>
+      <c r="M130" s="342"/>
+      <c r="N130" s="342"/>
       <c r="O130" s="39"/>
     </row>
     <row r="131" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C131" s="589"/>
-      <c r="D131" s="589"/>
-      <c r="E131" s="589"/>
-      <c r="F131" s="589"/>
-      <c r="G131" s="589"/>
-      <c r="H131" s="589"/>
-      <c r="J131" s="590"/>
-      <c r="K131" s="590"/>
-      <c r="L131" s="590"/>
-      <c r="M131" s="590"/>
-      <c r="N131" s="590"/>
+      <c r="C131" s="343"/>
+      <c r="D131" s="343"/>
+      <c r="E131" s="343"/>
+      <c r="F131" s="343"/>
+      <c r="G131" s="343"/>
+      <c r="H131" s="343"/>
+      <c r="J131" s="342"/>
+      <c r="K131" s="342"/>
+      <c r="L131" s="342"/>
+      <c r="M131" s="342"/>
+      <c r="N131" s="342"/>
       <c r="O131" s="39"/>
     </row>
     <row r="132" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C132" s="589"/>
-      <c r="D132" s="589"/>
-      <c r="E132" s="589"/>
-      <c r="F132" s="589"/>
-      <c r="G132" s="589"/>
-      <c r="H132" s="589"/>
-      <c r="J132" s="590"/>
-      <c r="K132" s="590"/>
-      <c r="L132" s="590"/>
-      <c r="M132" s="590"/>
-      <c r="N132" s="590"/>
+      <c r="C132" s="343"/>
+      <c r="D132" s="343"/>
+      <c r="E132" s="343"/>
+      <c r="F132" s="343"/>
+      <c r="G132" s="343"/>
+      <c r="H132" s="343"/>
+      <c r="J132" s="342"/>
+      <c r="K132" s="342"/>
+      <c r="L132" s="342"/>
+      <c r="M132" s="342"/>
+      <c r="N132" s="342"/>
       <c r="O132" s="39"/>
     </row>
     <row r="133" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C133" s="589"/>
-      <c r="D133" s="589"/>
-      <c r="E133" s="589"/>
-      <c r="F133" s="589"/>
-      <c r="G133" s="589"/>
-      <c r="H133" s="589"/>
-      <c r="J133" s="590"/>
-      <c r="K133" s="590"/>
-      <c r="L133" s="590"/>
-      <c r="M133" s="590"/>
-      <c r="N133" s="590"/>
+      <c r="C133" s="343"/>
+      <c r="D133" s="343"/>
+      <c r="E133" s="343"/>
+      <c r="F133" s="343"/>
+      <c r="G133" s="343"/>
+      <c r="H133" s="343"/>
+      <c r="J133" s="342"/>
+      <c r="K133" s="342"/>
+      <c r="L133" s="342"/>
+      <c r="M133" s="342"/>
+      <c r="N133" s="342"/>
       <c r="O133" s="39"/>
     </row>
     <row r="134" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C134" s="589"/>
-      <c r="D134" s="589"/>
-      <c r="E134" s="589"/>
-      <c r="F134" s="589"/>
-      <c r="G134" s="589"/>
-      <c r="H134" s="589"/>
-      <c r="J134" s="590"/>
-      <c r="K134" s="590"/>
-      <c r="L134" s="590"/>
-      <c r="M134" s="590"/>
-      <c r="N134" s="590"/>
+      <c r="C134" s="343"/>
+      <c r="D134" s="343"/>
+      <c r="E134" s="343"/>
+      <c r="F134" s="343"/>
+      <c r="G134" s="343"/>
+      <c r="H134" s="343"/>
+      <c r="J134" s="342"/>
+      <c r="K134" s="342"/>
+      <c r="L134" s="342"/>
+      <c r="M134" s="342"/>
+      <c r="N134" s="342"/>
       <c r="O134" s="39"/>
     </row>
     <row r="135" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C135" s="589"/>
-      <c r="D135" s="589"/>
-      <c r="E135" s="589"/>
-      <c r="F135" s="589"/>
-      <c r="G135" s="589"/>
-      <c r="H135" s="589"/>
-      <c r="J135" s="590"/>
-      <c r="K135" s="590"/>
-      <c r="L135" s="590"/>
-      <c r="M135" s="590"/>
-      <c r="N135" s="590"/>
+      <c r="C135" s="343"/>
+      <c r="D135" s="343"/>
+      <c r="E135" s="343"/>
+      <c r="F135" s="343"/>
+      <c r="G135" s="343"/>
+      <c r="H135" s="343"/>
+      <c r="J135" s="342"/>
+      <c r="K135" s="342"/>
+      <c r="L135" s="342"/>
+      <c r="M135" s="342"/>
+      <c r="N135" s="342"/>
       <c r="O135" s="39"/>
     </row>
     <row r="136" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C136" s="589"/>
-      <c r="D136" s="589"/>
-      <c r="E136" s="589"/>
-      <c r="F136" s="589"/>
-      <c r="G136" s="589"/>
-      <c r="H136" s="589"/>
-      <c r="J136" s="590"/>
-      <c r="K136" s="590"/>
-      <c r="L136" s="590"/>
-      <c r="M136" s="590"/>
-      <c r="N136" s="590"/>
+      <c r="C136" s="343"/>
+      <c r="D136" s="343"/>
+      <c r="E136" s="343"/>
+      <c r="F136" s="343"/>
+      <c r="G136" s="343"/>
+      <c r="H136" s="343"/>
+      <c r="J136" s="342"/>
+      <c r="K136" s="342"/>
+      <c r="L136" s="342"/>
+      <c r="M136" s="342"/>
+      <c r="N136" s="342"/>
       <c r="O136" s="39"/>
     </row>
     <row r="137" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C137" s="589"/>
-      <c r="D137" s="589"/>
-      <c r="E137" s="589"/>
-      <c r="F137" s="589"/>
-      <c r="G137" s="589"/>
-      <c r="H137" s="589"/>
-      <c r="J137" s="590"/>
-      <c r="K137" s="590"/>
-      <c r="L137" s="590"/>
-      <c r="M137" s="590"/>
-      <c r="N137" s="590"/>
+      <c r="C137" s="343"/>
+      <c r="D137" s="343"/>
+      <c r="E137" s="343"/>
+      <c r="F137" s="343"/>
+      <c r="G137" s="343"/>
+      <c r="H137" s="343"/>
+      <c r="J137" s="342"/>
+      <c r="K137" s="342"/>
+      <c r="L137" s="342"/>
+      <c r="M137" s="342"/>
+      <c r="N137" s="342"/>
       <c r="O137" s="39"/>
     </row>
     <row r="138" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C138" s="589"/>
-      <c r="D138" s="589"/>
-      <c r="E138" s="589"/>
-      <c r="F138" s="589"/>
-      <c r="G138" s="589"/>
-      <c r="H138" s="589"/>
-      <c r="J138" s="590"/>
-      <c r="K138" s="590"/>
-      <c r="L138" s="590"/>
-      <c r="M138" s="590"/>
-      <c r="N138" s="590"/>
+      <c r="C138" s="343"/>
+      <c r="D138" s="343"/>
+      <c r="E138" s="343"/>
+      <c r="F138" s="343"/>
+      <c r="G138" s="343"/>
+      <c r="H138" s="343"/>
+      <c r="J138" s="342"/>
+      <c r="K138" s="342"/>
+      <c r="L138" s="342"/>
+      <c r="M138" s="342"/>
+      <c r="N138" s="342"/>
       <c r="O138" s="39"/>
     </row>
     <row r="139" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C139" s="589"/>
-      <c r="D139" s="589"/>
-      <c r="E139" s="589"/>
-      <c r="F139" s="589"/>
-      <c r="G139" s="589"/>
-      <c r="H139" s="589"/>
-      <c r="J139" s="590"/>
-      <c r="K139" s="590"/>
-      <c r="L139" s="590"/>
-      <c r="M139" s="590"/>
-      <c r="N139" s="590"/>
+      <c r="C139" s="343"/>
+      <c r="D139" s="343"/>
+      <c r="E139" s="343"/>
+      <c r="F139" s="343"/>
+      <c r="G139" s="343"/>
+      <c r="H139" s="343"/>
+      <c r="J139" s="342"/>
+      <c r="K139" s="342"/>
+      <c r="L139" s="342"/>
+      <c r="M139" s="342"/>
+      <c r="N139" s="342"/>
       <c r="O139" s="39"/>
     </row>
     <row r="140" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C140" s="589"/>
-      <c r="D140" s="589"/>
-      <c r="E140" s="589"/>
-      <c r="F140" s="589"/>
-      <c r="G140" s="589"/>
-      <c r="H140" s="589"/>
-      <c r="J140" s="590"/>
-      <c r="K140" s="590"/>
-      <c r="L140" s="590"/>
-      <c r="M140" s="590"/>
-      <c r="N140" s="590"/>
+      <c r="C140" s="343"/>
+      <c r="D140" s="343"/>
+      <c r="E140" s="343"/>
+      <c r="F140" s="343"/>
+      <c r="G140" s="343"/>
+      <c r="H140" s="343"/>
+      <c r="J140" s="342"/>
+      <c r="K140" s="342"/>
+      <c r="L140" s="342"/>
+      <c r="M140" s="342"/>
+      <c r="N140" s="342"/>
       <c r="O140" s="39"/>
     </row>
     <row r="141" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C141" s="589"/>
-      <c r="D141" s="589"/>
-      <c r="E141" s="589"/>
-      <c r="F141" s="589"/>
-      <c r="G141" s="589"/>
-      <c r="H141" s="589"/>
-      <c r="J141" s="590"/>
-      <c r="K141" s="590"/>
-      <c r="L141" s="590"/>
-      <c r="M141" s="590"/>
-      <c r="N141" s="590"/>
+      <c r="C141" s="343"/>
+      <c r="D141" s="343"/>
+      <c r="E141" s="343"/>
+      <c r="F141" s="343"/>
+      <c r="G141" s="343"/>
+      <c r="H141" s="343"/>
+      <c r="J141" s="342"/>
+      <c r="K141" s="342"/>
+      <c r="L141" s="342"/>
+      <c r="M141" s="342"/>
+      <c r="N141" s="342"/>
       <c r="O141" s="39"/>
     </row>
     <row r="142" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C142" s="589"/>
-      <c r="D142" s="589"/>
-      <c r="E142" s="589"/>
-      <c r="F142" s="589"/>
-      <c r="G142" s="589"/>
-      <c r="H142" s="589"/>
-      <c r="J142" s="590"/>
-      <c r="K142" s="590"/>
-      <c r="L142" s="590"/>
-      <c r="M142" s="590"/>
-      <c r="N142" s="590"/>
+      <c r="C142" s="343"/>
+      <c r="D142" s="343"/>
+      <c r="E142" s="343"/>
+      <c r="F142" s="343"/>
+      <c r="G142" s="343"/>
+      <c r="H142" s="343"/>
+      <c r="J142" s="342"/>
+      <c r="K142" s="342"/>
+      <c r="L142" s="342"/>
+      <c r="M142" s="342"/>
+      <c r="N142" s="342"/>
       <c r="O142" s="39"/>
     </row>
     <row r="143" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C143" s="589"/>
-      <c r="D143" s="589"/>
-      <c r="E143" s="589"/>
-      <c r="F143" s="589"/>
-      <c r="G143" s="589"/>
-      <c r="H143" s="589"/>
-      <c r="J143" s="590"/>
-      <c r="K143" s="590"/>
-      <c r="L143" s="590"/>
-      <c r="M143" s="590"/>
-      <c r="N143" s="590"/>
+      <c r="C143" s="343"/>
+      <c r="D143" s="343"/>
+      <c r="E143" s="343"/>
+      <c r="F143" s="343"/>
+      <c r="G143" s="343"/>
+      <c r="H143" s="343"/>
+      <c r="J143" s="342"/>
+      <c r="K143" s="342"/>
+      <c r="L143" s="342"/>
+      <c r="M143" s="342"/>
+      <c r="N143" s="342"/>
       <c r="O143" s="39"/>
     </row>
     <row r="144" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C144" s="589"/>
-      <c r="D144" s="589"/>
-      <c r="E144" s="589"/>
-      <c r="F144" s="589"/>
-      <c r="G144" s="589"/>
-      <c r="H144" s="589"/>
-      <c r="J144" s="590"/>
-      <c r="K144" s="590"/>
-      <c r="L144" s="590"/>
-      <c r="M144" s="590"/>
-      <c r="N144" s="590"/>
+      <c r="C144" s="343"/>
+      <c r="D144" s="343"/>
+      <c r="E144" s="343"/>
+      <c r="F144" s="343"/>
+      <c r="G144" s="343"/>
+      <c r="H144" s="343"/>
+      <c r="J144" s="342"/>
+      <c r="K144" s="342"/>
+      <c r="L144" s="342"/>
+      <c r="M144" s="342"/>
+      <c r="N144" s="342"/>
       <c r="O144" s="39"/>
     </row>
     <row r="145" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C145" s="589"/>
-      <c r="D145" s="589"/>
-      <c r="E145" s="589"/>
-      <c r="F145" s="589"/>
-      <c r="G145" s="589"/>
-      <c r="H145" s="589"/>
-      <c r="J145" s="590"/>
-      <c r="K145" s="590"/>
-      <c r="L145" s="590"/>
-      <c r="M145" s="590"/>
-      <c r="N145" s="590"/>
+      <c r="C145" s="343"/>
+      <c r="D145" s="343"/>
+      <c r="E145" s="343"/>
+      <c r="F145" s="343"/>
+      <c r="G145" s="343"/>
+      <c r="H145" s="343"/>
+      <c r="J145" s="342"/>
+      <c r="K145" s="342"/>
+      <c r="L145" s="342"/>
+      <c r="M145" s="342"/>
+      <c r="N145" s="342"/>
       <c r="O145" s="39"/>
     </row>
     <row r="146" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C146" s="589"/>
-      <c r="D146" s="589"/>
-      <c r="E146" s="589"/>
-      <c r="F146" s="589"/>
-      <c r="G146" s="589"/>
-      <c r="H146" s="589"/>
-      <c r="J146" s="590"/>
-      <c r="K146" s="590"/>
-      <c r="L146" s="590"/>
-      <c r="M146" s="590"/>
-      <c r="N146" s="590"/>
+      <c r="C146" s="343"/>
+      <c r="D146" s="343"/>
+      <c r="E146" s="343"/>
+      <c r="F146" s="343"/>
+      <c r="G146" s="343"/>
+      <c r="H146" s="343"/>
+      <c r="J146" s="342"/>
+      <c r="K146" s="342"/>
+      <c r="L146" s="342"/>
+      <c r="M146" s="342"/>
+      <c r="N146" s="342"/>
       <c r="O146" s="39"/>
     </row>
     <row r="147" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C147" s="589"/>
-      <c r="D147" s="589"/>
-      <c r="E147" s="589"/>
-      <c r="F147" s="589"/>
-      <c r="G147" s="589"/>
-      <c r="H147" s="589"/>
-      <c r="J147" s="590"/>
-      <c r="K147" s="590"/>
-      <c r="L147" s="590"/>
-      <c r="M147" s="590"/>
-      <c r="N147" s="590"/>
+      <c r="C147" s="343"/>
+      <c r="D147" s="343"/>
+      <c r="E147" s="343"/>
+      <c r="F147" s="343"/>
+      <c r="G147" s="343"/>
+      <c r="H147" s="343"/>
+      <c r="J147" s="342"/>
+      <c r="K147" s="342"/>
+      <c r="L147" s="342"/>
+      <c r="M147" s="342"/>
+      <c r="N147" s="342"/>
       <c r="O147" s="39"/>
     </row>
     <row r="148" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C148" s="589"/>
-      <c r="D148" s="589"/>
-      <c r="E148" s="589"/>
-      <c r="F148" s="589"/>
-      <c r="G148" s="589"/>
-      <c r="H148" s="589"/>
-      <c r="J148" s="590"/>
-      <c r="K148" s="590"/>
-      <c r="L148" s="590"/>
-      <c r="M148" s="590"/>
-      <c r="N148" s="590"/>
+      <c r="C148" s="343"/>
+      <c r="D148" s="343"/>
+      <c r="E148" s="343"/>
+      <c r="F148" s="343"/>
+      <c r="G148" s="343"/>
+      <c r="H148" s="343"/>
+      <c r="J148" s="342"/>
+      <c r="K148" s="342"/>
+      <c r="L148" s="342"/>
+      <c r="M148" s="342"/>
+      <c r="N148" s="342"/>
       <c r="O148" s="39"/>
     </row>
     <row r="149" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C149" s="589"/>
-      <c r="D149" s="589"/>
-      <c r="E149" s="589"/>
-      <c r="F149" s="589"/>
-      <c r="G149" s="589"/>
-      <c r="H149" s="589"/>
-      <c r="J149" s="590"/>
-      <c r="K149" s="590"/>
-      <c r="L149" s="590"/>
-      <c r="M149" s="590"/>
-      <c r="N149" s="590"/>
+      <c r="C149" s="343"/>
+      <c r="D149" s="343"/>
+      <c r="E149" s="343"/>
+      <c r="F149" s="343"/>
+      <c r="G149" s="343"/>
+      <c r="H149" s="343"/>
+      <c r="J149" s="342"/>
+      <c r="K149" s="342"/>
+      <c r="L149" s="342"/>
+      <c r="M149" s="342"/>
+      <c r="N149" s="342"/>
       <c r="O149" s="39"/>
     </row>
     <row r="150" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C150" s="589"/>
-      <c r="D150" s="589"/>
-      <c r="E150" s="589"/>
-      <c r="F150" s="589"/>
-      <c r="G150" s="589"/>
-      <c r="H150" s="589"/>
-      <c r="J150" s="590"/>
-      <c r="K150" s="590"/>
-      <c r="L150" s="590"/>
-      <c r="M150" s="590"/>
-      <c r="N150" s="590"/>
+      <c r="C150" s="343"/>
+      <c r="D150" s="343"/>
+      <c r="E150" s="343"/>
+      <c r="F150" s="343"/>
+      <c r="G150" s="343"/>
+      <c r="H150" s="343"/>
+      <c r="J150" s="342"/>
+      <c r="K150" s="342"/>
+      <c r="L150" s="342"/>
+      <c r="M150" s="342"/>
+      <c r="N150" s="342"/>
       <c r="O150" s="39"/>
     </row>
     <row r="151" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C151" s="589"/>
-      <c r="D151" s="589"/>
-      <c r="E151" s="589"/>
-      <c r="F151" s="589"/>
-      <c r="G151" s="589"/>
-      <c r="H151" s="589"/>
-      <c r="J151" s="590"/>
-      <c r="K151" s="590"/>
-      <c r="L151" s="590"/>
-      <c r="M151" s="590"/>
-      <c r="N151" s="590"/>
+      <c r="C151" s="343"/>
+      <c r="D151" s="343"/>
+      <c r="E151" s="343"/>
+      <c r="F151" s="343"/>
+      <c r="G151" s="343"/>
+      <c r="H151" s="343"/>
+      <c r="J151" s="342"/>
+      <c r="K151" s="342"/>
+      <c r="L151" s="342"/>
+      <c r="M151" s="342"/>
+      <c r="N151" s="342"/>
       <c r="O151" s="39"/>
     </row>
     <row r="152" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C152" s="589"/>
-      <c r="D152" s="589"/>
-      <c r="E152" s="589"/>
-      <c r="F152" s="589"/>
-      <c r="G152" s="589"/>
-      <c r="H152" s="589"/>
-      <c r="J152" s="590"/>
-      <c r="K152" s="590"/>
-      <c r="L152" s="590"/>
-      <c r="M152" s="590"/>
-      <c r="N152" s="590"/>
+      <c r="C152" s="343"/>
+      <c r="D152" s="343"/>
+      <c r="E152" s="343"/>
+      <c r="F152" s="343"/>
+      <c r="G152" s="343"/>
+      <c r="H152" s="343"/>
+      <c r="J152" s="342"/>
+      <c r="K152" s="342"/>
+      <c r="L152" s="342"/>
+      <c r="M152" s="342"/>
+      <c r="N152" s="342"/>
       <c r="O152" s="39"/>
     </row>
     <row r="153" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C153" s="589"/>
-      <c r="D153" s="589"/>
-      <c r="E153" s="589"/>
-      <c r="F153" s="589"/>
-      <c r="G153" s="589"/>
-      <c r="H153" s="589"/>
-      <c r="J153" s="590"/>
-      <c r="K153" s="590"/>
-      <c r="L153" s="590"/>
-      <c r="M153" s="590"/>
-      <c r="N153" s="590"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
+      <c r="G153" s="343"/>
+      <c r="H153" s="343"/>
+      <c r="J153" s="342"/>
+      <c r="K153" s="342"/>
+      <c r="L153" s="342"/>
+      <c r="M153" s="342"/>
+      <c r="N153" s="342"/>
       <c r="O153" s="39"/>
     </row>
     <row r="154" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C154" s="589"/>
-      <c r="D154" s="589"/>
-      <c r="E154" s="589"/>
-      <c r="F154" s="589"/>
-      <c r="G154" s="589"/>
-      <c r="H154" s="589"/>
-      <c r="J154" s="590"/>
-      <c r="K154" s="590"/>
-      <c r="L154" s="590"/>
-      <c r="M154" s="590"/>
-      <c r="N154" s="590"/>
+      <c r="C154" s="343"/>
+      <c r="D154" s="343"/>
+      <c r="E154" s="343"/>
+      <c r="F154" s="343"/>
+      <c r="G154" s="343"/>
+      <c r="H154" s="343"/>
+      <c r="J154" s="342"/>
+      <c r="K154" s="342"/>
+      <c r="L154" s="342"/>
+      <c r="M154" s="342"/>
+      <c r="N154" s="342"/>
       <c r="O154" s="39"/>
     </row>
     <row r="155" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C155" s="589"/>
-      <c r="D155" s="589"/>
-      <c r="E155" s="589"/>
-      <c r="F155" s="589"/>
-      <c r="G155" s="589"/>
-      <c r="H155" s="589"/>
-      <c r="J155" s="590"/>
-      <c r="K155" s="590"/>
-      <c r="L155" s="590"/>
-      <c r="M155" s="590"/>
-      <c r="N155" s="590"/>
+      <c r="C155" s="343"/>
+      <c r="D155" s="343"/>
+      <c r="E155" s="343"/>
+      <c r="F155" s="343"/>
+      <c r="G155" s="343"/>
+      <c r="H155" s="343"/>
+      <c r="J155" s="342"/>
+      <c r="K155" s="342"/>
+      <c r="L155" s="342"/>
+      <c r="M155" s="342"/>
+      <c r="N155" s="342"/>
       <c r="O155" s="39"/>
     </row>
     <row r="156" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C156" s="589"/>
-      <c r="D156" s="589"/>
-      <c r="E156" s="589"/>
-      <c r="F156" s="589"/>
-      <c r="G156" s="589"/>
-      <c r="H156" s="589"/>
-      <c r="J156" s="590"/>
-      <c r="K156" s="590"/>
-      <c r="L156" s="590"/>
-      <c r="M156" s="590"/>
-      <c r="N156" s="590"/>
+      <c r="C156" s="343"/>
+      <c r="D156" s="343"/>
+      <c r="E156" s="343"/>
+      <c r="F156" s="343"/>
+      <c r="G156" s="343"/>
+      <c r="H156" s="343"/>
+      <c r="J156" s="342"/>
+      <c r="K156" s="342"/>
+      <c r="L156" s="342"/>
+      <c r="M156" s="342"/>
+      <c r="N156" s="342"/>
       <c r="O156" s="39"/>
     </row>
     <row r="157" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C157" s="589"/>
-      <c r="D157" s="589"/>
-      <c r="E157" s="589"/>
-      <c r="F157" s="589"/>
-      <c r="G157" s="589"/>
-      <c r="H157" s="589"/>
-      <c r="J157" s="590"/>
-      <c r="K157" s="590"/>
-      <c r="L157" s="590"/>
-      <c r="M157" s="590"/>
-      <c r="N157" s="590"/>
+      <c r="C157" s="343"/>
+      <c r="D157" s="343"/>
+      <c r="E157" s="343"/>
+      <c r="F157" s="343"/>
+      <c r="G157" s="343"/>
+      <c r="H157" s="343"/>
+      <c r="J157" s="342"/>
+      <c r="K157" s="342"/>
+      <c r="L157" s="342"/>
+      <c r="M157" s="342"/>
+      <c r="N157" s="342"/>
       <c r="O157" s="39"/>
     </row>
     <row r="158" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C158" s="589"/>
-      <c r="D158" s="589"/>
-      <c r="E158" s="589"/>
-      <c r="F158" s="589"/>
-      <c r="G158" s="589"/>
-      <c r="H158" s="589"/>
-      <c r="J158" s="590"/>
-      <c r="K158" s="590"/>
-      <c r="L158" s="590"/>
-      <c r="M158" s="590"/>
-      <c r="N158" s="590"/>
+      <c r="C158" s="343"/>
+      <c r="D158" s="343"/>
+      <c r="E158" s="343"/>
+      <c r="F158" s="343"/>
+      <c r="G158" s="343"/>
+      <c r="H158" s="343"/>
+      <c r="J158" s="342"/>
+      <c r="K158" s="342"/>
+      <c r="L158" s="342"/>
+      <c r="M158" s="342"/>
+      <c r="N158" s="342"/>
       <c r="O158" s="39"/>
     </row>
     <row r="159" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C159" s="589"/>
-      <c r="D159" s="589"/>
-      <c r="E159" s="589"/>
-      <c r="F159" s="589"/>
-      <c r="G159" s="589"/>
-      <c r="H159" s="589"/>
-      <c r="J159" s="590"/>
-      <c r="K159" s="590"/>
-      <c r="L159" s="590"/>
-      <c r="M159" s="590"/>
-      <c r="N159" s="590"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
+      <c r="G159" s="343"/>
+      <c r="H159" s="343"/>
+      <c r="J159" s="342"/>
+      <c r="K159" s="342"/>
+      <c r="L159" s="342"/>
+      <c r="M159" s="342"/>
+      <c r="N159" s="342"/>
       <c r="O159" s="39"/>
     </row>
     <row r="160" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C160" s="589"/>
-      <c r="D160" s="589"/>
-      <c r="E160" s="589"/>
-      <c r="F160" s="589"/>
-      <c r="G160" s="589"/>
-      <c r="H160" s="589"/>
-      <c r="J160" s="590"/>
-      <c r="K160" s="590"/>
-      <c r="L160" s="590"/>
-      <c r="M160" s="590"/>
-      <c r="N160" s="590"/>
+      <c r="C160" s="343"/>
+      <c r="D160" s="343"/>
+      <c r="E160" s="343"/>
+      <c r="F160" s="343"/>
+      <c r="G160" s="343"/>
+      <c r="H160" s="343"/>
+      <c r="J160" s="342"/>
+      <c r="K160" s="342"/>
+      <c r="L160" s="342"/>
+      <c r="M160" s="342"/>
+      <c r="N160" s="342"/>
       <c r="O160" s="39"/>
     </row>
     <row r="161" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C161" s="589"/>
-      <c r="D161" s="589"/>
-      <c r="E161" s="589"/>
-      <c r="F161" s="589"/>
-      <c r="G161" s="589"/>
-      <c r="H161" s="589"/>
-      <c r="J161" s="590"/>
-      <c r="K161" s="590"/>
-      <c r="L161" s="590"/>
-      <c r="M161" s="590"/>
-      <c r="N161" s="590"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
+      <c r="G161" s="343"/>
+      <c r="H161" s="343"/>
+      <c r="J161" s="342"/>
+      <c r="K161" s="342"/>
+      <c r="L161" s="342"/>
+      <c r="M161" s="342"/>
+      <c r="N161" s="342"/>
       <c r="O161" s="39"/>
     </row>
     <row r="162" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C162" s="589"/>
-      <c r="D162" s="589"/>
-      <c r="E162" s="589"/>
-      <c r="F162" s="589"/>
-      <c r="G162" s="589"/>
-      <c r="H162" s="589"/>
-      <c r="J162" s="590"/>
-      <c r="K162" s="590"/>
-      <c r="L162" s="590"/>
-      <c r="M162" s="590"/>
-      <c r="N162" s="590"/>
+      <c r="C162" s="343"/>
+      <c r="D162" s="343"/>
+      <c r="E162" s="343"/>
+      <c r="F162" s="343"/>
+      <c r="G162" s="343"/>
+      <c r="H162" s="343"/>
+      <c r="J162" s="342"/>
+      <c r="K162" s="342"/>
+      <c r="L162" s="342"/>
+      <c r="M162" s="342"/>
+      <c r="N162" s="342"/>
       <c r="O162" s="39"/>
     </row>
     <row r="163" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C163" s="589"/>
-      <c r="D163" s="589"/>
-      <c r="E163" s="589"/>
-      <c r="F163" s="589"/>
-      <c r="G163" s="589"/>
-      <c r="H163" s="589"/>
-      <c r="J163" s="590"/>
-      <c r="K163" s="590"/>
-      <c r="L163" s="590"/>
-      <c r="M163" s="590"/>
-      <c r="N163" s="590"/>
+      <c r="C163" s="343"/>
+      <c r="D163" s="343"/>
+      <c r="E163" s="343"/>
+      <c r="F163" s="343"/>
+      <c r="G163" s="343"/>
+      <c r="H163" s="343"/>
+      <c r="J163" s="342"/>
+      <c r="K163" s="342"/>
+      <c r="L163" s="342"/>
+      <c r="M163" s="342"/>
+      <c r="N163" s="342"/>
       <c r="O163" s="39"/>
     </row>
     <row r="164" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C164" s="589"/>
-      <c r="D164" s="589"/>
-      <c r="E164" s="589"/>
-      <c r="F164" s="589"/>
-      <c r="G164" s="589"/>
-      <c r="H164" s="589"/>
-      <c r="J164" s="590"/>
-      <c r="K164" s="590"/>
-      <c r="L164" s="590"/>
-      <c r="M164" s="590"/>
-      <c r="N164" s="590"/>
+      <c r="C164" s="343"/>
+      <c r="D164" s="343"/>
+      <c r="E164" s="343"/>
+      <c r="F164" s="343"/>
+      <c r="G164" s="343"/>
+      <c r="H164" s="343"/>
+      <c r="J164" s="342"/>
+      <c r="K164" s="342"/>
+      <c r="L164" s="342"/>
+      <c r="M164" s="342"/>
+      <c r="N164" s="342"/>
       <c r="O164" s="39"/>
     </row>
     <row r="165" spans="3:15" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C165" s="589"/>
-      <c r="D165" s="589"/>
-      <c r="E165" s="589"/>
-      <c r="F165" s="589"/>
-      <c r="G165" s="589"/>
-      <c r="H165" s="589"/>
-      <c r="J165" s="590"/>
-      <c r="K165" s="590"/>
-      <c r="L165" s="590"/>
-      <c r="M165" s="590"/>
-      <c r="N165" s="590"/>
+      <c r="C165" s="343"/>
+      <c r="D165" s="343"/>
+      <c r="E165" s="343"/>
+      <c r="F165" s="343"/>
+      <c r="G165" s="343"/>
+      <c r="H165" s="343"/>
+      <c r="J165" s="342"/>
+      <c r="K165" s="342"/>
+      <c r="L165" s="342"/>
+      <c r="M165" s="342"/>
+      <c r="N165" s="342"/>
       <c r="O165" s="39"/>
     </row>
     <row r="166" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C166" s="589"/>
-      <c r="D166" s="589"/>
-      <c r="E166" s="589"/>
-      <c r="F166" s="589"/>
-      <c r="G166" s="589"/>
-      <c r="H166" s="589"/>
-      <c r="J166" s="590"/>
-      <c r="K166" s="590"/>
-      <c r="L166" s="590"/>
-      <c r="M166" s="590"/>
-      <c r="N166" s="590"/>
+      <c r="C166" s="343"/>
+      <c r="D166" s="343"/>
+      <c r="E166" s="343"/>
+      <c r="F166" s="343"/>
+      <c r="G166" s="343"/>
+      <c r="H166" s="343"/>
+      <c r="J166" s="342"/>
+      <c r="K166" s="342"/>
+      <c r="L166" s="342"/>
+      <c r="M166" s="342"/>
+      <c r="N166" s="342"/>
       <c r="O166" s="39"/>
     </row>
     <row r="167" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C167" s="589"/>
-      <c r="D167" s="589"/>
-      <c r="E167" s="589"/>
-      <c r="F167" s="589"/>
-      <c r="G167" s="589"/>
-      <c r="H167" s="589"/>
-      <c r="J167" s="590"/>
-      <c r="K167" s="590"/>
-      <c r="L167" s="590"/>
-      <c r="M167" s="590"/>
-      <c r="N167" s="590"/>
+      <c r="C167" s="343"/>
+      <c r="D167" s="343"/>
+      <c r="E167" s="343"/>
+      <c r="F167" s="343"/>
+      <c r="G167" s="343"/>
+      <c r="H167" s="343"/>
+      <c r="J167" s="342"/>
+      <c r="K167" s="342"/>
+      <c r="L167" s="342"/>
+      <c r="M167" s="342"/>
+      <c r="N167" s="342"/>
       <c r="O167" s="39"/>
     </row>
     <row r="168" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C168" s="589"/>
-      <c r="D168" s="589"/>
-      <c r="E168" s="589"/>
-      <c r="F168" s="589"/>
-      <c r="G168" s="589"/>
-      <c r="H168" s="589"/>
-      <c r="J168" s="590"/>
-      <c r="K168" s="590"/>
-      <c r="L168" s="590"/>
-      <c r="M168" s="590"/>
-      <c r="N168" s="590"/>
+      <c r="C168" s="343"/>
+      <c r="D168" s="343"/>
+      <c r="E168" s="343"/>
+      <c r="F168" s="343"/>
+      <c r="G168" s="343"/>
+      <c r="H168" s="343"/>
+      <c r="J168" s="342"/>
+      <c r="K168" s="342"/>
+      <c r="L168" s="342"/>
+      <c r="M168" s="342"/>
+      <c r="N168" s="342"/>
       <c r="O168" s="39"/>
     </row>
     <row r="169" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C169" s="589"/>
-      <c r="D169" s="589"/>
-      <c r="E169" s="589"/>
-      <c r="F169" s="589"/>
-      <c r="G169" s="589"/>
-      <c r="H169" s="589"/>
-      <c r="J169" s="590"/>
-      <c r="K169" s="590"/>
-      <c r="L169" s="590"/>
-      <c r="M169" s="590"/>
-      <c r="N169" s="590"/>
+      <c r="C169" s="343"/>
+      <c r="D169" s="343"/>
+      <c r="E169" s="343"/>
+      <c r="F169" s="343"/>
+      <c r="G169" s="343"/>
+      <c r="H169" s="343"/>
+      <c r="J169" s="342"/>
+      <c r="K169" s="342"/>
+      <c r="L169" s="342"/>
+      <c r="M169" s="342"/>
+      <c r="N169" s="342"/>
       <c r="O169" s="39"/>
     </row>
     <row r="170" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C170" s="589"/>
-      <c r="D170" s="589"/>
-      <c r="E170" s="589"/>
-      <c r="F170" s="589"/>
-      <c r="G170" s="589"/>
-      <c r="H170" s="589"/>
-      <c r="J170" s="590"/>
-      <c r="K170" s="590"/>
-      <c r="L170" s="590"/>
-      <c r="M170" s="590"/>
-      <c r="N170" s="590"/>
+      <c r="C170" s="343"/>
+      <c r="D170" s="343"/>
+      <c r="E170" s="343"/>
+      <c r="F170" s="343"/>
+      <c r="G170" s="343"/>
+      <c r="H170" s="343"/>
+      <c r="J170" s="342"/>
+      <c r="K170" s="342"/>
+      <c r="L170" s="342"/>
+      <c r="M170" s="342"/>
+      <c r="N170" s="342"/>
       <c r="O170" s="39"/>
     </row>
     <row r="171" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
-      <c r="C171" s="589"/>
-      <c r="D171" s="589"/>
-      <c r="E171" s="589"/>
-      <c r="F171" s="589"/>
-      <c r="G171" s="589"/>
-      <c r="H171" s="589"/>
-      <c r="J171" s="590"/>
-      <c r="K171" s="590"/>
-      <c r="L171" s="590"/>
-      <c r="M171" s="590"/>
-      <c r="N171" s="590"/>
+      <c r="C171" s="343"/>
+      <c r="D171" s="343"/>
+      <c r="E171" s="343"/>
+      <c r="F171" s="343"/>
+      <c r="G171" s="343"/>
+      <c r="H171" s="343"/>
+      <c r="J171" s="342"/>
+      <c r="K171" s="342"/>
+      <c r="L171" s="342"/>
+      <c r="M171" s="342"/>
+      <c r="N171" s="342"/>
       <c r="O171" s="39"/>
     </row>
     <row r="172" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C172" s="589"/>
-      <c r="D172" s="589"/>
-      <c r="E172" s="589"/>
-      <c r="F172" s="589"/>
-      <c r="G172" s="589"/>
-      <c r="H172" s="589"/>
-      <c r="J172" s="590"/>
-      <c r="K172" s="590"/>
-      <c r="L172" s="590"/>
-      <c r="M172" s="590"/>
-      <c r="N172" s="590"/>
+      <c r="C172" s="343"/>
+      <c r="D172" s="343"/>
+      <c r="E172" s="343"/>
+      <c r="F172" s="343"/>
+      <c r="G172" s="343"/>
+      <c r="H172" s="343"/>
+      <c r="J172" s="342"/>
+      <c r="K172" s="342"/>
+      <c r="L172" s="342"/>
+      <c r="M172" s="342"/>
+      <c r="N172" s="342"/>
       <c r="O172" s="39"/>
     </row>
     <row r="173" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C173" s="589"/>
-      <c r="D173" s="589"/>
-      <c r="E173" s="589"/>
-      <c r="F173" s="589"/>
-      <c r="G173" s="589"/>
-      <c r="H173" s="589"/>
-      <c r="J173" s="590"/>
-      <c r="K173" s="590"/>
-      <c r="L173" s="590"/>
-      <c r="M173" s="590"/>
-      <c r="N173" s="590"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
+      <c r="G173" s="343"/>
+      <c r="H173" s="343"/>
+      <c r="J173" s="342"/>
+      <c r="K173" s="342"/>
+      <c r="L173" s="342"/>
+      <c r="M173" s="342"/>
+      <c r="N173" s="342"/>
       <c r="O173" s="39"/>
     </row>
     <row r="174" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C174" s="589"/>
-      <c r="D174" s="589"/>
-      <c r="E174" s="589"/>
-      <c r="F174" s="589"/>
-      <c r="G174" s="589"/>
-      <c r="H174" s="589"/>
-      <c r="J174" s="590"/>
-      <c r="K174" s="590"/>
-      <c r="L174" s="590"/>
-      <c r="M174" s="590"/>
-      <c r="N174" s="590"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
+      <c r="G174" s="343"/>
+      <c r="H174" s="343"/>
+      <c r="J174" s="342"/>
+      <c r="K174" s="342"/>
+      <c r="L174" s="342"/>
+      <c r="M174" s="342"/>
+      <c r="N174" s="342"/>
       <c r="O174" s="39"/>
     </row>
     <row r="175" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C175" s="589"/>
-      <c r="D175" s="589"/>
-      <c r="E175" s="589"/>
-      <c r="F175" s="589"/>
-      <c r="G175" s="589"/>
-      <c r="H175" s="589"/>
-      <c r="J175" s="590"/>
-      <c r="K175" s="590"/>
-      <c r="L175" s="590"/>
-      <c r="M175" s="590"/>
-      <c r="N175" s="590"/>
+      <c r="C175" s="343"/>
+      <c r="D175" s="343"/>
+      <c r="E175" s="343"/>
+      <c r="F175" s="343"/>
+      <c r="G175" s="343"/>
+      <c r="H175" s="343"/>
+      <c r="J175" s="342"/>
+      <c r="K175" s="342"/>
+      <c r="L175" s="342"/>
+      <c r="M175" s="342"/>
+      <c r="N175" s="342"/>
       <c r="O175" s="39"/>
     </row>
     <row r="176" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C176" s="589"/>
-      <c r="D176" s="589"/>
-      <c r="E176" s="589"/>
-      <c r="F176" s="589"/>
-      <c r="G176" s="589"/>
-      <c r="H176" s="589"/>
-      <c r="J176" s="590"/>
-      <c r="K176" s="590"/>
-      <c r="L176" s="590"/>
-      <c r="M176" s="590"/>
-      <c r="N176" s="590"/>
+      <c r="C176" s="343"/>
+      <c r="D176" s="343"/>
+      <c r="E176" s="343"/>
+      <c r="F176" s="343"/>
+      <c r="G176" s="343"/>
+      <c r="H176" s="343"/>
+      <c r="J176" s="342"/>
+      <c r="K176" s="342"/>
+      <c r="L176" s="342"/>
+      <c r="M176" s="342"/>
+      <c r="N176" s="342"/>
       <c r="O176" s="39"/>
     </row>
     <row r="177" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C177" s="589"/>
-      <c r="D177" s="589"/>
-      <c r="E177" s="589"/>
-      <c r="F177" s="589"/>
-      <c r="G177" s="589"/>
-      <c r="H177" s="589"/>
-      <c r="J177" s="590"/>
-      <c r="K177" s="590"/>
-      <c r="L177" s="590"/>
-      <c r="M177" s="590"/>
-      <c r="N177" s="590"/>
+      <c r="C177" s="343"/>
+      <c r="D177" s="343"/>
+      <c r="E177" s="343"/>
+      <c r="F177" s="343"/>
+      <c r="G177" s="343"/>
+      <c r="H177" s="343"/>
+      <c r="J177" s="342"/>
+      <c r="K177" s="342"/>
+      <c r="L177" s="342"/>
+      <c r="M177" s="342"/>
+      <c r="N177" s="342"/>
       <c r="O177" s="39"/>
     </row>
     <row r="178" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C178" s="589"/>
-      <c r="D178" s="589"/>
-      <c r="E178" s="589"/>
-      <c r="F178" s="589"/>
-      <c r="G178" s="589"/>
-      <c r="H178" s="589"/>
-      <c r="J178" s="590"/>
-      <c r="K178" s="590"/>
-      <c r="L178" s="590"/>
-      <c r="M178" s="590"/>
-      <c r="N178" s="590"/>
+      <c r="C178" s="343"/>
+      <c r="D178" s="343"/>
+      <c r="E178" s="343"/>
+      <c r="F178" s="343"/>
+      <c r="G178" s="343"/>
+      <c r="H178" s="343"/>
+      <c r="J178" s="342"/>
+      <c r="K178" s="342"/>
+      <c r="L178" s="342"/>
+      <c r="M178" s="342"/>
+      <c r="N178" s="342"/>
       <c r="O178" s="39"/>
     </row>
     <row r="179" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C179" s="589"/>
-      <c r="D179" s="589"/>
-      <c r="E179" s="589"/>
-      <c r="F179" s="589"/>
-      <c r="G179" s="589"/>
-      <c r="H179" s="589"/>
-      <c r="J179" s="590"/>
-      <c r="K179" s="590"/>
-      <c r="L179" s="590"/>
-      <c r="M179" s="590"/>
-      <c r="N179" s="590"/>
+      <c r="C179" s="343"/>
+      <c r="D179" s="343"/>
+      <c r="E179" s="343"/>
+      <c r="F179" s="343"/>
+      <c r="G179" s="343"/>
+      <c r="H179" s="343"/>
+      <c r="J179" s="342"/>
+      <c r="K179" s="342"/>
+      <c r="L179" s="342"/>
+      <c r="M179" s="342"/>
+      <c r="N179" s="342"/>
       <c r="O179" s="39"/>
     </row>
     <row r="180" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C180" s="589"/>
-      <c r="D180" s="589"/>
-      <c r="E180" s="589"/>
-      <c r="F180" s="589"/>
-      <c r="G180" s="589"/>
-      <c r="H180" s="589"/>
-      <c r="J180" s="590"/>
-      <c r="K180" s="590"/>
-      <c r="L180" s="590"/>
-      <c r="M180" s="590"/>
-      <c r="N180" s="590"/>
+      <c r="C180" s="343"/>
+      <c r="D180" s="343"/>
+      <c r="E180" s="343"/>
+      <c r="F180" s="343"/>
+      <c r="G180" s="343"/>
+      <c r="H180" s="343"/>
+      <c r="J180" s="342"/>
+      <c r="K180" s="342"/>
+      <c r="L180" s="342"/>
+      <c r="M180" s="342"/>
+      <c r="N180" s="342"/>
       <c r="O180" s="39"/>
     </row>
     <row r="181" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C181" s="589"/>
-      <c r="D181" s="589"/>
-      <c r="E181" s="589"/>
-      <c r="F181" s="589"/>
-      <c r="G181" s="589"/>
-      <c r="H181" s="589"/>
-      <c r="J181" s="590"/>
-      <c r="K181" s="590"/>
-      <c r="L181" s="590"/>
-      <c r="M181" s="590"/>
-      <c r="N181" s="590"/>
+      <c r="C181" s="343"/>
+      <c r="D181" s="343"/>
+      <c r="E181" s="343"/>
+      <c r="F181" s="343"/>
+      <c r="G181" s="343"/>
+      <c r="H181" s="343"/>
+      <c r="J181" s="342"/>
+      <c r="K181" s="342"/>
+      <c r="L181" s="342"/>
+      <c r="M181" s="342"/>
+      <c r="N181" s="342"/>
       <c r="O181" s="39"/>
     </row>
     <row r="182" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C182" s="589"/>
-      <c r="D182" s="589"/>
-      <c r="E182" s="589"/>
-      <c r="F182" s="589"/>
-      <c r="G182" s="589"/>
-      <c r="H182" s="589"/>
-      <c r="J182" s="590"/>
-      <c r="K182" s="590"/>
-      <c r="L182" s="590"/>
-      <c r="M182" s="590"/>
-      <c r="N182" s="590"/>
+      <c r="C182" s="343"/>
+      <c r="D182" s="343"/>
+      <c r="E182" s="343"/>
+      <c r="F182" s="343"/>
+      <c r="G182" s="343"/>
+      <c r="H182" s="343"/>
+      <c r="J182" s="342"/>
+      <c r="K182" s="342"/>
+      <c r="L182" s="342"/>
+      <c r="M182" s="342"/>
+      <c r="N182" s="342"/>
       <c r="O182" s="39"/>
     </row>
     <row r="183" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C183" s="589"/>
-      <c r="D183" s="589"/>
-      <c r="E183" s="589"/>
-      <c r="F183" s="589"/>
-      <c r="G183" s="589"/>
-      <c r="H183" s="589"/>
-      <c r="J183" s="590"/>
-      <c r="K183" s="590"/>
-      <c r="L183" s="590"/>
-      <c r="M183" s="590"/>
-      <c r="N183" s="590"/>
+      <c r="C183" s="343"/>
+      <c r="D183" s="343"/>
+      <c r="E183" s="343"/>
+      <c r="F183" s="343"/>
+      <c r="G183" s="343"/>
+      <c r="H183" s="343"/>
+      <c r="J183" s="342"/>
+      <c r="K183" s="342"/>
+      <c r="L183" s="342"/>
+      <c r="M183" s="342"/>
+      <c r="N183" s="342"/>
       <c r="O183" s="39"/>
     </row>
     <row r="184" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C184" s="589"/>
-      <c r="D184" s="589"/>
-      <c r="E184" s="589"/>
-      <c r="F184" s="589"/>
-      <c r="G184" s="589"/>
-      <c r="H184" s="589"/>
-      <c r="J184" s="590"/>
-      <c r="K184" s="590"/>
-      <c r="L184" s="590"/>
-      <c r="M184" s="590"/>
-      <c r="N184" s="590"/>
+      <c r="C184" s="343"/>
+      <c r="D184" s="343"/>
+      <c r="E184" s="343"/>
+      <c r="F184" s="343"/>
+      <c r="G184" s="343"/>
+      <c r="H184" s="343"/>
+      <c r="J184" s="342"/>
+      <c r="K184" s="342"/>
+      <c r="L184" s="342"/>
+      <c r="M184" s="342"/>
+      <c r="N184" s="342"/>
       <c r="O184" s="39"/>
     </row>
     <row r="185" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C185" s="589"/>
-      <c r="D185" s="589"/>
-      <c r="E185" s="589"/>
-      <c r="F185" s="589"/>
-      <c r="G185" s="589"/>
-      <c r="H185" s="589"/>
-      <c r="J185" s="590"/>
-      <c r="K185" s="590"/>
-      <c r="L185" s="590"/>
-      <c r="M185" s="590"/>
-      <c r="N185" s="590"/>
+      <c r="C185" s="343"/>
+      <c r="D185" s="343"/>
+      <c r="E185" s="343"/>
+      <c r="F185" s="343"/>
+      <c r="G185" s="343"/>
+      <c r="H185" s="343"/>
+      <c r="J185" s="342"/>
+      <c r="K185" s="342"/>
+      <c r="L185" s="342"/>
+      <c r="M185" s="342"/>
+      <c r="N185" s="342"/>
       <c r="O185" s="39"/>
     </row>
     <row r="186" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C186" s="589"/>
-      <c r="D186" s="589"/>
-      <c r="E186" s="589"/>
-      <c r="F186" s="589"/>
-      <c r="G186" s="589"/>
-      <c r="H186" s="589"/>
-      <c r="J186" s="590"/>
-      <c r="K186" s="590"/>
-      <c r="L186" s="590"/>
-      <c r="M186" s="590"/>
-      <c r="N186" s="590"/>
+      <c r="C186" s="343"/>
+      <c r="D186" s="343"/>
+      <c r="E186" s="343"/>
+      <c r="F186" s="343"/>
+      <c r="G186" s="343"/>
+      <c r="H186" s="343"/>
+      <c r="J186" s="342"/>
+      <c r="K186" s="342"/>
+      <c r="L186" s="342"/>
+      <c r="M186" s="342"/>
+      <c r="N186" s="342"/>
       <c r="O186" s="39"/>
     </row>
     <row r="187" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C187" s="589"/>
-      <c r="D187" s="589"/>
-      <c r="E187" s="589"/>
-      <c r="F187" s="589"/>
-      <c r="G187" s="589"/>
-      <c r="H187" s="589"/>
-      <c r="J187" s="590"/>
-      <c r="K187" s="590"/>
-      <c r="L187" s="590"/>
-      <c r="M187" s="590"/>
-      <c r="N187" s="590"/>
+      <c r="C187" s="343"/>
+      <c r="D187" s="343"/>
+      <c r="E187" s="343"/>
+      <c r="F187" s="343"/>
+      <c r="G187" s="343"/>
+      <c r="H187" s="343"/>
+      <c r="J187" s="342"/>
+      <c r="K187" s="342"/>
+      <c r="L187" s="342"/>
+      <c r="M187" s="342"/>
+      <c r="N187" s="342"/>
       <c r="O187" s="39"/>
     </row>
     <row r="188" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C188" s="589"/>
-      <c r="D188" s="589"/>
-      <c r="E188" s="589"/>
-      <c r="F188" s="589"/>
-      <c r="G188" s="589"/>
-      <c r="H188" s="589"/>
-      <c r="J188" s="590"/>
-      <c r="K188" s="590"/>
-      <c r="L188" s="590"/>
-      <c r="M188" s="590"/>
-      <c r="N188" s="590"/>
+      <c r="C188" s="343"/>
+      <c r="D188" s="343"/>
+      <c r="E188" s="343"/>
+      <c r="F188" s="343"/>
+      <c r="G188" s="343"/>
+      <c r="H188" s="343"/>
+      <c r="J188" s="342"/>
+      <c r="K188" s="342"/>
+      <c r="L188" s="342"/>
+      <c r="M188" s="342"/>
+      <c r="N188" s="342"/>
       <c r="O188" s="39"/>
     </row>
     <row r="189" spans="3:15" ht="24" x14ac:dyDescent="0.15">
-      <c r="C189" s="589"/>
-      <c r="D189" s="589"/>
-      <c r="E189" s="589"/>
-      <c r="F189" s="589"/>
-      <c r="G189" s="589"/>
-      <c r="H189" s="589"/>
-      <c r="J189" s="590"/>
-      <c r="K189" s="590"/>
-      <c r="L189" s="590"/>
-      <c r="M189" s="590"/>
-      <c r="N189" s="590"/>
+      <c r="C189" s="343"/>
+      <c r="D189" s="343"/>
+      <c r="E189" s="343"/>
+      <c r="F189" s="343"/>
+      <c r="G189" s="343"/>
+      <c r="H189" s="343"/>
+      <c r="J189" s="342"/>
+      <c r="K189" s="342"/>
+      <c r="L189" s="342"/>
+      <c r="M189" s="342"/>
+      <c r="N189" s="342"/>
       <c r="O189" s="39"/>
     </row>
     <row r="190" spans="3:15" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="J190" s="590"/>
-      <c r="K190" s="590"/>
-      <c r="L190" s="590"/>
-      <c r="M190" s="590"/>
-      <c r="N190" s="590"/>
+      <c r="J190" s="342"/>
+      <c r="K190" s="342"/>
+      <c r="L190" s="342"/>
+      <c r="M190" s="342"/>
+      <c r="N190" s="342"/>
       <c r="O190" s="39"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="313">
-    <mergeCell ref="J85:N85"/>
-    <mergeCell ref="J88:O88"/>
-    <mergeCell ref="J89:O89"/>
-    <mergeCell ref="J82:N82"/>
-    <mergeCell ref="J81:N81"/>
-    <mergeCell ref="J61:N61"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="K56:M56"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="K57:M57"/>
-    <mergeCell ref="O57:P57"/>
-    <mergeCell ref="J97:N97"/>
-    <mergeCell ref="J96:N96"/>
-    <mergeCell ref="J86:N86"/>
-    <mergeCell ref="J87:N87"/>
-    <mergeCell ref="J91:O91"/>
-    <mergeCell ref="J90:O90"/>
-    <mergeCell ref="C108:H108"/>
-    <mergeCell ref="C102:H102"/>
-    <mergeCell ref="C105:H105"/>
-    <mergeCell ref="C103:H103"/>
-    <mergeCell ref="C104:H104"/>
-    <mergeCell ref="J99:N99"/>
-    <mergeCell ref="J100:N100"/>
-    <mergeCell ref="C106:H106"/>
-    <mergeCell ref="J92:O92"/>
-    <mergeCell ref="J93:O93"/>
-    <mergeCell ref="J95:N95"/>
-    <mergeCell ref="J94:N94"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="Q43:R43"/>
+    <mergeCell ref="Q44:R44"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="Q51:R51"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="Q42:R42"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="J3:P3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="K55:M55"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J44:N44"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="J53:P53"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B10:B24"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="J38:L38"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="J62:N62"/>
+    <mergeCell ref="B59:P59"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="O54:P54"/>
+    <mergeCell ref="O55:P55"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="L51:N51"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="C189:H189"/>
+    <mergeCell ref="J161:N161"/>
+    <mergeCell ref="C169:H169"/>
+    <mergeCell ref="C167:H167"/>
+    <mergeCell ref="C188:H188"/>
+    <mergeCell ref="C185:H185"/>
+    <mergeCell ref="C181:H181"/>
+    <mergeCell ref="C182:H182"/>
+    <mergeCell ref="C148:H148"/>
+    <mergeCell ref="C187:H187"/>
+    <mergeCell ref="C151:H151"/>
+    <mergeCell ref="C149:H149"/>
+    <mergeCell ref="J173:N173"/>
+    <mergeCell ref="J150:N150"/>
+    <mergeCell ref="C158:H158"/>
+    <mergeCell ref="C150:H150"/>
+    <mergeCell ref="J153:N153"/>
+    <mergeCell ref="C153:H153"/>
+    <mergeCell ref="J172:N172"/>
+    <mergeCell ref="C184:H184"/>
+    <mergeCell ref="C174:H174"/>
+    <mergeCell ref="C186:H186"/>
+    <mergeCell ref="C175:H175"/>
+    <mergeCell ref="C180:H180"/>
+    <mergeCell ref="J190:N190"/>
+    <mergeCell ref="J170:N170"/>
+    <mergeCell ref="J176:N176"/>
+    <mergeCell ref="J160:N160"/>
+    <mergeCell ref="J182:N182"/>
+    <mergeCell ref="J183:N183"/>
+    <mergeCell ref="J184:N184"/>
+    <mergeCell ref="J185:N185"/>
+    <mergeCell ref="J186:N186"/>
+    <mergeCell ref="J187:N187"/>
+    <mergeCell ref="J174:N174"/>
+    <mergeCell ref="J162:N162"/>
+    <mergeCell ref="J180:N180"/>
+    <mergeCell ref="J177:N177"/>
+    <mergeCell ref="J168:N168"/>
+    <mergeCell ref="J175:N175"/>
+    <mergeCell ref="J188:N188"/>
+    <mergeCell ref="J181:N181"/>
+    <mergeCell ref="J171:N171"/>
+    <mergeCell ref="J179:N179"/>
+    <mergeCell ref="J166:N166"/>
+    <mergeCell ref="J178:N178"/>
+    <mergeCell ref="J189:N189"/>
+    <mergeCell ref="J163:N163"/>
+    <mergeCell ref="C183:H183"/>
+    <mergeCell ref="C179:H179"/>
+    <mergeCell ref="J164:N164"/>
+    <mergeCell ref="C166:H166"/>
+    <mergeCell ref="C168:H168"/>
+    <mergeCell ref="C173:H173"/>
+    <mergeCell ref="C172:H172"/>
+    <mergeCell ref="C171:H171"/>
+    <mergeCell ref="C164:H164"/>
+    <mergeCell ref="C170:H170"/>
+    <mergeCell ref="C178:H178"/>
+    <mergeCell ref="J165:N165"/>
+    <mergeCell ref="J167:N167"/>
+    <mergeCell ref="J169:N169"/>
+    <mergeCell ref="C176:H176"/>
+    <mergeCell ref="C177:H177"/>
+    <mergeCell ref="C165:H165"/>
+    <mergeCell ref="J143:N143"/>
+    <mergeCell ref="C144:H144"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="C145:H145"/>
+    <mergeCell ref="J145:N145"/>
+    <mergeCell ref="J144:N144"/>
+    <mergeCell ref="J156:N156"/>
+    <mergeCell ref="J151:N151"/>
+    <mergeCell ref="J155:N155"/>
+    <mergeCell ref="C154:H154"/>
+    <mergeCell ref="J149:N149"/>
+    <mergeCell ref="C121:H121"/>
+    <mergeCell ref="C139:H139"/>
+    <mergeCell ref="J127:N127"/>
+    <mergeCell ref="C130:H130"/>
+    <mergeCell ref="C129:H129"/>
+    <mergeCell ref="C141:H141"/>
+    <mergeCell ref="J131:N131"/>
+    <mergeCell ref="C157:H157"/>
+    <mergeCell ref="C155:H155"/>
+    <mergeCell ref="C156:H156"/>
+    <mergeCell ref="C146:H146"/>
+    <mergeCell ref="J147:N147"/>
+    <mergeCell ref="C152:H152"/>
+    <mergeCell ref="C147:H147"/>
+    <mergeCell ref="J134:N134"/>
+    <mergeCell ref="C142:H142"/>
+    <mergeCell ref="C136:H136"/>
+    <mergeCell ref="C140:H140"/>
+    <mergeCell ref="C134:H134"/>
+    <mergeCell ref="C135:H135"/>
+    <mergeCell ref="C138:H138"/>
+    <mergeCell ref="C128:H128"/>
+    <mergeCell ref="J148:N148"/>
+    <mergeCell ref="J146:N146"/>
+    <mergeCell ref="C160:H160"/>
+    <mergeCell ref="C163:H163"/>
+    <mergeCell ref="C162:H162"/>
+    <mergeCell ref="C161:H161"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="J130:N130"/>
+    <mergeCell ref="J142:N142"/>
+    <mergeCell ref="J138:N138"/>
+    <mergeCell ref="J141:N141"/>
+    <mergeCell ref="J133:N133"/>
+    <mergeCell ref="J132:N132"/>
+    <mergeCell ref="J135:N135"/>
+    <mergeCell ref="C132:H132"/>
+    <mergeCell ref="J137:N137"/>
+    <mergeCell ref="J140:N140"/>
+    <mergeCell ref="J136:N136"/>
+    <mergeCell ref="C137:H137"/>
+    <mergeCell ref="J139:N139"/>
+    <mergeCell ref="J159:N159"/>
+    <mergeCell ref="J158:N158"/>
+    <mergeCell ref="J157:N157"/>
+    <mergeCell ref="J152:N152"/>
+    <mergeCell ref="J154:N154"/>
+    <mergeCell ref="C159:H159"/>
+    <mergeCell ref="C131:H131"/>
+    <mergeCell ref="C133:H133"/>
+    <mergeCell ref="J129:N129"/>
+    <mergeCell ref="J126:N126"/>
+    <mergeCell ref="J125:N125"/>
+    <mergeCell ref="J122:N122"/>
+    <mergeCell ref="J118:N118"/>
+    <mergeCell ref="J114:N114"/>
+    <mergeCell ref="J117:N117"/>
+    <mergeCell ref="J128:N128"/>
+    <mergeCell ref="C125:H125"/>
+    <mergeCell ref="C124:H124"/>
+    <mergeCell ref="C122:H122"/>
+    <mergeCell ref="J123:N123"/>
+    <mergeCell ref="J121:N121"/>
+    <mergeCell ref="C115:H115"/>
+    <mergeCell ref="C114:H114"/>
+    <mergeCell ref="C127:H127"/>
+    <mergeCell ref="J124:N124"/>
+    <mergeCell ref="C118:H118"/>
+    <mergeCell ref="J116:N116"/>
+    <mergeCell ref="C116:H116"/>
+    <mergeCell ref="J119:N119"/>
+    <mergeCell ref="C123:H123"/>
     <mergeCell ref="J115:N115"/>
     <mergeCell ref="J120:N120"/>
     <mergeCell ref="J103:N103"/>
@@ -8780,262 +9001,39 @@
     <mergeCell ref="C119:H119"/>
     <mergeCell ref="C113:H113"/>
     <mergeCell ref="C110:H110"/>
-    <mergeCell ref="C131:H131"/>
-    <mergeCell ref="C133:H133"/>
-    <mergeCell ref="J129:N129"/>
-    <mergeCell ref="J126:N126"/>
-    <mergeCell ref="J125:N125"/>
-    <mergeCell ref="J122:N122"/>
-    <mergeCell ref="J118:N118"/>
-    <mergeCell ref="J114:N114"/>
-    <mergeCell ref="J117:N117"/>
-    <mergeCell ref="J128:N128"/>
-    <mergeCell ref="C125:H125"/>
-    <mergeCell ref="C124:H124"/>
-    <mergeCell ref="C122:H122"/>
-    <mergeCell ref="J123:N123"/>
-    <mergeCell ref="J121:N121"/>
-    <mergeCell ref="C115:H115"/>
-    <mergeCell ref="C114:H114"/>
-    <mergeCell ref="C127:H127"/>
-    <mergeCell ref="J124:N124"/>
-    <mergeCell ref="C118:H118"/>
-    <mergeCell ref="J116:N116"/>
-    <mergeCell ref="C116:H116"/>
-    <mergeCell ref="J119:N119"/>
-    <mergeCell ref="C123:H123"/>
-    <mergeCell ref="C160:H160"/>
-    <mergeCell ref="C163:H163"/>
-    <mergeCell ref="C162:H162"/>
-    <mergeCell ref="C161:H161"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="J130:N130"/>
-    <mergeCell ref="J142:N142"/>
-    <mergeCell ref="J138:N138"/>
-    <mergeCell ref="J141:N141"/>
-    <mergeCell ref="J133:N133"/>
-    <mergeCell ref="J132:N132"/>
-    <mergeCell ref="J135:N135"/>
-    <mergeCell ref="C132:H132"/>
-    <mergeCell ref="J137:N137"/>
-    <mergeCell ref="J140:N140"/>
-    <mergeCell ref="J136:N136"/>
-    <mergeCell ref="C137:H137"/>
-    <mergeCell ref="J139:N139"/>
-    <mergeCell ref="J159:N159"/>
-    <mergeCell ref="J158:N158"/>
-    <mergeCell ref="J157:N157"/>
-    <mergeCell ref="J152:N152"/>
-    <mergeCell ref="J154:N154"/>
-    <mergeCell ref="C159:H159"/>
-    <mergeCell ref="C121:H121"/>
-    <mergeCell ref="C139:H139"/>
-    <mergeCell ref="J127:N127"/>
-    <mergeCell ref="C130:H130"/>
-    <mergeCell ref="C129:H129"/>
-    <mergeCell ref="C141:H141"/>
-    <mergeCell ref="J131:N131"/>
-    <mergeCell ref="C157:H157"/>
-    <mergeCell ref="C155:H155"/>
-    <mergeCell ref="C156:H156"/>
-    <mergeCell ref="C146:H146"/>
-    <mergeCell ref="J147:N147"/>
-    <mergeCell ref="C152:H152"/>
-    <mergeCell ref="C147:H147"/>
-    <mergeCell ref="J134:N134"/>
-    <mergeCell ref="C142:H142"/>
-    <mergeCell ref="C136:H136"/>
-    <mergeCell ref="C140:H140"/>
-    <mergeCell ref="C134:H134"/>
-    <mergeCell ref="C135:H135"/>
-    <mergeCell ref="C138:H138"/>
-    <mergeCell ref="C128:H128"/>
-    <mergeCell ref="J148:N148"/>
-    <mergeCell ref="J146:N146"/>
-    <mergeCell ref="J143:N143"/>
-    <mergeCell ref="C144:H144"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="C145:H145"/>
-    <mergeCell ref="J145:N145"/>
-    <mergeCell ref="J144:N144"/>
-    <mergeCell ref="J156:N156"/>
-    <mergeCell ref="J151:N151"/>
-    <mergeCell ref="J155:N155"/>
-    <mergeCell ref="C154:H154"/>
-    <mergeCell ref="J149:N149"/>
-    <mergeCell ref="C183:H183"/>
-    <mergeCell ref="C179:H179"/>
-    <mergeCell ref="J164:N164"/>
-    <mergeCell ref="C166:H166"/>
-    <mergeCell ref="C168:H168"/>
-    <mergeCell ref="C173:H173"/>
-    <mergeCell ref="C172:H172"/>
-    <mergeCell ref="C171:H171"/>
-    <mergeCell ref="C164:H164"/>
-    <mergeCell ref="C170:H170"/>
-    <mergeCell ref="C178:H178"/>
-    <mergeCell ref="J165:N165"/>
-    <mergeCell ref="J167:N167"/>
-    <mergeCell ref="J169:N169"/>
-    <mergeCell ref="C176:H176"/>
-    <mergeCell ref="C177:H177"/>
-    <mergeCell ref="C165:H165"/>
-    <mergeCell ref="J190:N190"/>
-    <mergeCell ref="J170:N170"/>
-    <mergeCell ref="J176:N176"/>
-    <mergeCell ref="J160:N160"/>
-    <mergeCell ref="J182:N182"/>
-    <mergeCell ref="J183:N183"/>
-    <mergeCell ref="J184:N184"/>
-    <mergeCell ref="J185:N185"/>
-    <mergeCell ref="J186:N186"/>
-    <mergeCell ref="J187:N187"/>
-    <mergeCell ref="J174:N174"/>
-    <mergeCell ref="J162:N162"/>
-    <mergeCell ref="J180:N180"/>
-    <mergeCell ref="J177:N177"/>
-    <mergeCell ref="J168:N168"/>
-    <mergeCell ref="J175:N175"/>
-    <mergeCell ref="J188:N188"/>
-    <mergeCell ref="J181:N181"/>
-    <mergeCell ref="J171:N171"/>
-    <mergeCell ref="J179:N179"/>
-    <mergeCell ref="J166:N166"/>
-    <mergeCell ref="J178:N178"/>
-    <mergeCell ref="J189:N189"/>
-    <mergeCell ref="J163:N163"/>
-    <mergeCell ref="C189:H189"/>
-    <mergeCell ref="J161:N161"/>
-    <mergeCell ref="C169:H169"/>
-    <mergeCell ref="C167:H167"/>
-    <mergeCell ref="C188:H188"/>
-    <mergeCell ref="C185:H185"/>
-    <mergeCell ref="C181:H181"/>
-    <mergeCell ref="C182:H182"/>
-    <mergeCell ref="C148:H148"/>
-    <mergeCell ref="C187:H187"/>
-    <mergeCell ref="C151:H151"/>
-    <mergeCell ref="C149:H149"/>
-    <mergeCell ref="J173:N173"/>
-    <mergeCell ref="J150:N150"/>
-    <mergeCell ref="C158:H158"/>
-    <mergeCell ref="C150:H150"/>
-    <mergeCell ref="J153:N153"/>
-    <mergeCell ref="C153:H153"/>
-    <mergeCell ref="J172:N172"/>
-    <mergeCell ref="C184:H184"/>
-    <mergeCell ref="C174:H174"/>
-    <mergeCell ref="C186:H186"/>
-    <mergeCell ref="C175:H175"/>
-    <mergeCell ref="C180:H180"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B10:B24"/>
-    <mergeCell ref="C62:F62"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="J38:L38"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="J62:N62"/>
-    <mergeCell ref="B59:P59"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="O54:P54"/>
-    <mergeCell ref="O55:P55"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="L51:N51"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="K55:M55"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="J44:N44"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="J53:P53"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="C1:J1"/>
-    <mergeCell ref="J3:P3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="Q43:R43"/>
-    <mergeCell ref="Q44:R44"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="Q51:R51"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="Q42:R42"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="J97:N97"/>
+    <mergeCell ref="J96:N96"/>
+    <mergeCell ref="J86:N86"/>
+    <mergeCell ref="J87:N87"/>
+    <mergeCell ref="J91:O91"/>
+    <mergeCell ref="J90:O90"/>
+    <mergeCell ref="C108:H108"/>
+    <mergeCell ref="C102:H102"/>
+    <mergeCell ref="C105:H105"/>
+    <mergeCell ref="C103:H103"/>
+    <mergeCell ref="C104:H104"/>
+    <mergeCell ref="J99:N99"/>
+    <mergeCell ref="J100:N100"/>
+    <mergeCell ref="C106:H106"/>
+    <mergeCell ref="J92:O92"/>
+    <mergeCell ref="J93:O93"/>
+    <mergeCell ref="J95:N95"/>
+    <mergeCell ref="J94:N94"/>
+    <mergeCell ref="J85:N85"/>
+    <mergeCell ref="J88:O88"/>
+    <mergeCell ref="J89:O89"/>
+    <mergeCell ref="J82:N82"/>
+    <mergeCell ref="J81:N81"/>
+    <mergeCell ref="J61:N61"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="K56:M56"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="K57:M57"/>
+    <mergeCell ref="O57:P57"/>
   </mergeCells>
   <phoneticPr fontId="38" alignment="center"/>
   <conditionalFormatting sqref="A1:A51 A59:A60">
@@ -9122,204 +9120,204 @@
   <sheetData>
     <row r="1" spans="1:31" ht="21.75" x14ac:dyDescent="0.25">
       <c r="A1" s="211"/>
-      <c r="B1" s="335" t="s">
+      <c r="B1" s="570" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="335"/>
-      <c r="D1" s="335"/>
-      <c r="E1" s="335"/>
-      <c r="F1" s="335"/>
-      <c r="G1" s="335"/>
-      <c r="H1" s="335"/>
-      <c r="I1" s="335"/>
-      <c r="J1" s="335"/>
-      <c r="K1" s="335"/>
-      <c r="L1" s="335"/>
-      <c r="M1" s="335"/>
-      <c r="N1" s="335"/>
-      <c r="O1" s="335"/>
-      <c r="P1" s="335"/>
-      <c r="Q1" s="335"/>
-      <c r="R1" s="335"/>
-      <c r="S1" s="335"/>
-      <c r="T1" s="335"/>
-      <c r="U1" s="335"/>
-      <c r="V1" s="335"/>
-      <c r="W1" s="335"/>
-      <c r="X1" s="335"/>
+      <c r="C1" s="570"/>
+      <c r="D1" s="570"/>
+      <c r="E1" s="570"/>
+      <c r="F1" s="570"/>
+      <c r="G1" s="570"/>
+      <c r="H1" s="570"/>
+      <c r="I1" s="570"/>
+      <c r="J1" s="570"/>
+      <c r="K1" s="570"/>
+      <c r="L1" s="570"/>
+      <c r="M1" s="570"/>
+      <c r="N1" s="570"/>
+      <c r="O1" s="570"/>
+      <c r="P1" s="570"/>
+      <c r="Q1" s="570"/>
+      <c r="R1" s="570"/>
+      <c r="S1" s="570"/>
+      <c r="T1" s="570"/>
+      <c r="U1" s="570"/>
+      <c r="V1" s="570"/>
+      <c r="W1" s="570"/>
+      <c r="X1" s="570"/>
       <c r="Y1" s="212"/>
       <c r="Z1" s="212"/>
       <c r="AA1" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="336" t="s">
+      <c r="AB1" s="571" t="s">
         <v>223</v>
       </c>
-      <c r="AC1" s="336"/>
-      <c r="AD1" s="336"/>
-      <c r="AE1" s="336"/>
+      <c r="AC1" s="571"/>
+      <c r="AD1" s="571"/>
+      <c r="AE1" s="571"/>
     </row>
     <row r="2" spans="1:31" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="337" t="s">
+      <c r="A2" s="559" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="340" t="s">
+      <c r="B2" s="573" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="341"/>
-      <c r="D2" s="341"/>
-      <c r="E2" s="341"/>
-      <c r="F2" s="341"/>
-      <c r="G2" s="341"/>
-      <c r="H2" s="341"/>
-      <c r="I2" s="341"/>
-      <c r="J2" s="341"/>
-      <c r="K2" s="341"/>
-      <c r="L2" s="341"/>
-      <c r="M2" s="341"/>
-      <c r="N2" s="341"/>
-      <c r="O2" s="341"/>
-      <c r="P2" s="341"/>
-      <c r="Q2" s="341"/>
-      <c r="R2" s="341"/>
-      <c r="S2" s="341"/>
-      <c r="T2" s="341"/>
-      <c r="U2" s="341"/>
-      <c r="V2" s="341"/>
-      <c r="W2" s="342"/>
-      <c r="X2" s="343"/>
-      <c r="Y2" s="344"/>
-      <c r="Z2" s="344"/>
-      <c r="AA2" s="344"/>
-      <c r="AB2" s="344"/>
-      <c r="AC2" s="344"/>
-      <c r="AD2" s="345"/>
-      <c r="AE2" s="346" t="s">
+      <c r="C2" s="574"/>
+      <c r="D2" s="574"/>
+      <c r="E2" s="574"/>
+      <c r="F2" s="574"/>
+      <c r="G2" s="574"/>
+      <c r="H2" s="574"/>
+      <c r="I2" s="574"/>
+      <c r="J2" s="574"/>
+      <c r="K2" s="574"/>
+      <c r="L2" s="574"/>
+      <c r="M2" s="574"/>
+      <c r="N2" s="574"/>
+      <c r="O2" s="574"/>
+      <c r="P2" s="574"/>
+      <c r="Q2" s="574"/>
+      <c r="R2" s="574"/>
+      <c r="S2" s="574"/>
+      <c r="T2" s="574"/>
+      <c r="U2" s="574"/>
+      <c r="V2" s="574"/>
+      <c r="W2" s="575"/>
+      <c r="X2" s="576"/>
+      <c r="Y2" s="577"/>
+      <c r="Z2" s="577"/>
+      <c r="AA2" s="577"/>
+      <c r="AB2" s="577"/>
+      <c r="AC2" s="577"/>
+      <c r="AD2" s="578"/>
+      <c r="AE2" s="579" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="338"/>
-      <c r="B3" s="349" t="s">
+      <c r="A3" s="572"/>
+      <c r="B3" s="556" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="350"/>
-      <c r="D3" s="351"/>
-      <c r="E3" s="349" t="s">
+      <c r="C3" s="558"/>
+      <c r="D3" s="557"/>
+      <c r="E3" s="556" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="J3" s="350"/>
-      <c r="K3" s="350"/>
-      <c r="L3" s="350"/>
-      <c r="M3" s="350"/>
-      <c r="N3" s="350"/>
-      <c r="O3" s="350"/>
-      <c r="P3" s="350"/>
-      <c r="Q3" s="350"/>
-      <c r="R3" s="351"/>
+      <c r="F3" s="558"/>
+      <c r="G3" s="558"/>
+      <c r="H3" s="558"/>
+      <c r="I3" s="558"/>
+      <c r="J3" s="558"/>
+      <c r="K3" s="558"/>
+      <c r="L3" s="558"/>
+      <c r="M3" s="558"/>
+      <c r="N3" s="558"/>
+      <c r="O3" s="558"/>
+      <c r="P3" s="558"/>
+      <c r="Q3" s="558"/>
+      <c r="R3" s="557"/>
       <c r="S3" s="225"/>
       <c r="T3" s="225"/>
-      <c r="U3" s="352" t="s">
+      <c r="U3" s="582" t="s">
         <v>62</v>
       </c>
-      <c r="V3" s="353"/>
-      <c r="W3" s="354"/>
-      <c r="X3" s="361" t="s">
+      <c r="V3" s="583"/>
+      <c r="W3" s="584"/>
+      <c r="X3" s="591" t="s">
         <v>64</v>
       </c>
-      <c r="Y3" s="362"/>
-      <c r="Z3" s="362"/>
-      <c r="AA3" s="363"/>
-      <c r="AB3" s="361" t="s">
+      <c r="Y3" s="592"/>
+      <c r="Z3" s="592"/>
+      <c r="AA3" s="593"/>
+      <c r="AB3" s="591" t="s">
         <v>65</v>
       </c>
-      <c r="AC3" s="362"/>
-      <c r="AD3" s="363"/>
-      <c r="AE3" s="347"/>
+      <c r="AC3" s="592"/>
+      <c r="AD3" s="593"/>
+      <c r="AE3" s="580"/>
     </row>
     <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="338"/>
-      <c r="B4" s="337" t="s">
+      <c r="A4" s="572"/>
+      <c r="B4" s="559" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="337" t="s">
+      <c r="C4" s="559" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="337" t="s">
+      <c r="D4" s="559" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="349" t="s">
+      <c r="E4" s="556" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="350"/>
-      <c r="G4" s="350"/>
-      <c r="H4" s="350"/>
-      <c r="I4" s="350"/>
-      <c r="J4" s="350"/>
-      <c r="K4" s="350"/>
-      <c r="L4" s="350"/>
-      <c r="M4" s="351"/>
-      <c r="N4" s="349"/>
-      <c r="O4" s="350"/>
-      <c r="P4" s="350"/>
-      <c r="Q4" s="350"/>
-      <c r="R4" s="351"/>
+      <c r="F4" s="558"/>
+      <c r="G4" s="558"/>
+      <c r="H4" s="558"/>
+      <c r="I4" s="558"/>
+      <c r="J4" s="558"/>
+      <c r="K4" s="558"/>
+      <c r="L4" s="558"/>
+      <c r="M4" s="557"/>
+      <c r="N4" s="556"/>
+      <c r="O4" s="558"/>
+      <c r="P4" s="558"/>
+      <c r="Q4" s="558"/>
+      <c r="R4" s="557"/>
       <c r="S4" s="226"/>
       <c r="T4" s="226"/>
-      <c r="U4" s="355"/>
-      <c r="V4" s="356"/>
-      <c r="W4" s="357"/>
-      <c r="X4" s="364" t="s">
+      <c r="U4" s="585"/>
+      <c r="V4" s="586"/>
+      <c r="W4" s="587"/>
+      <c r="X4" s="561" t="s">
         <v>31</v>
       </c>
-      <c r="Y4" s="365"/>
-      <c r="Z4" s="366"/>
-      <c r="AA4" s="370" t="s">
+      <c r="Y4" s="562"/>
+      <c r="Z4" s="563"/>
+      <c r="AA4" s="567" t="s">
         <v>32</v>
       </c>
-      <c r="AB4" s="370" t="s">
+      <c r="AB4" s="567" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="370" t="s">
+      <c r="AC4" s="567" t="s">
         <v>84</v>
       </c>
-      <c r="AD4" s="370" t="s">
+      <c r="AD4" s="567" t="s">
         <v>32</v>
       </c>
-      <c r="AE4" s="347"/>
+      <c r="AE4" s="580"/>
     </row>
     <row r="5" spans="1:31" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="338"/>
-      <c r="B5" s="338"/>
-      <c r="C5" s="338"/>
-      <c r="D5" s="338"/>
-      <c r="E5" s="349" t="s">
+      <c r="A5" s="572"/>
+      <c r="B5" s="572"/>
+      <c r="C5" s="572"/>
+      <c r="D5" s="572"/>
+      <c r="E5" s="556" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="351"/>
-      <c r="G5" s="349" t="s">
+      <c r="F5" s="557"/>
+      <c r="G5" s="556" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="351"/>
-      <c r="I5" s="349" t="s">
+      <c r="H5" s="557"/>
+      <c r="I5" s="556" t="s">
         <v>69</v>
       </c>
-      <c r="J5" s="350"/>
-      <c r="K5" s="351"/>
+      <c r="J5" s="558"/>
+      <c r="K5" s="557"/>
       <c r="L5" s="227" t="s">
         <v>88</v>
       </c>
-      <c r="M5" s="337" t="s">
+      <c r="M5" s="559" t="s">
         <v>35</v>
       </c>
-      <c r="N5" s="349"/>
-      <c r="O5" s="350"/>
-      <c r="P5" s="350"/>
-      <c r="Q5" s="351"/>
+      <c r="N5" s="556"/>
+      <c r="O5" s="558"/>
+      <c r="P5" s="558"/>
+      <c r="Q5" s="557"/>
       <c r="R5" s="228" t="s">
         <v>47</v>
       </c>
@@ -9329,23 +9327,23 @@
       <c r="T5" s="228" t="s">
         <v>76</v>
       </c>
-      <c r="U5" s="358"/>
-      <c r="V5" s="359"/>
-      <c r="W5" s="360"/>
-      <c r="X5" s="367"/>
-      <c r="Y5" s="368"/>
-      <c r="Z5" s="369"/>
-      <c r="AA5" s="371"/>
-      <c r="AB5" s="371"/>
-      <c r="AC5" s="371"/>
-      <c r="AD5" s="371"/>
-      <c r="AE5" s="347"/>
+      <c r="U5" s="588"/>
+      <c r="V5" s="589"/>
+      <c r="W5" s="590"/>
+      <c r="X5" s="564"/>
+      <c r="Y5" s="565"/>
+      <c r="Z5" s="566"/>
+      <c r="AA5" s="568"/>
+      <c r="AB5" s="568"/>
+      <c r="AC5" s="568"/>
+      <c r="AD5" s="568"/>
+      <c r="AE5" s="580"/>
     </row>
     <row r="6" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="339"/>
-      <c r="B6" s="339"/>
-      <c r="C6" s="339"/>
-      <c r="D6" s="339"/>
+      <c r="A6" s="560"/>
+      <c r="B6" s="560"/>
+      <c r="C6" s="560"/>
+      <c r="D6" s="560"/>
       <c r="E6" s="228" t="s">
         <v>61</v>
       </c>
@@ -9370,7 +9368,7 @@
       <c r="L6" s="228" t="s">
         <v>77</v>
       </c>
-      <c r="M6" s="339"/>
+      <c r="M6" s="560"/>
       <c r="N6" s="228" t="s">
         <v>36</v>
       </c>
@@ -9410,11 +9408,11 @@
       <c r="Z6" s="230" t="s">
         <v>153</v>
       </c>
-      <c r="AA6" s="372"/>
-      <c r="AB6" s="372"/>
-      <c r="AC6" s="372"/>
-      <c r="AD6" s="372"/>
-      <c r="AE6" s="348"/>
+      <c r="AA6" s="569"/>
+      <c r="AB6" s="569"/>
+      <c r="AC6" s="569"/>
+      <c r="AD6" s="569"/>
+      <c r="AE6" s="581"/>
     </row>
     <row r="7" spans="1:31" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="236">
@@ -10047,205 +10045,205 @@
       </c>
     </row>
     <row r="13" spans="1:31" ht="21.75" x14ac:dyDescent="0.15">
-      <c r="A13" s="373" t="s">
+      <c r="A13" s="537" t="s">
         <v>187</v>
       </c>
-      <c r="B13" s="373"/>
-      <c r="C13" s="373"/>
-      <c r="D13" s="373"/>
-      <c r="E13" s="373"/>
-      <c r="F13" s="373"/>
-      <c r="G13" s="373"/>
-      <c r="H13" s="373"/>
-      <c r="I13" s="373"/>
-      <c r="J13" s="373"/>
-      <c r="K13" s="373"/>
-      <c r="L13" s="373"/>
-      <c r="M13" s="373"/>
-      <c r="N13" s="373"/>
-      <c r="O13" s="373"/>
-      <c r="P13" s="373"/>
-      <c r="Q13" s="373"/>
-      <c r="R13" s="373"/>
-      <c r="S13" s="373"/>
-      <c r="T13" s="373"/>
-      <c r="U13" s="373"/>
-      <c r="V13" s="373"/>
-      <c r="W13" s="373"/>
-      <c r="X13" s="373"/>
-      <c r="Y13" s="373"/>
-      <c r="Z13" s="373"/>
-      <c r="AA13" s="373"/>
-      <c r="AB13" s="373"/>
-      <c r="AC13" s="373"/>
-      <c r="AD13" s="373"/>
-      <c r="AE13" s="373"/>
+      <c r="B13" s="537"/>
+      <c r="C13" s="537"/>
+      <c r="D13" s="537"/>
+      <c r="E13" s="537"/>
+      <c r="F13" s="537"/>
+      <c r="G13" s="537"/>
+      <c r="H13" s="537"/>
+      <c r="I13" s="537"/>
+      <c r="J13" s="537"/>
+      <c r="K13" s="537"/>
+      <c r="L13" s="537"/>
+      <c r="M13" s="537"/>
+      <c r="N13" s="537"/>
+      <c r="O13" s="537"/>
+      <c r="P13" s="537"/>
+      <c r="Q13" s="537"/>
+      <c r="R13" s="537"/>
+      <c r="S13" s="537"/>
+      <c r="T13" s="537"/>
+      <c r="U13" s="537"/>
+      <c r="V13" s="537"/>
+      <c r="W13" s="537"/>
+      <c r="X13" s="537"/>
+      <c r="Y13" s="537"/>
+      <c r="Z13" s="537"/>
+      <c r="AA13" s="537"/>
+      <c r="AB13" s="537"/>
+      <c r="AC13" s="537"/>
+      <c r="AD13" s="537"/>
+      <c r="AE13" s="537"/>
     </row>
     <row r="14" spans="1:31" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="374" t="s">
+      <c r="A14" s="525" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="377" t="s">
+      <c r="B14" s="538" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="378"/>
-      <c r="D14" s="378"/>
-      <c r="E14" s="378"/>
-      <c r="F14" s="378"/>
-      <c r="G14" s="378"/>
-      <c r="H14" s="378"/>
-      <c r="I14" s="378"/>
-      <c r="J14" s="378"/>
-      <c r="K14" s="378"/>
-      <c r="L14" s="378"/>
-      <c r="M14" s="378"/>
-      <c r="N14" s="378"/>
-      <c r="O14" s="378"/>
-      <c r="P14" s="378"/>
-      <c r="Q14" s="378"/>
-      <c r="R14" s="378"/>
-      <c r="S14" s="378"/>
-      <c r="T14" s="378"/>
-      <c r="U14" s="378"/>
-      <c r="V14" s="378"/>
-      <c r="W14" s="379"/>
-      <c r="X14" s="377" t="s">
+      <c r="C14" s="539"/>
+      <c r="D14" s="539"/>
+      <c r="E14" s="539"/>
+      <c r="F14" s="539"/>
+      <c r="G14" s="539"/>
+      <c r="H14" s="539"/>
+      <c r="I14" s="539"/>
+      <c r="J14" s="539"/>
+      <c r="K14" s="539"/>
+      <c r="L14" s="539"/>
+      <c r="M14" s="539"/>
+      <c r="N14" s="539"/>
+      <c r="O14" s="539"/>
+      <c r="P14" s="539"/>
+      <c r="Q14" s="539"/>
+      <c r="R14" s="539"/>
+      <c r="S14" s="539"/>
+      <c r="T14" s="539"/>
+      <c r="U14" s="539"/>
+      <c r="V14" s="539"/>
+      <c r="W14" s="540"/>
+      <c r="X14" s="538" t="s">
         <v>27</v>
       </c>
-      <c r="Y14" s="378"/>
-      <c r="Z14" s="378"/>
-      <c r="AA14" s="378"/>
-      <c r="AB14" s="378"/>
-      <c r="AC14" s="378"/>
-      <c r="AD14" s="379"/>
-      <c r="AE14" s="380" t="s">
+      <c r="Y14" s="539"/>
+      <c r="Z14" s="539"/>
+      <c r="AA14" s="539"/>
+      <c r="AB14" s="539"/>
+      <c r="AC14" s="539"/>
+      <c r="AD14" s="540"/>
+      <c r="AE14" s="541" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="375"/>
-      <c r="B15" s="377" t="s">
+      <c r="A15" s="526"/>
+      <c r="B15" s="538" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="378"/>
-      <c r="D15" s="379"/>
-      <c r="E15" s="377" t="s">
+      <c r="C15" s="539"/>
+      <c r="D15" s="540"/>
+      <c r="E15" s="538" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="378"/>
-      <c r="G15" s="378"/>
-      <c r="H15" s="378"/>
-      <c r="I15" s="378"/>
-      <c r="J15" s="378"/>
-      <c r="K15" s="378"/>
-      <c r="L15" s="378"/>
-      <c r="M15" s="378"/>
-      <c r="N15" s="378"/>
-      <c r="O15" s="378"/>
-      <c r="P15" s="378"/>
-      <c r="Q15" s="378"/>
-      <c r="R15" s="379"/>
+      <c r="F15" s="539"/>
+      <c r="G15" s="539"/>
+      <c r="H15" s="539"/>
+      <c r="I15" s="539"/>
+      <c r="J15" s="539"/>
+      <c r="K15" s="539"/>
+      <c r="L15" s="539"/>
+      <c r="M15" s="539"/>
+      <c r="N15" s="539"/>
+      <c r="O15" s="539"/>
+      <c r="P15" s="539"/>
+      <c r="Q15" s="539"/>
+      <c r="R15" s="540"/>
       <c r="S15" s="231"/>
       <c r="T15" s="231"/>
-      <c r="U15" s="383" t="s">
+      <c r="U15" s="544" t="s">
         <v>63</v>
       </c>
-      <c r="V15" s="384"/>
-      <c r="W15" s="385"/>
-      <c r="X15" s="392" t="s">
+      <c r="V15" s="545"/>
+      <c r="W15" s="546"/>
+      <c r="X15" s="528" t="s">
         <v>64</v>
       </c>
-      <c r="Y15" s="393"/>
-      <c r="Z15" s="393"/>
-      <c r="AA15" s="394"/>
-      <c r="AB15" s="392" t="s">
+      <c r="Y15" s="530"/>
+      <c r="Z15" s="530"/>
+      <c r="AA15" s="529"/>
+      <c r="AB15" s="528" t="s">
         <v>65</v>
       </c>
-      <c r="AC15" s="393"/>
-      <c r="AD15" s="394"/>
-      <c r="AE15" s="381"/>
+      <c r="AC15" s="530"/>
+      <c r="AD15" s="529"/>
+      <c r="AE15" s="542"/>
     </row>
     <row r="16" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="375"/>
-      <c r="B16" s="374" t="s">
+      <c r="A16" s="526"/>
+      <c r="B16" s="525" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="374" t="s">
+      <c r="C16" s="525" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="374" t="s">
+      <c r="D16" s="525" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="395" t="s">
+      <c r="E16" s="553" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="396"/>
-      <c r="G16" s="396"/>
-      <c r="H16" s="396"/>
-      <c r="I16" s="396"/>
-      <c r="J16" s="396"/>
-      <c r="K16" s="396"/>
-      <c r="L16" s="396"/>
-      <c r="M16" s="397"/>
-      <c r="N16" s="392"/>
-      <c r="O16" s="393"/>
-      <c r="P16" s="393"/>
-      <c r="Q16" s="393"/>
-      <c r="R16" s="394"/>
+      <c r="F16" s="554"/>
+      <c r="G16" s="554"/>
+      <c r="H16" s="554"/>
+      <c r="I16" s="554"/>
+      <c r="J16" s="554"/>
+      <c r="K16" s="554"/>
+      <c r="L16" s="554"/>
+      <c r="M16" s="555"/>
+      <c r="N16" s="528"/>
+      <c r="O16" s="530"/>
+      <c r="P16" s="530"/>
+      <c r="Q16" s="530"/>
+      <c r="R16" s="529"/>
       <c r="S16" s="231"/>
       <c r="T16" s="231"/>
-      <c r="U16" s="386"/>
-      <c r="V16" s="387"/>
-      <c r="W16" s="388"/>
-      <c r="X16" s="398" t="s">
+      <c r="U16" s="547"/>
+      <c r="V16" s="548"/>
+      <c r="W16" s="549"/>
+      <c r="X16" s="531" t="s">
         <v>31</v>
       </c>
-      <c r="Y16" s="399"/>
-      <c r="Z16" s="400"/>
-      <c r="AA16" s="374" t="s">
+      <c r="Y16" s="532"/>
+      <c r="Z16" s="533"/>
+      <c r="AA16" s="525" t="s">
         <v>32</v>
       </c>
-      <c r="AB16" s="374" t="s">
+      <c r="AB16" s="525" t="s">
         <v>31</v>
       </c>
-      <c r="AC16" s="374" t="s">
+      <c r="AC16" s="525" t="s">
         <v>84</v>
       </c>
-      <c r="AD16" s="374" t="s">
+      <c r="AD16" s="525" t="s">
         <v>32</v>
       </c>
-      <c r="AE16" s="381"/>
+      <c r="AE16" s="542"/>
     </row>
     <row r="17" spans="1:31" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="375"/>
-      <c r="B17" s="375"/>
-      <c r="C17" s="375"/>
-      <c r="D17" s="375"/>
-      <c r="E17" s="392" t="s">
+      <c r="A17" s="526"/>
+      <c r="B17" s="526"/>
+      <c r="C17" s="526"/>
+      <c r="D17" s="526"/>
+      <c r="E17" s="528" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="394"/>
-      <c r="G17" s="392" t="s">
+      <c r="F17" s="529"/>
+      <c r="G17" s="528" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="394"/>
-      <c r="I17" s="392" t="s">
+      <c r="H17" s="529"/>
+      <c r="I17" s="528" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="393"/>
-      <c r="K17" s="394"/>
+      <c r="J17" s="530"/>
+      <c r="K17" s="529"/>
       <c r="L17" s="232" t="s">
         <v>88</v>
       </c>
-      <c r="M17" s="374" t="s">
+      <c r="M17" s="525" t="s">
         <v>35</v>
       </c>
-      <c r="N17" s="392" t="s">
+      <c r="N17" s="528" t="s">
         <v>48</v>
       </c>
-      <c r="O17" s="393"/>
-      <c r="P17" s="393"/>
-      <c r="Q17" s="394"/>
+      <c r="O17" s="530"/>
+      <c r="P17" s="530"/>
+      <c r="Q17" s="529"/>
       <c r="R17" s="233" t="s">
         <v>47</v>
       </c>
@@ -10255,23 +10253,23 @@
       <c r="T17" s="233" t="s">
         <v>76</v>
       </c>
-      <c r="U17" s="389"/>
-      <c r="V17" s="390"/>
-      <c r="W17" s="391"/>
-      <c r="X17" s="401"/>
-      <c r="Y17" s="402"/>
-      <c r="Z17" s="403"/>
-      <c r="AA17" s="375"/>
-      <c r="AB17" s="375"/>
-      <c r="AC17" s="375"/>
-      <c r="AD17" s="375"/>
-      <c r="AE17" s="381"/>
+      <c r="U17" s="550"/>
+      <c r="V17" s="551"/>
+      <c r="W17" s="552"/>
+      <c r="X17" s="534"/>
+      <c r="Y17" s="535"/>
+      <c r="Z17" s="536"/>
+      <c r="AA17" s="526"/>
+      <c r="AB17" s="526"/>
+      <c r="AC17" s="526"/>
+      <c r="AD17" s="526"/>
+      <c r="AE17" s="542"/>
     </row>
     <row r="18" spans="1:31" ht="28.5" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A18" s="376"/>
-      <c r="B18" s="376"/>
-      <c r="C18" s="376"/>
-      <c r="D18" s="376"/>
+      <c r="A18" s="527"/>
+      <c r="B18" s="527"/>
+      <c r="C18" s="527"/>
+      <c r="D18" s="527"/>
       <c r="E18" s="233" t="s">
         <v>61</v>
       </c>
@@ -10294,7 +10292,7 @@
         <v>83</v>
       </c>
       <c r="L18" s="233"/>
-      <c r="M18" s="376"/>
+      <c r="M18" s="527"/>
       <c r="N18" s="233" t="s">
         <v>154</v>
       </c>
@@ -10334,11 +10332,11 @@
       <c r="Z18" s="233" t="s">
         <v>153</v>
       </c>
-      <c r="AA18" s="376"/>
-      <c r="AB18" s="376"/>
-      <c r="AC18" s="376"/>
-      <c r="AD18" s="376"/>
-      <c r="AE18" s="382"/>
+      <c r="AA18" s="527"/>
+      <c r="AB18" s="527"/>
+      <c r="AC18" s="527"/>
+      <c r="AD18" s="527"/>
+      <c r="AE18" s="543"/>
     </row>
     <row r="19" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="214" t="s">
@@ -12330,139 +12328,139 @@
       <c r="AE40" s="195"/>
     </row>
     <row r="41" spans="1:31" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="404" t="s">
+      <c r="A41" s="501" t="s">
         <v>87</v>
       </c>
-      <c r="B41" s="405"/>
-      <c r="C41" s="405"/>
-      <c r="D41" s="405"/>
-      <c r="E41" s="405"/>
-      <c r="F41" s="405"/>
-      <c r="G41" s="406"/>
-      <c r="H41" s="407" t="s">
+      <c r="B41" s="502"/>
+      <c r="C41" s="502"/>
+      <c r="D41" s="502"/>
+      <c r="E41" s="502"/>
+      <c r="F41" s="502"/>
+      <c r="G41" s="503"/>
+      <c r="H41" s="504" t="s">
         <v>178</v>
       </c>
-      <c r="I41" s="407"/>
+      <c r="I41" s="504"/>
       <c r="J41" s="196"/>
       <c r="K41" s="196"/>
       <c r="L41" s="196"/>
       <c r="M41" s="196"/>
-      <c r="N41" s="408" t="s">
+      <c r="N41" s="505" t="s">
         <v>235</v>
       </c>
-      <c r="O41" s="408"/>
-      <c r="P41" s="408"/>
-      <c r="Q41" s="408"/>
-      <c r="R41" s="408"/>
-      <c r="S41" s="408"/>
-      <c r="T41" s="408"/>
-      <c r="U41" s="408"/>
-      <c r="V41" s="408"/>
-      <c r="W41" s="408"/>
-      <c r="X41" s="408"/>
-      <c r="Y41" s="408"/>
-      <c r="Z41" s="408"/>
-      <c r="AA41" s="408"/>
+      <c r="O41" s="505"/>
+      <c r="P41" s="505"/>
+      <c r="Q41" s="505"/>
+      <c r="R41" s="505"/>
+      <c r="S41" s="505"/>
+      <c r="T41" s="505"/>
+      <c r="U41" s="505"/>
+      <c r="V41" s="505"/>
+      <c r="W41" s="505"/>
+      <c r="X41" s="505"/>
+      <c r="Y41" s="505"/>
+      <c r="Z41" s="505"/>
+      <c r="AA41" s="505"/>
       <c r="AB41" s="105"/>
       <c r="AC41" s="105"/>
       <c r="AD41" s="105"/>
       <c r="AE41" s="197"/>
     </row>
     <row r="42" spans="1:31" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="404"/>
-      <c r="B42" s="406"/>
-      <c r="C42" s="409" t="s">
+      <c r="A42" s="501"/>
+      <c r="B42" s="503"/>
+      <c r="C42" s="506" t="s">
         <v>85</v>
       </c>
-      <c r="D42" s="410"/>
-      <c r="E42" s="409" t="s">
+      <c r="D42" s="507"/>
+      <c r="E42" s="506" t="s">
         <v>86</v>
       </c>
-      <c r="F42" s="410"/>
+      <c r="F42" s="507"/>
       <c r="G42" s="198"/>
-      <c r="H42" s="407"/>
-      <c r="I42" s="407"/>
+      <c r="H42" s="504"/>
+      <c r="I42" s="504"/>
       <c r="J42" s="196"/>
       <c r="K42" s="196"/>
       <c r="L42" s="196"/>
       <c r="M42" s="196"/>
-      <c r="N42" s="411" t="s">
+      <c r="N42" s="508" t="s">
         <v>52</v>
       </c>
-      <c r="O42" s="412"/>
-      <c r="P42" s="413"/>
-      <c r="Q42" s="420" t="s">
+      <c r="O42" s="509"/>
+      <c r="P42" s="510"/>
+      <c r="Q42" s="517" t="s">
         <v>51</v>
       </c>
-      <c r="R42" s="421"/>
-      <c r="S42" s="421"/>
-      <c r="T42" s="421"/>
-      <c r="U42" s="421"/>
-      <c r="V42" s="421"/>
-      <c r="W42" s="421"/>
-      <c r="X42" s="421"/>
-      <c r="Y42" s="421"/>
-      <c r="Z42" s="421"/>
-      <c r="AA42" s="422"/>
+      <c r="R42" s="518"/>
+      <c r="S42" s="518"/>
+      <c r="T42" s="518"/>
+      <c r="U42" s="518"/>
+      <c r="V42" s="518"/>
+      <c r="W42" s="518"/>
+      <c r="X42" s="518"/>
+      <c r="Y42" s="518"/>
+      <c r="Z42" s="518"/>
+      <c r="AA42" s="519"/>
       <c r="AB42" s="105"/>
       <c r="AC42" s="105"/>
       <c r="AD42" s="105"/>
       <c r="AE42" s="197"/>
     </row>
     <row r="43" spans="1:31" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="423" t="s">
+      <c r="A43" s="520" t="s">
         <v>155</v>
       </c>
-      <c r="B43" s="424"/>
-      <c r="C43" s="425">
+      <c r="B43" s="521"/>
+      <c r="C43" s="495">
         <v>26</v>
       </c>
-      <c r="D43" s="426"/>
-      <c r="E43" s="425">
+      <c r="D43" s="496"/>
+      <c r="E43" s="495">
         <v>5</v>
       </c>
-      <c r="F43" s="426"/>
+      <c r="F43" s="496"/>
       <c r="G43" s="199"/>
-      <c r="H43" s="435">
+      <c r="H43" s="497">
         <v>25</v>
       </c>
-      <c r="I43" s="435"/>
+      <c r="I43" s="497"/>
       <c r="J43" s="196"/>
       <c r="K43" s="196"/>
       <c r="L43" s="196"/>
       <c r="M43" s="196"/>
-      <c r="N43" s="414"/>
-      <c r="O43" s="415"/>
-      <c r="P43" s="416"/>
-      <c r="Q43" s="428" t="s">
+      <c r="N43" s="511"/>
+      <c r="O43" s="512"/>
+      <c r="P43" s="513"/>
+      <c r="Q43" s="498" t="s">
         <v>40</v>
       </c>
-      <c r="R43" s="429"/>
-      <c r="S43" s="429"/>
-      <c r="T43" s="429"/>
-      <c r="U43" s="430"/>
-      <c r="V43" s="428" t="s">
+      <c r="R43" s="499"/>
+      <c r="S43" s="499"/>
+      <c r="T43" s="499"/>
+      <c r="U43" s="500"/>
+      <c r="V43" s="498" t="s">
         <v>41</v>
       </c>
-      <c r="W43" s="430"/>
-      <c r="X43" s="428" t="s">
+      <c r="W43" s="500"/>
+      <c r="X43" s="498" t="s">
         <v>37</v>
       </c>
-      <c r="Y43" s="429"/>
-      <c r="Z43" s="429"/>
-      <c r="AA43" s="430"/>
+      <c r="Y43" s="499"/>
+      <c r="Z43" s="499"/>
+      <c r="AA43" s="500"/>
       <c r="AB43" s="105"/>
       <c r="AC43" s="105"/>
       <c r="AD43" s="105"/>
       <c r="AE43" s="197"/>
     </row>
     <row r="44" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="427"/>
-      <c r="B44" s="427"/>
-      <c r="C44" s="427"/>
-      <c r="D44" s="427"/>
-      <c r="E44" s="427"/>
-      <c r="F44" s="427"/>
+      <c r="A44" s="522"/>
+      <c r="B44" s="522"/>
+      <c r="C44" s="522"/>
+      <c r="D44" s="522"/>
+      <c r="E44" s="522"/>
+      <c r="F44" s="522"/>
       <c r="G44" s="200"/>
       <c r="H44" s="196"/>
       <c r="I44" s="196"/>
@@ -12470,15 +12468,15 @@
       <c r="K44" s="196"/>
       <c r="L44" s="196"/>
       <c r="M44" s="196"/>
-      <c r="N44" s="417"/>
-      <c r="O44" s="418"/>
-      <c r="P44" s="419"/>
-      <c r="Q44" s="428" t="s">
+      <c r="N44" s="514"/>
+      <c r="O44" s="515"/>
+      <c r="P44" s="516"/>
+      <c r="Q44" s="498" t="s">
         <v>42</v>
       </c>
-      <c r="R44" s="429"/>
-      <c r="S44" s="429"/>
-      <c r="T44" s="430"/>
+      <c r="R44" s="499"/>
+      <c r="S44" s="499"/>
+      <c r="T44" s="500"/>
       <c r="U44" s="184" t="s">
         <v>43</v>
       </c>
@@ -12488,10 +12486,10 @@
       <c r="W44" s="201" t="s">
         <v>43</v>
       </c>
-      <c r="X44" s="431" t="s">
+      <c r="X44" s="523" t="s">
         <v>42</v>
       </c>
-      <c r="Y44" s="432"/>
+      <c r="Y44" s="524"/>
       <c r="Z44" s="202"/>
       <c r="AA44" s="201" t="s">
         <v>43</v>
@@ -12502,30 +12500,32 @@
       <c r="AE44" s="197"/>
     </row>
     <row r="45" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="436"/>
-      <c r="B45" s="436"/>
-      <c r="C45" s="437"/>
-      <c r="D45" s="437"/>
-      <c r="E45" s="437"/>
+      <c r="A45" s="488"/>
+      <c r="B45" s="488"/>
+      <c r="C45" s="489"/>
+      <c r="D45" s="489"/>
+      <c r="E45" s="489"/>
       <c r="F45" s="203"/>
       <c r="G45" s="204"/>
-      <c r="H45" s="438" t="s">
+      <c r="H45" s="480" t="s">
         <v>44</v>
       </c>
-      <c r="I45" s="439"/>
-      <c r="J45" s="439"/>
-      <c r="K45" s="439"/>
-      <c r="L45" s="439"/>
-      <c r="M45" s="440"/>
-      <c r="N45" s="441"/>
-      <c r="O45" s="442"/>
-      <c r="P45" s="443"/>
-      <c r="Q45" s="444">
+      <c r="I45" s="481"/>
+      <c r="J45" s="481"/>
+      <c r="K45" s="481"/>
+      <c r="L45" s="481"/>
+      <c r="M45" s="482"/>
+      <c r="N45" s="490">
+        <v>19.72</v>
+      </c>
+      <c r="O45" s="491"/>
+      <c r="P45" s="492"/>
+      <c r="Q45" s="493">
         <v>4</v>
       </c>
-      <c r="R45" s="445"/>
-      <c r="S45" s="445"/>
-      <c r="T45" s="445"/>
+      <c r="R45" s="494"/>
+      <c r="S45" s="494"/>
+      <c r="T45" s="494"/>
       <c r="U45" s="205">
         <v>3.8</v>
       </c>
@@ -12535,11 +12535,11 @@
       <c r="W45" s="207">
         <v>8.75</v>
       </c>
-      <c r="X45" s="433">
+      <c r="X45" s="474">
         <f>Q45+V45</f>
         <v>20</v>
       </c>
-      <c r="Y45" s="434"/>
+      <c r="Y45" s="475"/>
       <c r="Z45" s="208"/>
       <c r="AA45" s="207">
         <f>U45+W45</f>
@@ -12551,30 +12551,32 @@
       <c r="AE45" s="197"/>
     </row>
     <row r="46" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="450"/>
-      <c r="B46" s="450"/>
-      <c r="C46" s="451"/>
-      <c r="D46" s="451"/>
-      <c r="E46" s="451"/>
-      <c r="F46" s="451"/>
+      <c r="A46" s="478"/>
+      <c r="B46" s="478"/>
+      <c r="C46" s="479"/>
+      <c r="D46" s="479"/>
+      <c r="E46" s="479"/>
+      <c r="F46" s="479"/>
       <c r="G46" s="204"/>
-      <c r="H46" s="438" t="s">
+      <c r="H46" s="480" t="s">
         <v>45</v>
       </c>
-      <c r="I46" s="439"/>
-      <c r="J46" s="439"/>
-      <c r="K46" s="439"/>
-      <c r="L46" s="439"/>
-      <c r="M46" s="440"/>
-      <c r="N46" s="452"/>
-      <c r="O46" s="453"/>
-      <c r="P46" s="454"/>
-      <c r="Q46" s="455">
-        <v>0</v>
-      </c>
-      <c r="R46" s="456"/>
-      <c r="S46" s="456"/>
-      <c r="T46" s="456"/>
+      <c r="I46" s="481"/>
+      <c r="J46" s="481"/>
+      <c r="K46" s="481"/>
+      <c r="L46" s="481"/>
+      <c r="M46" s="482"/>
+      <c r="N46" s="483">
+        <v>3.6</v>
+      </c>
+      <c r="O46" s="484"/>
+      <c r="P46" s="485"/>
+      <c r="Q46" s="486">
+        <v>0</v>
+      </c>
+      <c r="R46" s="487"/>
+      <c r="S46" s="487"/>
+      <c r="T46" s="487"/>
       <c r="U46" s="209">
         <v>0</v>
       </c>
@@ -12584,11 +12586,11 @@
       <c r="W46" s="207">
         <v>1.8</v>
       </c>
-      <c r="X46" s="433">
+      <c r="X46" s="474">
         <f>Q46+V46</f>
         <v>9</v>
       </c>
-      <c r="Y46" s="434"/>
+      <c r="Y46" s="475"/>
       <c r="Z46" s="208"/>
       <c r="AA46" s="207">
         <f>U46+W46</f>
@@ -12600,12 +12602,12 @@
       <c r="AE46" s="197"/>
     </row>
     <row r="47" spans="1:31" ht="20.25" x14ac:dyDescent="0.15">
-      <c r="A47" s="448"/>
-      <c r="B47" s="448"/>
-      <c r="C47" s="449"/>
-      <c r="D47" s="449"/>
-      <c r="E47" s="449"/>
-      <c r="F47" s="449"/>
+      <c r="A47" s="476"/>
+      <c r="B47" s="476"/>
+      <c r="C47" s="477"/>
+      <c r="D47" s="477"/>
+      <c r="E47" s="477"/>
+      <c r="F47" s="477"/>
       <c r="G47" s="173"/>
       <c r="H47" s="172"/>
       <c r="I47" s="172"/>
@@ -12629,29 +12631,29 @@
       <c r="AE48" s="24"/>
     </row>
     <row r="49" spans="1:31" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A49" s="446" t="s">
+      <c r="A49" s="472" t="s">
         <v>156</v>
       </c>
-      <c r="B49" s="446"/>
-      <c r="C49" s="446"/>
-      <c r="D49" s="446"/>
-      <c r="E49" s="446"/>
-      <c r="F49" s="446"/>
-      <c r="G49" s="446"/>
-      <c r="H49" s="446"/>
-      <c r="I49" s="446"/>
-      <c r="J49" s="446"/>
-      <c r="K49" s="446"/>
-      <c r="L49" s="446"/>
-      <c r="M49" s="446"/>
-      <c r="N49" s="447" t="str">
+      <c r="B49" s="472"/>
+      <c r="C49" s="472"/>
+      <c r="D49" s="472"/>
+      <c r="E49" s="472"/>
+      <c r="F49" s="472"/>
+      <c r="G49" s="472"/>
+      <c r="H49" s="472"/>
+      <c r="I49" s="472"/>
+      <c r="J49" s="472"/>
+      <c r="K49" s="472"/>
+      <c r="L49" s="472"/>
+      <c r="M49" s="472"/>
+      <c r="N49" s="473" t="str">
         <f>AB1</f>
         <v>14.09.2026</v>
       </c>
-      <c r="O49" s="447"/>
-      <c r="P49" s="447"/>
-      <c r="Q49" s="447"/>
-      <c r="R49" s="447"/>
+      <c r="O49" s="473"/>
+      <c r="P49" s="473"/>
+      <c r="Q49" s="473"/>
+      <c r="R49" s="473"/>
       <c r="S49" s="183"/>
       <c r="T49" s="183"/>
       <c r="U49" s="36"/>
@@ -12668,29 +12670,29 @@
       <c r="AE50" s="24"/>
     </row>
     <row r="51" spans="1:31" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="446" t="s">
+      <c r="A51" s="472" t="s">
         <v>157</v>
       </c>
-      <c r="B51" s="446"/>
-      <c r="C51" s="446"/>
-      <c r="D51" s="446"/>
-      <c r="E51" s="446"/>
-      <c r="F51" s="446"/>
-      <c r="G51" s="446"/>
-      <c r="H51" s="446"/>
-      <c r="I51" s="446"/>
-      <c r="J51" s="446"/>
-      <c r="K51" s="446"/>
-      <c r="L51" s="446"/>
-      <c r="M51" s="446"/>
-      <c r="N51" s="447" t="str">
+      <c r="B51" s="472"/>
+      <c r="C51" s="472"/>
+      <c r="D51" s="472"/>
+      <c r="E51" s="472"/>
+      <c r="F51" s="472"/>
+      <c r="G51" s="472"/>
+      <c r="H51" s="472"/>
+      <c r="I51" s="472"/>
+      <c r="J51" s="472"/>
+      <c r="K51" s="472"/>
+      <c r="L51" s="472"/>
+      <c r="M51" s="472"/>
+      <c r="N51" s="473" t="str">
         <f>AB1</f>
         <v>14.09.2026</v>
       </c>
-      <c r="O51" s="447"/>
-      <c r="P51" s="447"/>
-      <c r="Q51" s="447"/>
-      <c r="R51" s="447"/>
+      <c r="O51" s="473"/>
+      <c r="P51" s="473"/>
+      <c r="Q51" s="473"/>
+      <c r="R51" s="473"/>
       <c r="S51" s="175"/>
       <c r="T51" s="175"/>
       <c r="U51" s="36"/>
@@ -12748,55 +12750,32 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="A51:M51"/>
-    <mergeCell ref="N51:R51"/>
-    <mergeCell ref="X46:Y46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="A49:M49"/>
-    <mergeCell ref="N49:R49"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="Q46:T46"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="Q45:T45"/>
-    <mergeCell ref="X45:Y45"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="Q43:U43"/>
-    <mergeCell ref="V43:W43"/>
-    <mergeCell ref="X43:AA43"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="H41:I42"/>
-    <mergeCell ref="N41:AA41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="N42:P44"/>
-    <mergeCell ref="Q42:AA42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="Q44:T44"/>
-    <mergeCell ref="X44:Y44"/>
-    <mergeCell ref="AB16:AB18"/>
-    <mergeCell ref="AC16:AC18"/>
-    <mergeCell ref="AD16:AD18"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="N17:Q17"/>
-    <mergeCell ref="X16:Z17"/>
+    <mergeCell ref="B1:X1"/>
+    <mergeCell ref="AB1:AE1"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:W2"/>
+    <mergeCell ref="X2:AD2"/>
+    <mergeCell ref="AE2:AE6"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:R3"/>
+    <mergeCell ref="U3:W5"/>
+    <mergeCell ref="X3:AA3"/>
+    <mergeCell ref="AB3:AD3"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:M4"/>
+    <mergeCell ref="N4:R4"/>
+    <mergeCell ref="X4:Z5"/>
+    <mergeCell ref="AA4:AA6"/>
+    <mergeCell ref="AB4:AB6"/>
+    <mergeCell ref="AC4:AC6"/>
+    <mergeCell ref="AD4:AD6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:Q5"/>
     <mergeCell ref="A13:AE13"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="B14:W14"/>
@@ -12813,32 +12792,55 @@
     <mergeCell ref="E16:M16"/>
     <mergeCell ref="N16:R16"/>
     <mergeCell ref="AA16:AA18"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:Q5"/>
-    <mergeCell ref="X4:Z5"/>
-    <mergeCell ref="AA4:AA6"/>
-    <mergeCell ref="AB4:AB6"/>
-    <mergeCell ref="AC4:AC6"/>
-    <mergeCell ref="AD4:AD6"/>
-    <mergeCell ref="B1:X1"/>
-    <mergeCell ref="AB1:AE1"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="B2:W2"/>
-    <mergeCell ref="X2:AD2"/>
-    <mergeCell ref="AE2:AE6"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:R3"/>
-    <mergeCell ref="U3:W5"/>
-    <mergeCell ref="X3:AA3"/>
-    <mergeCell ref="AB3:AD3"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="E4:M4"/>
-    <mergeCell ref="N4:R4"/>
+    <mergeCell ref="AB16:AB18"/>
+    <mergeCell ref="AC16:AC18"/>
+    <mergeCell ref="AD16:AD18"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="N17:Q17"/>
+    <mergeCell ref="X16:Z17"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="H41:I42"/>
+    <mergeCell ref="N41:AA41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="N42:P44"/>
+    <mergeCell ref="Q42:AA42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="Q44:T44"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="X45:Y45"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="Q43:U43"/>
+    <mergeCell ref="V43:W43"/>
+    <mergeCell ref="X43:AA43"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="Q45:T45"/>
+    <mergeCell ref="A51:M51"/>
+    <mergeCell ref="N51:R51"/>
+    <mergeCell ref="X46:Y46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="A49:M49"/>
+    <mergeCell ref="N49:R49"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="Q46:T46"/>
   </mergeCells>
   <pageMargins left="0.38" right="0.27" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" verticalDpi="0" r:id="rId1"/>
